--- a/inst/extdata/blackfeet_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/blackfeet_tribe_criteria_crosswalk.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/k_salkgundersen_tetratech_com/Documents/EPA/R8_AssessmentTool/5_Work/Crosswalks/individual_criteria_crosswalks/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{19D1703B-4752-4FB9-91FC-F7CEE9456BFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE2C29A-85A3-47DA-AE79-CECEF22B8E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9CAA114B-CC1B-4AA7-94E1-A6CD4C5CB112}"/>
+    <workbookView xWindow="28690" yWindow="-110" windowWidth="20710" windowHeight="11020" xr2:uid="{9CAA114B-CC1B-4AA7-94E1-A6CD4C5CB112}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AQ$65</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -33,6 +36,24 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={74C1B013-894F-4592-8389-217DC3BFB221}</author>
+  </authors>
+  <commentList>
+    <comment ref="Q61" authorId="0" shapeId="0" xr:uid="{74C1B013-894F-4592-8389-217DC3BFB221}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Ex. Is the daily min for each day or each 7 day period?</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1076,7 +1097,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1112,6 +1133,12 @@
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1166,6 +1193,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Wong, Kenny" id="{4DAABA07-F53B-444F-99E0-85C2E47D97CC}" userId="S::Wong.Kenny@epa.gov::22d39ba2-7a17-454f-a1e0-b7fc51176133" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1483,12 +1516,24 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="Q61" dT="2025-12-22T20:49:43.95" personId="{4DAABA07-F53B-444F-99E0-85C2E47D97CC}" id="{74C1B013-894F-4592-8389-217DC3BFB221}">
+    <text>Ex. Is the daily min for each day or each 7 day period?</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{057945F5-944B-4C7F-AE65-F75344336C85}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{057945F5-944B-4C7F-AE65-F75344336C85}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AQ65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="19" max="19" width="19.7265625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="4" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" s="4" customFormat="1" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1619,7 +1664,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5"/>
       <c r="B2" s="5" t="s">
         <v>43</v>
@@ -1688,7 +1733,7 @@
       <c r="AL2" s="5"/>
       <c r="AM2" s="5"/>
     </row>
-    <row r="3" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5"/>
       <c r="B3" s="5" t="s">
         <v>43</v>
@@ -1759,7 +1804,7 @@
       <c r="AL3" s="5"/>
       <c r="AM3" s="5"/>
     </row>
-    <row r="4" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5"/>
       <c r="B4" s="5" t="s">
         <v>43</v>
@@ -1830,7 +1875,7 @@
       <c r="AL4" s="5"/>
       <c r="AM4" s="5"/>
     </row>
-    <row r="5" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5"/>
       <c r="B5" s="5" t="s">
         <v>43</v>
@@ -1897,7 +1942,7 @@
       <c r="AL5" s="5"/>
       <c r="AM5" s="5"/>
     </row>
-    <row r="6" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5"/>
       <c r="B6" s="5" t="s">
         <v>43</v>
@@ -1964,7 +2009,7 @@
       <c r="AL6" s="5"/>
       <c r="AM6" s="5"/>
     </row>
-    <row r="7" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5"/>
       <c r="B7" s="5" t="s">
         <v>43</v>
@@ -2035,7 +2080,7 @@
       <c r="AL7" s="5"/>
       <c r="AM7" s="5"/>
     </row>
-    <row r="8" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5"/>
       <c r="B8" s="5" t="s">
         <v>43</v>
@@ -2104,7 +2149,7 @@
       <c r="AL8" s="5"/>
       <c r="AM8" s="5"/>
     </row>
-    <row r="9" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5"/>
       <c r="B9" s="5" t="s">
         <v>43</v>
@@ -2171,7 +2216,7 @@
       <c r="AL9" s="5"/>
       <c r="AM9" s="5"/>
     </row>
-    <row r="10" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5"/>
       <c r="B10" s="5" t="s">
         <v>43</v>
@@ -2246,7 +2291,7 @@
       <c r="AL10" s="5"/>
       <c r="AM10" s="5"/>
     </row>
-    <row r="11" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5"/>
       <c r="B11" s="5" t="s">
         <v>43</v>
@@ -2321,7 +2366,7 @@
       <c r="AL11" s="5"/>
       <c r="AM11" s="5"/>
     </row>
-    <row r="12" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5"/>
       <c r="B12" s="5" t="s">
         <v>43</v>
@@ -2390,7 +2435,7 @@
       <c r="AL12" s="5"/>
       <c r="AM12" s="5"/>
     </row>
-    <row r="13" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5"/>
       <c r="B13" s="5" t="s">
         <v>43</v>
@@ -2461,7 +2506,7 @@
       <c r="AL13" s="5"/>
       <c r="AM13" s="5"/>
     </row>
-    <row r="14" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5"/>
       <c r="B14" s="5" t="s">
         <v>43</v>
@@ -2532,7 +2577,7 @@
       <c r="AL14" s="5"/>
       <c r="AM14" s="5"/>
     </row>
-    <row r="15" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5"/>
       <c r="B15" s="5" t="s">
         <v>43</v>
@@ -2601,7 +2646,7 @@
       <c r="AL15" s="5"/>
       <c r="AM15" s="5"/>
     </row>
-    <row r="16" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="5"/>
       <c r="B16" s="5" t="s">
         <v>43</v>
@@ -2670,7 +2715,7 @@
       <c r="AL16" s="5"/>
       <c r="AM16" s="5"/>
     </row>
-    <row r="17" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5"/>
       <c r="B17" s="5" t="s">
         <v>43</v>
@@ -2737,7 +2782,7 @@
       <c r="AL17" s="5"/>
       <c r="AM17" s="5"/>
     </row>
-    <row r="18" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="5"/>
       <c r="B18" s="5" t="s">
         <v>43</v>
@@ -2804,7 +2849,7 @@
       <c r="AL18" s="5"/>
       <c r="AM18" s="5"/>
     </row>
-    <row r="19" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="5"/>
       <c r="B19" s="5" t="s">
         <v>43</v>
@@ -2875,7 +2920,7 @@
       <c r="AL19" s="5"/>
       <c r="AM19" s="5"/>
     </row>
-    <row r="20" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="5"/>
       <c r="B20" s="5" t="s">
         <v>43</v>
@@ -2946,7 +2991,7 @@
       <c r="AL20" s="5"/>
       <c r="AM20" s="5"/>
     </row>
-    <row r="21" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5"/>
       <c r="B21" s="5" t="s">
         <v>43</v>
@@ -3015,7 +3060,7 @@
       <c r="AL21" s="5"/>
       <c r="AM21" s="5"/>
     </row>
-    <row r="22" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="5"/>
       <c r="B22" s="5" t="s">
         <v>43</v>
@@ -3084,7 +3129,7 @@
       <c r="AL22" s="5"/>
       <c r="AM22" s="5"/>
     </row>
-    <row r="23" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="5"/>
       <c r="B23" s="5" t="s">
         <v>43</v>
@@ -3153,7 +3198,7 @@
       <c r="AL23" s="5"/>
       <c r="AM23" s="5"/>
     </row>
-    <row r="24" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5"/>
       <c r="B24" s="5" t="s">
         <v>43</v>
@@ -3222,7 +3267,7 @@
       <c r="AL24" s="5"/>
       <c r="AM24" s="5"/>
     </row>
-    <row r="25" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5"/>
       <c r="B25" s="5" t="s">
         <v>43</v>
@@ -3291,7 +3336,7 @@
       <c r="AL25" s="5"/>
       <c r="AM25" s="5"/>
     </row>
-    <row r="26" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5"/>
       <c r="B26" s="5" t="s">
         <v>43</v>
@@ -3360,7 +3405,7 @@
       <c r="AL26" s="5"/>
       <c r="AM26" s="5"/>
     </row>
-    <row r="27" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="5"/>
       <c r="B27" s="5" t="s">
         <v>43</v>
@@ -3429,7 +3474,7 @@
       <c r="AL27" s="5"/>
       <c r="AM27" s="5"/>
     </row>
-    <row r="28" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="5"/>
       <c r="B28" s="5" t="s">
         <v>43</v>
@@ -3498,7 +3543,7 @@
       <c r="AL28" s="5"/>
       <c r="AM28" s="5"/>
     </row>
-    <row r="29" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5"/>
       <c r="B29" s="5" t="s">
         <v>43</v>
@@ -3567,7 +3612,7 @@
       <c r="AL29" s="5"/>
       <c r="AM29" s="5"/>
     </row>
-    <row r="30" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5"/>
       <c r="B30" s="5" t="s">
         <v>43</v>
@@ -3636,7 +3681,7 @@
       <c r="AL30" s="5"/>
       <c r="AM30" s="5"/>
     </row>
-    <row r="31" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="5"/>
       <c r="B31" s="5" t="s">
         <v>43</v>
@@ -3703,7 +3748,7 @@
       <c r="AL31" s="5"/>
       <c r="AM31" s="5"/>
     </row>
-    <row r="32" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5"/>
       <c r="B32" s="5" t="s">
         <v>43</v>
@@ -3770,7 +3815,7 @@
       <c r="AL32" s="5"/>
       <c r="AM32" s="5"/>
     </row>
-    <row r="33" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="5"/>
       <c r="B33" s="5" t="s">
         <v>43</v>
@@ -3837,7 +3882,7 @@
       <c r="AL33" s="5"/>
       <c r="AM33" s="5"/>
     </row>
-    <row r="34" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="5"/>
       <c r="B34" s="5" t="s">
         <v>43</v>
@@ -3922,7 +3967,7 @@
       </c>
       <c r="AM34" s="5"/>
     </row>
-    <row r="35" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="5"/>
       <c r="B35" s="5" t="s">
         <v>43</v>
@@ -4007,7 +4052,7 @@
       </c>
       <c r="AM35" s="5"/>
     </row>
-    <row r="36" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="5"/>
       <c r="B36" s="5" t="s">
         <v>43</v>
@@ -4088,7 +4133,7 @@
       </c>
       <c r="AM36" s="5"/>
     </row>
-    <row r="37" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="5"/>
       <c r="B37" s="5" t="s">
         <v>43</v>
@@ -4169,7 +4214,7 @@
       </c>
       <c r="AM37" s="5"/>
     </row>
-    <row r="38" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="5"/>
       <c r="B38" s="5" t="s">
         <v>43</v>
@@ -4254,7 +4299,7 @@
       </c>
       <c r="AM38" s="5"/>
     </row>
-    <row r="39" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="5"/>
       <c r="B39" s="5" t="s">
         <v>43</v>
@@ -4339,7 +4384,7 @@
       </c>
       <c r="AM39" s="5"/>
     </row>
-    <row r="40" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="5"/>
       <c r="B40" s="5" t="s">
         <v>43</v>
@@ -4420,7 +4465,7 @@
       </c>
       <c r="AM40" s="5"/>
     </row>
-    <row r="41" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="5"/>
       <c r="B41" s="5" t="s">
         <v>43</v>
@@ -4501,7 +4546,7 @@
       </c>
       <c r="AM41" s="5"/>
     </row>
-    <row r="42" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="5"/>
       <c r="B42" s="5" t="s">
         <v>43</v>
@@ -4582,7 +4627,7 @@
       </c>
       <c r="AM42" s="5"/>
     </row>
-    <row r="43" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5"/>
       <c r="B43" s="5" t="s">
         <v>43</v>
@@ -4663,7 +4708,7 @@
       </c>
       <c r="AM43" s="5"/>
     </row>
-    <row r="44" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="5"/>
       <c r="B44" s="5" t="s">
         <v>43</v>
@@ -4744,7 +4789,7 @@
       </c>
       <c r="AM44" s="5"/>
     </row>
-    <row r="45" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="5"/>
       <c r="B45" s="5" t="s">
         <v>43</v>
@@ -4811,7 +4856,7 @@
       <c r="AL45" s="5"/>
       <c r="AM45" s="5"/>
     </row>
-    <row r="46" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="5"/>
       <c r="B46" s="5" t="s">
         <v>43</v>
@@ -4880,7 +4925,7 @@
       <c r="AL46" s="5"/>
       <c r="AM46" s="5"/>
     </row>
-    <row r="47" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="5"/>
       <c r="B47" s="5" t="s">
         <v>43</v>
@@ -4949,7 +4994,7 @@
       <c r="AL47" s="5"/>
       <c r="AM47" s="5"/>
     </row>
-    <row r="48" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="5"/>
       <c r="B48" s="5" t="s">
         <v>43</v>
@@ -5020,7 +5065,7 @@
       <c r="AL48" s="5"/>
       <c r="AM48" s="5"/>
     </row>
-    <row r="49" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="5"/>
       <c r="B49" s="5" t="s">
         <v>43</v>
@@ -5091,7 +5136,7 @@
       <c r="AL49" s="5"/>
       <c r="AM49" s="5"/>
     </row>
-    <row r="50" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="5"/>
       <c r="B50" s="5" t="s">
         <v>43</v>
@@ -5160,7 +5205,7 @@
       <c r="AL50" s="5"/>
       <c r="AM50" s="5"/>
     </row>
-    <row r="51" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="5"/>
       <c r="B51" s="5" t="s">
         <v>43</v>
@@ -5227,7 +5272,7 @@
       <c r="AL51" s="5"/>
       <c r="AM51" s="5"/>
     </row>
-    <row r="52" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="5"/>
       <c r="B52" s="5" t="s">
         <v>43</v>
@@ -5298,7 +5343,7 @@
       <c r="AL52" s="5"/>
       <c r="AM52" s="5"/>
     </row>
-    <row r="53" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="5"/>
       <c r="B53" s="5" t="s">
         <v>43</v>
@@ -5367,7 +5412,7 @@
       <c r="AL53" s="5"/>
       <c r="AM53" s="5"/>
     </row>
-    <row r="54" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="5"/>
       <c r="B54" s="5" t="s">
         <v>43</v>
@@ -5436,7 +5481,7 @@
       <c r="AL54" s="5"/>
       <c r="AM54" s="5"/>
     </row>
-    <row r="55" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="5"/>
       <c r="B55" s="5" t="s">
         <v>43</v>
@@ -5503,7 +5548,7 @@
       <c r="AL55" s="5"/>
       <c r="AM55" s="5"/>
     </row>
-    <row r="56" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="5"/>
       <c r="B56" s="5" t="s">
         <v>43</v>
@@ -5570,7 +5615,7 @@
       <c r="AL56" s="5"/>
       <c r="AM56" s="5"/>
     </row>
-    <row r="57" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="5"/>
       <c r="B57" s="5" t="s">
         <v>43</v>
@@ -5637,7 +5682,7 @@
       <c r="AL57" s="5"/>
       <c r="AM57" s="5"/>
     </row>
-    <row r="58" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="5"/>
       <c r="B58" s="5" t="s">
         <v>43</v>
@@ -5704,7 +5749,7 @@
       <c r="AL58" s="5"/>
       <c r="AM58" s="5"/>
     </row>
-    <row r="59" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="5"/>
       <c r="B59" s="5" t="s">
         <v>43</v>
@@ -5775,7 +5820,7 @@
       <c r="AL59" s="5"/>
       <c r="AM59" s="5"/>
     </row>
-    <row r="60" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="5"/>
       <c r="B60" s="5" t="s">
         <v>43</v>
@@ -5846,7 +5891,7 @@
       <c r="AL60" s="5"/>
       <c r="AM60" s="5"/>
     </row>
-    <row r="61" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A61" s="5"/>
       <c r="B61" s="5" t="s">
         <v>43</v>
@@ -5917,7 +5962,7 @@
       <c r="AL61" s="5"/>
       <c r="AM61" s="5"/>
     </row>
-    <row r="62" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="5"/>
       <c r="B62" s="5" t="s">
         <v>43</v>
@@ -5988,7 +6033,7 @@
       <c r="AL62" s="5"/>
       <c r="AM62" s="5"/>
     </row>
-    <row r="63" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="5"/>
       <c r="B63" s="5" t="s">
         <v>43</v>
@@ -6059,7 +6104,7 @@
       <c r="AL63" s="5"/>
       <c r="AM63" s="5"/>
     </row>
-    <row r="64" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="5"/>
       <c r="B64" s="5" t="s">
         <v>43</v>
@@ -6134,7 +6179,7 @@
       <c r="AL64" s="5"/>
       <c r="AM64" s="5"/>
     </row>
-    <row r="65" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="5"/>
       <c r="B65" s="5" t="s">
         <v>43</v>
@@ -6210,6 +6255,14 @@
       <c r="AM65" s="5"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AQ65" xr:uid="{057945F5-944B-4C7F-AE65-F75344336C85}">
+    <filterColumn colId="18">
+      <filters>
+        <filter val="arithmetic mean min"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/inst/extdata/blackfeet_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/blackfeet_tribe_criteria_crosswalk.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE2C29A-85A3-47DA-AE79-CECEF22B8E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84252655-2FDA-46BC-8634-C1BD3E628908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28690" yWindow="-110" windowWidth="20710" windowHeight="11020" xr2:uid="{9CAA114B-CC1B-4AA7-94E1-A6CD4C5CB112}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{9CAA114B-CC1B-4AA7-94E1-A6CD4C5CB112}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -302,9 +302,6 @@
     <t>Human Health - Organism</t>
   </si>
   <si>
-    <t>Mercury Methylmercury</t>
-  </si>
-  <si>
     <t>DIMETHYLMERCURY</t>
   </si>
   <si>
@@ -314,9 +311,6 @@
     <t>METHYLMERCURY(1+)</t>
   </si>
   <si>
-    <t>Chromium VI</t>
-  </si>
-  <si>
     <t>CHROMIUM(VI)</t>
   </si>
   <si>
@@ -368,9 +362,6 @@
     <t>e^(0.7409*ln(hardness)-4.719)*(1.101672-[ln(hardness)(0.041838)])</t>
   </si>
   <si>
-    <t>Chromium III</t>
-  </si>
-  <si>
     <t>CHROMIUM(III)</t>
   </si>
   <si>
@@ -431,9 +422,6 @@
     <t>IRON</t>
   </si>
   <si>
-    <t>Nitrates</t>
-  </si>
-  <si>
     <t>NITRATE</t>
   </si>
   <si>
@@ -449,15 +437,9 @@
     <t>arithmetic extremes</t>
   </si>
   <si>
-    <t>Solids Dissolved</t>
-  </si>
-  <si>
     <t>TOTAL DISSOLVED SOLIDS</t>
   </si>
   <si>
-    <t>E. coli</t>
-  </si>
-  <si>
     <t>Primary Recreation</t>
   </si>
   <si>
@@ -473,16 +455,10 @@
     <t>Percentile</t>
   </si>
   <si>
-    <t>Microcystin</t>
-  </si>
-  <si>
     <t>MICROCYSTIN</t>
   </si>
   <si>
     <t>n-samples in 3 10-day periods</t>
-  </si>
-  <si>
-    <t>Oxygen</t>
   </si>
   <si>
     <t>DISSOLVED OXYGEN (DO)</t>
@@ -1092,12 +1068,36 @@
   <si>
     <t>0.8876*(((0.0278/(1+10^(7.688-pH)))+(1.1994/(1+10^(pH-7.688))))*(2.126*10^(0.028*(20-max(Temperature,7)))))</t>
   </si>
+  <si>
+    <t>Methylmercury</t>
+  </si>
+  <si>
+    <t>CHROMIUM, HEXAVALENT</t>
+  </si>
+  <si>
+    <t>CHROMIUM, TRIVALENT, TOTAL</t>
+  </si>
+  <si>
+    <t>Nitrate</t>
+  </si>
+  <si>
+    <t>TOTAL DISSOLVED SOLIDS (TDS)</t>
+  </si>
+  <si>
+    <t>ESCHERICHIA COLI (E. COLI)</t>
+  </si>
+  <si>
+    <t>CYANOBACTERIA HEPATOTOXIC MICROCYSTINS</t>
+  </si>
+  <si>
+    <t>DISSOLVED OXYGEN</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1133,12 +1133,6 @@
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1526,10 +1520,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{057945F5-944B-4C7F-AE65-F75344336C85}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AQ65"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="19.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1664,7 +1658,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="5"/>
       <c r="B2" s="5" t="s">
         <v>43</v>
@@ -1733,7 +1727,7 @@
       <c r="AL2" s="5"/>
       <c r="AM2" s="5"/>
     </row>
-    <row r="3" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="5"/>
       <c r="B3" s="5" t="s">
         <v>43</v>
@@ -1804,7 +1798,7 @@
       <c r="AL3" s="5"/>
       <c r="AM3" s="5"/>
     </row>
-    <row r="4" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="5"/>
       <c r="B4" s="5" t="s">
         <v>43</v>
@@ -1875,7 +1869,7 @@
       <c r="AL4" s="5"/>
       <c r="AM4" s="5"/>
     </row>
-    <row r="5" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="5"/>
       <c r="B5" s="5" t="s">
         <v>43</v>
@@ -1942,7 +1936,7 @@
       <c r="AL5" s="5"/>
       <c r="AM5" s="5"/>
     </row>
-    <row r="6" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="5"/>
       <c r="B6" s="5" t="s">
         <v>43</v>
@@ -2009,7 +2003,7 @@
       <c r="AL6" s="5"/>
       <c r="AM6" s="5"/>
     </row>
-    <row r="7" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="5"/>
       <c r="B7" s="5" t="s">
         <v>43</v>
@@ -2080,7 +2074,7 @@
       <c r="AL7" s="5"/>
       <c r="AM7" s="5"/>
     </row>
-    <row r="8" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="5"/>
       <c r="B8" s="5" t="s">
         <v>43</v>
@@ -2149,7 +2143,7 @@
       <c r="AL8" s="5"/>
       <c r="AM8" s="5"/>
     </row>
-    <row r="9" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="5"/>
       <c r="B9" s="5" t="s">
         <v>43</v>
@@ -2216,7 +2210,7 @@
       <c r="AL9" s="5"/>
       <c r="AM9" s="5"/>
     </row>
-    <row r="10" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="5"/>
       <c r="B10" s="5" t="s">
         <v>43</v>
@@ -2291,7 +2285,7 @@
       <c r="AL10" s="5"/>
       <c r="AM10" s="5"/>
     </row>
-    <row r="11" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="5"/>
       <c r="B11" s="5" t="s">
         <v>43</v>
@@ -2366,7 +2360,7 @@
       <c r="AL11" s="5"/>
       <c r="AM11" s="5"/>
     </row>
-    <row r="12" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="5"/>
       <c r="B12" s="5" t="s">
         <v>43</v>
@@ -2435,7 +2429,7 @@
       <c r="AL12" s="5"/>
       <c r="AM12" s="5"/>
     </row>
-    <row r="13" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="5"/>
       <c r="B13" s="5" t="s">
         <v>43</v>
@@ -2506,7 +2500,7 @@
       <c r="AL13" s="5"/>
       <c r="AM13" s="5"/>
     </row>
-    <row r="14" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="5"/>
       <c r="B14" s="5" t="s">
         <v>43</v>
@@ -2577,7 +2571,7 @@
       <c r="AL14" s="5"/>
       <c r="AM14" s="5"/>
     </row>
-    <row r="15" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="5"/>
       <c r="B15" s="5" t="s">
         <v>43</v>
@@ -2646,7 +2640,7 @@
       <c r="AL15" s="5"/>
       <c r="AM15" s="5"/>
     </row>
-    <row r="16" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="5"/>
       <c r="B16" s="5" t="s">
         <v>43</v>
@@ -2715,19 +2709,19 @@
       <c r="AL16" s="5"/>
       <c r="AM16" s="5"/>
     </row>
-    <row r="17" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="5"/>
       <c r="B17" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>80</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -2746,7 +2740,7 @@
         <v>0.3</v>
       </c>
       <c r="P17" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q17" s="5">
         <v>30</v>
@@ -2782,19 +2776,19 @@
       <c r="AL17" s="5"/>
       <c r="AM17" s="5"/>
     </row>
-    <row r="18" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="5"/>
       <c r="B18" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>80</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
@@ -2813,7 +2807,7 @@
         <v>0.3</v>
       </c>
       <c r="P18" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q18" s="5">
         <v>30</v>
@@ -2849,19 +2843,19 @@
       <c r="AL18" s="5"/>
       <c r="AM18" s="5"/>
     </row>
-    <row r="19" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="5"/>
       <c r="B19" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>85</v>
+        <v>148</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>75</v>
@@ -2920,19 +2914,19 @@
       <c r="AL19" s="5"/>
       <c r="AM19" s="5"/>
     </row>
-    <row r="20" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="5"/>
       <c r="B20" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>85</v>
+        <v>148</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>75</v>
@@ -2991,19 +2985,19 @@
       <c r="AL20" s="5"/>
       <c r="AM20" s="5"/>
     </row>
-    <row r="21" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="5"/>
       <c r="B21" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>73</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>75</v>
@@ -3060,19 +3054,19 @@
       <c r="AL21" s="5"/>
       <c r="AM21" s="5"/>
     </row>
-    <row r="22" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="5"/>
       <c r="B22" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>80</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>75</v>
@@ -3129,7 +3123,7 @@
       <c r="AL22" s="5"/>
       <c r="AM22" s="5"/>
     </row>
-    <row r="23" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="5"/>
       <c r="B23" s="5" t="s">
         <v>43</v>
@@ -3198,7 +3192,7 @@
       <c r="AL23" s="5"/>
       <c r="AM23" s="5"/>
     </row>
-    <row r="24" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="5"/>
       <c r="B24" s="5" t="s">
         <v>43</v>
@@ -3267,19 +3261,19 @@
       <c r="AL24" s="5"/>
       <c r="AM24" s="5"/>
     </row>
-    <row r="25" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="5"/>
       <c r="B25" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>73</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>75</v>
@@ -3336,19 +3330,19 @@
       <c r="AL25" s="5"/>
       <c r="AM25" s="5"/>
     </row>
-    <row r="26" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="5"/>
       <c r="B26" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>80</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>75</v>
@@ -3405,19 +3399,19 @@
       <c r="AL26" s="5"/>
       <c r="AM26" s="5"/>
     </row>
-    <row r="27" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="5"/>
       <c r="B27" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>73</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>75</v>
@@ -3474,19 +3468,19 @@
       <c r="AL27" s="5"/>
       <c r="AM27" s="5"/>
     </row>
-    <row r="28" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="5"/>
       <c r="B28" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>80</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>75</v>
@@ -3543,19 +3537,19 @@
       <c r="AL28" s="5"/>
       <c r="AM28" s="5"/>
     </row>
-    <row r="29" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="5"/>
       <c r="B29" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -3612,19 +3606,19 @@
       <c r="AL29" s="5"/>
       <c r="AM29" s="5"/>
     </row>
-    <row r="30" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="5"/>
       <c r="B30" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
@@ -3681,19 +3675,19 @@
       <c r="AL30" s="5"/>
       <c r="AM30" s="5"/>
     </row>
-    <row r="31" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="5"/>
       <c r="B31" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>73</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
@@ -3748,19 +3742,19 @@
       <c r="AL31" s="5"/>
       <c r="AM31" s="5"/>
     </row>
-    <row r="32" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="5"/>
       <c r="B32" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>80</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
@@ -3815,19 +3809,19 @@
       <c r="AL32" s="5"/>
       <c r="AM32" s="5"/>
     </row>
-    <row r="33" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="5"/>
       <c r="B33" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>73</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
@@ -3846,7 +3840,7 @@
         <v>7000000</v>
       </c>
       <c r="P33" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="Q33" s="5">
         <v>1</v>
@@ -3882,19 +3876,19 @@
       <c r="AL33" s="5"/>
       <c r="AM33" s="5"/>
     </row>
-    <row r="34" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="5"/>
       <c r="B34" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>75</v>
@@ -3942,13 +3936,13 @@
       <c r="AC34" s="5"/>
       <c r="AD34" s="5"/>
       <c r="AE34" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AF34" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AG34" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AH34" s="5">
         <v>1.1366719999999999</v>
@@ -3967,19 +3961,19 @@
       </c>
       <c r="AM34" s="5"/>
     </row>
-    <row r="35" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="5"/>
       <c r="B35" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>75</v>
@@ -4027,13 +4021,13 @@
       <c r="AC35" s="5"/>
       <c r="AD35" s="5"/>
       <c r="AE35" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AF35" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AG35" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AH35" s="5">
         <v>1.101672</v>
@@ -4052,19 +4046,19 @@
       </c>
       <c r="AM35" s="5"/>
     </row>
-    <row r="36" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="5"/>
       <c r="B36" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>103</v>
+        <v>149</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>75</v>
@@ -4112,13 +4106,13 @@
       <c r="AC36" s="5"/>
       <c r="AD36" s="5"/>
       <c r="AE36" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="AF36" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AG36" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="AH36" s="5"/>
       <c r="AI36" s="5"/>
@@ -4133,19 +4127,19 @@
       </c>
       <c r="AM36" s="5"/>
     </row>
-    <row r="37" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="5"/>
       <c r="B37" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>103</v>
+        <v>149</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>75</v>
@@ -4193,13 +4187,13 @@
       <c r="AC37" s="5"/>
       <c r="AD37" s="5"/>
       <c r="AE37" s="5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="AF37" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AG37" s="5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="AH37" s="5"/>
       <c r="AI37" s="5"/>
@@ -4214,7 +4208,7 @@
       </c>
       <c r="AM37" s="5"/>
     </row>
-    <row r="38" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="5"/>
       <c r="B38" s="5" t="s">
         <v>43</v>
@@ -4274,13 +4268,13 @@
       <c r="AC38" s="5"/>
       <c r="AD38" s="5"/>
       <c r="AE38" s="5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="AF38" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AG38" s="5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="AH38" s="5">
         <v>1.4620299999999999</v>
@@ -4299,7 +4293,7 @@
       </c>
       <c r="AM38" s="5"/>
     </row>
-    <row r="39" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="5"/>
       <c r="B39" s="5" t="s">
         <v>43</v>
@@ -4359,13 +4353,13 @@
       <c r="AC39" s="5"/>
       <c r="AD39" s="5"/>
       <c r="AE39" s="5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="AF39" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AG39" s="5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="AH39" s="5">
         <v>1.4620299999999999</v>
@@ -4384,19 +4378,19 @@
       </c>
       <c r="AM39" s="5"/>
     </row>
-    <row r="40" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="5"/>
       <c r="B40" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>75</v>
@@ -4444,13 +4438,13 @@
       <c r="AC40" s="5"/>
       <c r="AD40" s="5"/>
       <c r="AE40" s="5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="AF40" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AG40" s="5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="AH40" s="5"/>
       <c r="AI40" s="5"/>
@@ -4465,19 +4459,19 @@
       </c>
       <c r="AM40" s="5"/>
     </row>
-    <row r="41" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="5"/>
       <c r="B41" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>75</v>
@@ -4525,13 +4519,13 @@
       <c r="AC41" s="5"/>
       <c r="AD41" s="5"/>
       <c r="AE41" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AF41" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AG41" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AH41" s="5"/>
       <c r="AI41" s="5"/>
@@ -4546,19 +4540,19 @@
       </c>
       <c r="AM41" s="5"/>
     </row>
-    <row r="42" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="5"/>
       <c r="B42" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>75</v>
@@ -4606,13 +4600,13 @@
       <c r="AC42" s="5"/>
       <c r="AD42" s="5"/>
       <c r="AE42" s="5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="AF42" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AG42" s="5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="AH42" s="5"/>
       <c r="AI42" s="5"/>
@@ -4627,19 +4621,19 @@
       </c>
       <c r="AM42" s="5"/>
     </row>
-    <row r="43" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="5"/>
       <c r="B43" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>75</v>
@@ -4687,13 +4681,13 @@
       <c r="AC43" s="5"/>
       <c r="AD43" s="5"/>
       <c r="AE43" s="5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="AF43" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AG43" s="5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="AH43" s="5"/>
       <c r="AI43" s="5"/>
@@ -4708,19 +4702,19 @@
       </c>
       <c r="AM43" s="5"/>
     </row>
-    <row r="44" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="5"/>
       <c r="B44" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>75</v>
@@ -4768,13 +4762,13 @@
       <c r="AC44" s="5"/>
       <c r="AD44" s="5"/>
       <c r="AE44" s="5" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="AF44" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AG44" s="5" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="AH44" s="5"/>
       <c r="AI44" s="5"/>
@@ -4789,19 +4783,19 @@
       </c>
       <c r="AM44" s="5"/>
     </row>
-    <row r="45" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="5"/>
       <c r="B45" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>73</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
@@ -4856,19 +4850,19 @@
       <c r="AL45" s="5"/>
       <c r="AM45" s="5"/>
     </row>
-    <row r="46" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="5"/>
       <c r="B46" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
@@ -4925,19 +4919,19 @@
       <c r="AL46" s="5"/>
       <c r="AM46" s="5"/>
     </row>
-    <row r="47" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="5"/>
       <c r="B47" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
@@ -4994,19 +4988,19 @@
       <c r="AL47" s="5"/>
       <c r="AM47" s="5"/>
     </row>
-    <row r="48" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="5"/>
       <c r="B48" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>56</v>
@@ -5065,19 +5059,19 @@
       <c r="AL48" s="5"/>
       <c r="AM48" s="5"/>
     </row>
-    <row r="49" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="5"/>
       <c r="B49" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>56</v>
@@ -5136,19 +5130,19 @@
       <c r="AL49" s="5"/>
       <c r="AM49" s="5"/>
     </row>
-    <row r="50" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="5"/>
       <c r="B50" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
@@ -5205,19 +5199,19 @@
       <c r="AL50" s="5"/>
       <c r="AM50" s="5"/>
     </row>
-    <row r="51" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="5"/>
       <c r="B51" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>73</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
@@ -5272,19 +5266,19 @@
       <c r="AL51" s="5"/>
       <c r="AM51" s="5"/>
     </row>
-    <row r="52" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="5"/>
       <c r="B52" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
@@ -5307,7 +5301,7 @@
         <v>9</v>
       </c>
       <c r="P52" s="5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Q52" s="5">
         <v>7</v>
@@ -5316,7 +5310,7 @@
         <v>51</v>
       </c>
       <c r="S52" s="5" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="T52" s="5">
         <v>1</v>
@@ -5343,19 +5337,19 @@
       <c r="AL52" s="5"/>
       <c r="AM52" s="5"/>
     </row>
-    <row r="53" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="5"/>
       <c r="B53" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>73</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
@@ -5376,7 +5370,7 @@
         <v>9</v>
       </c>
       <c r="P53" s="5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Q53" s="5">
         <v>1</v>
@@ -5385,7 +5379,7 @@
         <v>51</v>
       </c>
       <c r="S53" s="5" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="T53" s="5">
         <v>1</v>
@@ -5412,19 +5406,19 @@
       <c r="AL53" s="5"/>
       <c r="AM53" s="5"/>
     </row>
-    <row r="54" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54" s="5"/>
       <c r="B54" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>73</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>56</v>
@@ -5481,19 +5475,19 @@
       <c r="AL54" s="5"/>
       <c r="AM54" s="5"/>
     </row>
-    <row r="55" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" s="5"/>
       <c r="B55" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
@@ -5512,7 +5506,7 @@
         <v>126</v>
       </c>
       <c r="P55" s="5" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="Q55" s="5">
         <v>90</v>
@@ -5521,7 +5515,7 @@
         <v>51</v>
       </c>
       <c r="S55" s="5" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="T55" s="5">
         <v>1</v>
@@ -5548,19 +5542,19 @@
       <c r="AL55" s="5"/>
       <c r="AM55" s="5"/>
     </row>
-    <row r="56" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56" s="5"/>
       <c r="B56" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
@@ -5579,7 +5573,7 @@
         <v>410</v>
       </c>
       <c r="P56" s="5" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="Q56" s="5">
         <v>90</v>
@@ -5594,7 +5588,7 @@
         <v>10</v>
       </c>
       <c r="U56" s="5" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="V56" s="5"/>
       <c r="W56" s="5"/>
@@ -5615,19 +5609,19 @@
       <c r="AL56" s="5"/>
       <c r="AM56" s="5"/>
     </row>
-    <row r="57" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57" s="5"/>
       <c r="B57" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
@@ -5661,7 +5655,7 @@
         <v>1</v>
       </c>
       <c r="U57" s="5" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="V57" s="5"/>
       <c r="W57" s="5"/>
@@ -5682,19 +5676,19 @@
       <c r="AL57" s="5"/>
       <c r="AM57" s="5"/>
     </row>
-    <row r="58" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A58" s="5"/>
       <c r="B58" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
@@ -5728,7 +5722,7 @@
         <v>1</v>
       </c>
       <c r="U58" s="5" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="V58" s="5"/>
       <c r="W58" s="5"/>
@@ -5749,22 +5743,22 @@
       <c r="AL58" s="5"/>
       <c r="AM58" s="5"/>
     </row>
-    <row r="59" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59" s="5"/>
       <c r="B59" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
@@ -5774,7 +5768,7 @@
       </c>
       <c r="K59" s="5"/>
       <c r="L59" s="5" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="M59" s="5" t="s">
         <v>49</v>
@@ -5784,7 +5778,7 @@
       </c>
       <c r="O59" s="5"/>
       <c r="P59" s="5" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="Q59" s="5">
         <v>7</v>
@@ -5820,22 +5814,22 @@
       <c r="AL59" s="5"/>
       <c r="AM59" s="5"/>
     </row>
-    <row r="60" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A60" s="5"/>
       <c r="B60" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
@@ -5845,7 +5839,7 @@
       </c>
       <c r="K60" s="5"/>
       <c r="L60" s="5" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="M60" s="5" t="s">
         <v>49</v>
@@ -5855,7 +5849,7 @@
       </c>
       <c r="O60" s="5"/>
       <c r="P60" s="5" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="Q60" s="5">
         <v>30</v>
@@ -5897,16 +5891,16 @@
         <v>43</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
@@ -5916,7 +5910,7 @@
       </c>
       <c r="K61" s="5"/>
       <c r="L61" s="5" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="M61" s="5" t="s">
         <v>49</v>
@@ -5926,7 +5920,7 @@
       </c>
       <c r="O61" s="5"/>
       <c r="P61" s="5" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="Q61" s="5">
         <v>7</v>
@@ -5935,7 +5929,7 @@
         <v>51</v>
       </c>
       <c r="S61" s="5" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="T61" s="5">
         <v>1</v>
@@ -5962,22 +5956,22 @@
       <c r="AL61" s="5"/>
       <c r="AM61" s="5"/>
     </row>
-    <row r="62" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A62" s="5"/>
       <c r="B62" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
@@ -5987,7 +5981,7 @@
       </c>
       <c r="K62" s="5"/>
       <c r="L62" s="5" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="M62" s="5" t="s">
         <v>49</v>
@@ -5997,7 +5991,7 @@
       </c>
       <c r="O62" s="5"/>
       <c r="P62" s="5" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="Q62" s="5">
         <v>1</v>
@@ -6006,7 +6000,7 @@
         <v>51</v>
       </c>
       <c r="S62" s="5" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="T62" s="5">
         <v>1</v>
@@ -6033,22 +6027,22 @@
       <c r="AL62" s="5"/>
       <c r="AM62" s="5"/>
     </row>
-    <row r="63" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A63" s="5"/>
       <c r="B63" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
@@ -6058,7 +6052,7 @@
       </c>
       <c r="K63" s="5"/>
       <c r="L63" s="5" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="M63" s="5" t="s">
         <v>49</v>
@@ -6068,7 +6062,7 @@
       </c>
       <c r="O63" s="5"/>
       <c r="P63" s="5" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="Q63" s="5">
         <v>1</v>
@@ -6077,7 +6071,7 @@
         <v>51</v>
       </c>
       <c r="S63" s="5" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="T63" s="5">
         <v>1</v>
@@ -6104,19 +6098,19 @@
       <c r="AL63" s="5"/>
       <c r="AM63" s="5"/>
     </row>
-    <row r="64" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A64" s="5"/>
       <c r="B64" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>56</v>
@@ -6137,7 +6131,7 @@
       <c r="N64" s="5"/>
       <c r="O64" s="5"/>
       <c r="P64" s="5" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="Q64" s="5">
         <v>1</v>
@@ -6164,13 +6158,13 @@
       <c r="AC64" s="5"/>
       <c r="AD64" s="5"/>
       <c r="AE64" s="5" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="AF64" s="5" t="s">
         <v>71</v>
       </c>
       <c r="AG64" s="5" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="AH64" s="5"/>
       <c r="AI64" s="5"/>
@@ -6179,19 +6173,19 @@
       <c r="AL64" s="5"/>
       <c r="AM64" s="5"/>
     </row>
-    <row r="65" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A65" s="5"/>
       <c r="B65" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>56</v>
@@ -6212,7 +6206,7 @@
       <c r="N65" s="5"/>
       <c r="O65" s="5"/>
       <c r="P65" s="5" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="Q65" s="5">
         <v>30</v>
@@ -6239,13 +6233,13 @@
       <c r="AC65" s="5"/>
       <c r="AD65" s="5"/>
       <c r="AE65" s="5" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="AF65" s="5" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="AG65" s="5" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="AH65" s="5"/>
       <c r="AI65" s="5"/>
@@ -6255,13 +6249,7 @@
       <c r="AM65" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ65" xr:uid="{057945F5-944B-4C7F-AE65-F75344336C85}">
-    <filterColumn colId="18">
-      <filters>
-        <filter val="arithmetic mean min"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AQ65" xr:uid="{057945F5-944B-4C7F-AE65-F75344336C85}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>

--- a/inst/extdata/blackfeet_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/blackfeet_tribe_criteria_crosswalk.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84252655-2FDA-46BC-8634-C1BD3E628908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E9182B-18E3-4224-BFD1-BB785E56107E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{9CAA114B-CC1B-4AA7-94E1-A6CD4C5CB112}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="154">
   <si>
     <t>TADA.ComparableDataIdentifier</t>
   </si>
@@ -278,9 +278,6 @@
     <t>Copper</t>
   </si>
   <si>
-    <t>Human Health - Water + organism</t>
-  </si>
-  <si>
     <t>COPPER</t>
   </si>
   <si>
@@ -299,9 +296,6 @@
     <t>MERCURY</t>
   </si>
   <si>
-    <t>Human Health - Organism</t>
-  </si>
-  <si>
     <t>DIMETHYLMERCURY</t>
   </si>
   <si>
@@ -438,9 +432,6 @@
   </si>
   <si>
     <t>TOTAL DISSOLVED SOLIDS</t>
-  </si>
-  <si>
-    <t>Primary Recreation</t>
   </si>
   <si>
     <t>ESCHERICHIA COLI</t>
@@ -1092,6 +1083,12 @@
   <si>
     <t>DISSOLVED OXYGEN</t>
   </si>
+  <si>
+    <t>Drinking Water</t>
+  </si>
+  <si>
+    <t>Recreation - Primary Contact</t>
+  </si>
 </sst>
 </file>
 
@@ -1524,6 +1521,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.6328125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="19.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2369,13 +2367,13 @@
         <v>72</v>
       </c>
       <c r="D12" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="F12" s="5" t="s">
         <v>74</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>75</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
@@ -2435,16 +2433,16 @@
         <v>43</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
@@ -2506,16 +2504,16 @@
         <v>43</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
@@ -2577,16 +2575,16 @@
         <v>43</v>
       </c>
       <c r="C15" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>79</v>
-      </c>
       <c r="F15" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
@@ -2646,16 +2644,16 @@
         <v>43</v>
       </c>
       <c r="C16" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>79</v>
-      </c>
       <c r="F16" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
@@ -2715,13 +2713,13 @@
         <v>43</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -2740,7 +2738,7 @@
         <v>0.3</v>
       </c>
       <c r="P17" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="Q17" s="5">
         <v>30</v>
@@ -2782,13 +2780,13 @@
         <v>43</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
@@ -2807,7 +2805,7 @@
         <v>0.3</v>
       </c>
       <c r="P18" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="Q18" s="5">
         <v>30</v>
@@ -2849,16 +2847,16 @@
         <v>43</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="s">
@@ -2920,16 +2918,16 @@
         <v>43</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5" t="s">
@@ -2991,16 +2989,16 @@
         <v>43</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>73</v>
+        <v>152</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
@@ -3060,16 +3058,16 @@
         <v>43</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
@@ -3132,13 +3130,13 @@
         <v>54</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>73</v>
+        <v>152</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>55</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
@@ -3201,13 +3199,13 @@
         <v>54</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>55</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
@@ -3267,16 +3265,16 @@
         <v>43</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>73</v>
+        <v>152</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
@@ -3336,16 +3334,16 @@
         <v>43</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
@@ -3405,16 +3403,16 @@
         <v>43</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>73</v>
+        <v>152</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
@@ -3474,16 +3472,16 @@
         <v>43</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
@@ -3543,13 +3541,13 @@
         <v>43</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -3612,13 +3610,13 @@
         <v>43</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
@@ -3681,13 +3679,13 @@
         <v>43</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>73</v>
+        <v>152</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
@@ -3748,13 +3746,13 @@
         <v>43</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
@@ -3815,13 +3813,13 @@
         <v>43</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>73</v>
+        <v>152</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
@@ -3840,7 +3838,7 @@
         <v>7000000</v>
       </c>
       <c r="P33" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="Q33" s="5">
         <v>1</v>
@@ -3882,16 +3880,16 @@
         <v>43</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5" t="s">
@@ -3936,13 +3934,13 @@
       <c r="AC34" s="5"/>
       <c r="AD34" s="5"/>
       <c r="AE34" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="AF34" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AG34" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="AH34" s="5">
         <v>1.1366719999999999</v>
@@ -3967,16 +3965,16 @@
         <v>43</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5" t="s">
@@ -4021,13 +4019,13 @@
       <c r="AC35" s="5"/>
       <c r="AD35" s="5"/>
       <c r="AE35" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AF35" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AG35" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AH35" s="5">
         <v>1.101672</v>
@@ -4052,16 +4050,16 @@
         <v>43</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5" t="s">
@@ -4106,13 +4104,13 @@
       <c r="AC36" s="5"/>
       <c r="AD36" s="5"/>
       <c r="AE36" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AF36" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AG36" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AH36" s="5"/>
       <c r="AI36" s="5"/>
@@ -4133,16 +4131,16 @@
         <v>43</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5" t="s">
@@ -4187,13 +4185,13 @@
       <c r="AC37" s="5"/>
       <c r="AD37" s="5"/>
       <c r="AE37" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AF37" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AG37" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AH37" s="5"/>
       <c r="AI37" s="5"/>
@@ -4214,16 +4212,16 @@
         <v>43</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5" t="s">
@@ -4268,13 +4266,13 @@
       <c r="AC38" s="5"/>
       <c r="AD38" s="5"/>
       <c r="AE38" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AF38" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AG38" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AH38" s="5">
         <v>1.4620299999999999</v>
@@ -4299,16 +4297,16 @@
         <v>43</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5" t="s">
@@ -4353,13 +4351,13 @@
       <c r="AC39" s="5"/>
       <c r="AD39" s="5"/>
       <c r="AE39" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="AF39" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AG39" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="AH39" s="5">
         <v>1.4620299999999999</v>
@@ -4384,16 +4382,16 @@
         <v>43</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5" t="s">
@@ -4438,13 +4436,13 @@
       <c r="AC40" s="5"/>
       <c r="AD40" s="5"/>
       <c r="AE40" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AF40" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AG40" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AH40" s="5"/>
       <c r="AI40" s="5"/>
@@ -4465,16 +4463,16 @@
         <v>43</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="5" t="s">
@@ -4519,13 +4517,13 @@
       <c r="AC41" s="5"/>
       <c r="AD41" s="5"/>
       <c r="AE41" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AF41" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AG41" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AH41" s="5"/>
       <c r="AI41" s="5"/>
@@ -4546,16 +4544,16 @@
         <v>43</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5" t="s">
@@ -4600,13 +4598,13 @@
       <c r="AC42" s="5"/>
       <c r="AD42" s="5"/>
       <c r="AE42" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF42" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AG42" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH42" s="5"/>
       <c r="AI42" s="5"/>
@@ -4627,16 +4625,16 @@
         <v>43</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5" t="s">
@@ -4681,13 +4679,13 @@
       <c r="AC43" s="5"/>
       <c r="AD43" s="5"/>
       <c r="AE43" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF43" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AG43" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH43" s="5"/>
       <c r="AI43" s="5"/>
@@ -4708,16 +4706,16 @@
         <v>43</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5" t="s">
@@ -4762,13 +4760,13 @@
       <c r="AC44" s="5"/>
       <c r="AD44" s="5"/>
       <c r="AE44" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AF44" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AG44" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AH44" s="5"/>
       <c r="AI44" s="5"/>
@@ -4789,13 +4787,13 @@
         <v>43</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>73</v>
+        <v>152</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
@@ -4856,13 +4854,13 @@
         <v>43</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
@@ -4925,13 +4923,13 @@
         <v>43</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
@@ -4994,13 +4992,13 @@
         <v>43</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>56</v>
@@ -5065,13 +5063,13 @@
         <v>43</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>56</v>
@@ -5136,13 +5134,13 @@
         <v>43</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
@@ -5205,13 +5203,13 @@
         <v>43</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>73</v>
+        <v>152</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
@@ -5272,13 +5270,13 @@
         <v>43</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
@@ -5301,7 +5299,7 @@
         <v>9</v>
       </c>
       <c r="P52" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="Q52" s="5">
         <v>7</v>
@@ -5310,7 +5308,7 @@
         <v>51</v>
       </c>
       <c r="S52" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="T52" s="5">
         <v>1</v>
@@ -5343,13 +5341,13 @@
         <v>43</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>73</v>
+        <v>152</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
@@ -5370,7 +5368,7 @@
         <v>9</v>
       </c>
       <c r="P53" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="Q53" s="5">
         <v>1</v>
@@ -5379,7 +5377,7 @@
         <v>51</v>
       </c>
       <c r="S53" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="T53" s="5">
         <v>1</v>
@@ -5412,13 +5410,13 @@
         <v>43</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>73</v>
+        <v>152</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>56</v>
@@ -5481,13 +5479,13 @@
         <v>43</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
@@ -5506,7 +5504,7 @@
         <v>126</v>
       </c>
       <c r="P55" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="Q55" s="5">
         <v>90</v>
@@ -5515,7 +5513,7 @@
         <v>51</v>
       </c>
       <c r="S55" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="T55" s="5">
         <v>1</v>
@@ -5548,13 +5546,13 @@
         <v>43</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
@@ -5573,7 +5571,7 @@
         <v>410</v>
       </c>
       <c r="P56" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="Q56" s="5">
         <v>90</v>
@@ -5588,7 +5586,7 @@
         <v>10</v>
       </c>
       <c r="U56" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="V56" s="5"/>
       <c r="W56" s="5"/>
@@ -5615,13 +5613,13 @@
         <v>43</v>
       </c>
       <c r="C57" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D57" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="D57" s="5" t="s">
-        <v>127</v>
-      </c>
       <c r="E57" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
@@ -5655,7 +5653,7 @@
         <v>1</v>
       </c>
       <c r="U57" s="5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="V57" s="5"/>
       <c r="W57" s="5"/>
@@ -5682,13 +5680,13 @@
         <v>43</v>
       </c>
       <c r="C58" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D58" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="D58" s="5" t="s">
-        <v>127</v>
-      </c>
       <c r="E58" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
@@ -5722,7 +5720,7 @@
         <v>1</v>
       </c>
       <c r="U58" s="5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="V58" s="5"/>
       <c r="W58" s="5"/>
@@ -5749,16 +5747,16 @@
         <v>43</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
@@ -5768,7 +5766,7 @@
       </c>
       <c r="K59" s="5"/>
       <c r="L59" s="5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="M59" s="5" t="s">
         <v>49</v>
@@ -5778,7 +5776,7 @@
       </c>
       <c r="O59" s="5"/>
       <c r="P59" s="5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="Q59" s="5">
         <v>7</v>
@@ -5820,16 +5818,16 @@
         <v>43</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
@@ -5839,7 +5837,7 @@
       </c>
       <c r="K60" s="5"/>
       <c r="L60" s="5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="M60" s="5" t="s">
         <v>49</v>
@@ -5849,7 +5847,7 @@
       </c>
       <c r="O60" s="5"/>
       <c r="P60" s="5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="Q60" s="5">
         <v>30</v>
@@ -5891,16 +5889,16 @@
         <v>43</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
@@ -5910,7 +5908,7 @@
       </c>
       <c r="K61" s="5"/>
       <c r="L61" s="5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="M61" s="5" t="s">
         <v>49</v>
@@ -5920,7 +5918,7 @@
       </c>
       <c r="O61" s="5"/>
       <c r="P61" s="5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="Q61" s="5">
         <v>7</v>
@@ -5929,7 +5927,7 @@
         <v>51</v>
       </c>
       <c r="S61" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="T61" s="5">
         <v>1</v>
@@ -5962,16 +5960,16 @@
         <v>43</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
@@ -5981,7 +5979,7 @@
       </c>
       <c r="K62" s="5"/>
       <c r="L62" s="5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="M62" s="5" t="s">
         <v>49</v>
@@ -5991,16 +5989,16 @@
       </c>
       <c r="O62" s="5"/>
       <c r="P62" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q62" s="5">
+        <v>1</v>
+      </c>
+      <c r="R62" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="S62" s="5" t="s">
         <v>137</v>
-      </c>
-      <c r="Q62" s="5">
-        <v>1</v>
-      </c>
-      <c r="R62" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="S62" s="5" t="s">
-        <v>140</v>
       </c>
       <c r="T62" s="5">
         <v>1</v>
@@ -6033,16 +6031,16 @@
         <v>43</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
@@ -6052,7 +6050,7 @@
       </c>
       <c r="K63" s="5"/>
       <c r="L63" s="5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="M63" s="5" t="s">
         <v>49</v>
@@ -6062,16 +6060,16 @@
       </c>
       <c r="O63" s="5"/>
       <c r="P63" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q63" s="5">
+        <v>1</v>
+      </c>
+      <c r="R63" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="S63" s="5" t="s">
         <v>137</v>
-      </c>
-      <c r="Q63" s="5">
-        <v>1</v>
-      </c>
-      <c r="R63" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="S63" s="5" t="s">
-        <v>140</v>
       </c>
       <c r="T63" s="5">
         <v>1</v>
@@ -6104,13 +6102,13 @@
         <v>43</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>56</v>
@@ -6131,7 +6129,7 @@
       <c r="N64" s="5"/>
       <c r="O64" s="5"/>
       <c r="P64" s="5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="Q64" s="5">
         <v>1</v>
@@ -6158,13 +6156,13 @@
       <c r="AC64" s="5"/>
       <c r="AD64" s="5"/>
       <c r="AE64" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="AF64" s="5" t="s">
         <v>71</v>
       </c>
       <c r="AG64" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="AH64" s="5"/>
       <c r="AI64" s="5"/>
@@ -6179,13 +6177,13 @@
         <v>43</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>56</v>
@@ -6206,7 +6204,7 @@
       <c r="N65" s="5"/>
       <c r="O65" s="5"/>
       <c r="P65" s="5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="Q65" s="5">
         <v>30</v>
@@ -6233,13 +6231,13 @@
       <c r="AC65" s="5"/>
       <c r="AD65" s="5"/>
       <c r="AE65" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="AF65" s="5" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="AG65" s="5" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AH65" s="5"/>
       <c r="AI65" s="5"/>

--- a/inst/extdata/blackfeet_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/blackfeet_tribe_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/sheila_saia_tetratech_com/Documents/Documents/github/TADACommunityHub/inst/extdata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="13_ncr:1_{82E9182B-18E3-4224-BFD1-BB785E56107E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E74FD0B-30E2-414D-9D8E-FB136CACD6F8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBB60F2B-4287-4E1F-B327-A1104AEB08CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9CAA114B-CC1B-4AA7-94E1-A6CD4C5CB112}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{9CAA114B-CC1B-4AA7-94E1-A6CD4C5CB112}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -383,9 +383,6 @@
     <t>ESCHERICHIA COLI</t>
   </si>
   <si>
-    <t>#/100mL</t>
-  </si>
-  <si>
     <t>geometric mean</t>
   </si>
   <si>
@@ -498,6 +495,9 @@
   </si>
   <si>
     <t>0.986*e^(0.8473*ln(hardness)+0.884)</t>
+  </si>
+  <si>
+    <t>CFU/100ML</t>
   </si>
 </sst>
 </file>
@@ -907,19 +907,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{057945F5-944B-4C7F-AE65-F75344336C85}">
   <dimension ref="A1:AP65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="9.140625" style="3"/>
+    <col min="1" max="2" width="9.1796875" style="3"/>
     <col min="3" max="3" width="27" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="18" width="9.140625" style="3"/>
-    <col min="19" max="19" width="19.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="20" max="31" width="9.140625" style="3"/>
-    <col min="32" max="32" width="12.42578125" style="3" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="3"/>
+    <col min="4" max="4" width="31.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="18" width="9.1796875" style="3"/>
+    <col min="19" max="19" width="19.7265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="20" max="31" width="9.1796875" style="3"/>
+    <col min="32" max="32" width="12.453125" style="3" customWidth="1"/>
+    <col min="33" max="16384" width="9.1796875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:42" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="4"/>
       <c r="B2" s="4" t="s">
         <v>42</v>
@@ -1119,7 +1119,7 @@
       <c r="AO2" s="6"/>
       <c r="AP2" s="6"/>
     </row>
-    <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="s">
         <v>42</v>
@@ -1193,7 +1193,7 @@
       <c r="AO3" s="6"/>
       <c r="AP3" s="6"/>
     </row>
-    <row r="4" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="s">
         <v>42</v>
@@ -1267,7 +1267,7 @@
       <c r="AO4" s="6"/>
       <c r="AP4" s="6"/>
     </row>
-    <row r="5" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
         <v>42</v>
@@ -1337,7 +1337,7 @@
       <c r="AO5" s="6"/>
       <c r="AP5" s="6"/>
     </row>
-    <row r="6" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
         <v>42</v>
@@ -1407,7 +1407,7 @@
       <c r="AO6" s="6"/>
       <c r="AP6" s="6"/>
     </row>
-    <row r="7" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>42</v>
@@ -1481,7 +1481,7 @@
       <c r="AO7" s="6"/>
       <c r="AP7" s="6"/>
     </row>
-    <row r="8" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>42</v>
@@ -1553,7 +1553,7 @@
       <c r="AO8" s="6"/>
       <c r="AP8" s="6"/>
     </row>
-    <row r="9" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>42</v>
@@ -1623,7 +1623,7 @@
       <c r="AO9" s="6"/>
       <c r="AP9" s="6"/>
     </row>
-    <row r="10" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>42</v>
@@ -1699,7 +1699,7 @@
       <c r="AO10" s="6"/>
       <c r="AP10" s="6"/>
     </row>
-    <row r="11" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
         <v>42</v>
@@ -1775,7 +1775,7 @@
       <c r="AO11" s="6"/>
       <c r="AP11" s="6"/>
     </row>
-    <row r="12" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
         <v>42</v>
@@ -1784,7 +1784,7 @@
         <v>71</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>72</v>
@@ -1847,7 +1847,7 @@
       <c r="AO12" s="6"/>
       <c r="AP12" s="6"/>
     </row>
-    <row r="13" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
         <v>42</v>
@@ -1921,7 +1921,7 @@
       <c r="AO13" s="6"/>
       <c r="AP13" s="6"/>
     </row>
-    <row r="14" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
         <v>42</v>
@@ -1995,7 +1995,7 @@
       <c r="AO14" s="6"/>
       <c r="AP14" s="6"/>
     </row>
-    <row r="15" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="4"/>
       <c r="B15" s="4" t="s">
         <v>42</v>
@@ -2004,7 +2004,7 @@
         <v>76</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>77</v>
@@ -2067,7 +2067,7 @@
       <c r="AO15" s="6"/>
       <c r="AP15" s="6"/>
     </row>
-    <row r="16" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="4"/>
       <c r="B16" s="4" t="s">
         <v>42</v>
@@ -2139,13 +2139,13 @@
       <c r="AO16" s="6"/>
       <c r="AP16" s="6"/>
     </row>
-    <row r="17" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="4"/>
       <c r="B17" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>44</v>
@@ -2209,13 +2209,13 @@
       <c r="AO17" s="6"/>
       <c r="AP17" s="6"/>
     </row>
-    <row r="18" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="4"/>
       <c r="B18" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>44</v>
@@ -2279,13 +2279,13 @@
       <c r="AO18" s="6"/>
       <c r="AP18" s="6"/>
     </row>
-    <row r="19" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="4"/>
       <c r="B19" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>44</v>
@@ -2353,13 +2353,13 @@
       <c r="AO19" s="6"/>
       <c r="AP19" s="6"/>
     </row>
-    <row r="20" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="4"/>
       <c r="B20" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>44</v>
@@ -2427,7 +2427,7 @@
       <c r="AO20" s="6"/>
       <c r="AP20" s="6"/>
     </row>
-    <row r="21" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="4"/>
       <c r="B21" s="4" t="s">
         <v>42</v>
@@ -2436,7 +2436,7 @@
         <v>82</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>83</v>
@@ -2499,7 +2499,7 @@
       <c r="AO21" s="6"/>
       <c r="AP21" s="6"/>
     </row>
-    <row r="22" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="4"/>
       <c r="B22" s="4" t="s">
         <v>42</v>
@@ -2571,7 +2571,7 @@
       <c r="AO22" s="6"/>
       <c r="AP22" s="6"/>
     </row>
-    <row r="23" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="4"/>
       <c r="B23" s="4" t="s">
         <v>42</v>
@@ -2580,7 +2580,7 @@
         <v>53</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>54</v>
@@ -2643,7 +2643,7 @@
       <c r="AO23" s="6"/>
       <c r="AP23" s="6"/>
     </row>
-    <row r="24" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="4"/>
       <c r="B24" s="4" t="s">
         <v>42</v>
@@ -2715,7 +2715,7 @@
       <c r="AO24" s="6"/>
       <c r="AP24" s="6"/>
     </row>
-    <row r="25" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="4"/>
       <c r="B25" s="4" t="s">
         <v>42</v>
@@ -2724,7 +2724,7 @@
         <v>84</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>85</v>
@@ -2787,7 +2787,7 @@
       <c r="AO25" s="6"/>
       <c r="AP25" s="6"/>
     </row>
-    <row r="26" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="4"/>
       <c r="B26" s="4" t="s">
         <v>42</v>
@@ -2859,7 +2859,7 @@
       <c r="AO26" s="6"/>
       <c r="AP26" s="6"/>
     </row>
-    <row r="27" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="4"/>
       <c r="B27" s="4" t="s">
         <v>42</v>
@@ -2868,7 +2868,7 @@
         <v>86</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>87</v>
@@ -2931,7 +2931,7 @@
       <c r="AO27" s="6"/>
       <c r="AP27" s="6"/>
     </row>
-    <row r="28" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="4"/>
       <c r="B28" s="4" t="s">
         <v>42</v>
@@ -3003,7 +3003,7 @@
       <c r="AO28" s="6"/>
       <c r="AP28" s="6"/>
     </row>
-    <row r="29" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="s">
         <v>42</v>
@@ -3075,7 +3075,7 @@
       <c r="AO29" s="6"/>
       <c r="AP29" s="6"/>
     </row>
-    <row r="30" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="4"/>
       <c r="B30" s="4" t="s">
         <v>42</v>
@@ -3147,7 +3147,7 @@
       <c r="AO30" s="6"/>
       <c r="AP30" s="6"/>
     </row>
-    <row r="31" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="4"/>
       <c r="B31" s="4" t="s">
         <v>42</v>
@@ -3156,7 +3156,7 @@
         <v>88</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>89</v>
@@ -3217,7 +3217,7 @@
       <c r="AO31" s="6"/>
       <c r="AP31" s="6"/>
     </row>
-    <row r="32" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="4"/>
       <c r="B32" s="4" t="s">
         <v>42</v>
@@ -3287,7 +3287,7 @@
       <c r="AO32" s="6"/>
       <c r="AP32" s="6"/>
     </row>
-    <row r="33" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="4"/>
       <c r="B33" s="4" t="s">
         <v>42</v>
@@ -3296,7 +3296,7 @@
         <v>90</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>91</v>
@@ -3357,7 +3357,7 @@
       <c r="AO33" s="6"/>
       <c r="AP33" s="6"/>
     </row>
-    <row r="34" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="4"/>
       <c r="B34" s="4" t="s">
         <v>42</v>
@@ -3420,7 +3420,7 @@
         <v>95</v>
       </c>
       <c r="AF34" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AG34" s="4">
         <v>1.1366719999999999</v>
@@ -3443,7 +3443,7 @@
       <c r="AO34" s="6"/>
       <c r="AP34" s="6"/>
     </row>
-    <row r="35" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="4"/>
       <c r="B35" s="4" t="s">
         <v>42</v>
@@ -3506,7 +3506,7 @@
         <v>95</v>
       </c>
       <c r="AF35" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AG35" s="4">
         <v>1.101672</v>
@@ -3529,13 +3529,13 @@
       <c r="AO35" s="6"/>
       <c r="AP35" s="6"/>
     </row>
-    <row r="36" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="4"/>
       <c r="B36" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>44</v>
@@ -3592,7 +3592,7 @@
         <v>95</v>
       </c>
       <c r="AF36" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG36" s="4"/>
       <c r="AH36" s="4"/>
@@ -3611,13 +3611,13 @@
       <c r="AO36" s="6"/>
       <c r="AP36" s="6"/>
     </row>
-    <row r="37" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="4"/>
       <c r="B37" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>44</v>
@@ -3674,7 +3674,7 @@
         <v>95</v>
       </c>
       <c r="AF37" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AG37" s="4"/>
       <c r="AH37" s="4"/>
@@ -3693,7 +3693,7 @@
       <c r="AO37" s="6"/>
       <c r="AP37" s="6"/>
     </row>
-    <row r="38" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="4"/>
       <c r="B38" s="4" t="s">
         <v>42</v>
@@ -3756,7 +3756,7 @@
         <v>95</v>
       </c>
       <c r="AF38" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AG38" s="4">
         <v>1.4620299999999999</v>
@@ -3779,7 +3779,7 @@
       <c r="AO38" s="6"/>
       <c r="AP38" s="6"/>
     </row>
-    <row r="39" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="4"/>
       <c r="B39" s="4" t="s">
         <v>42</v>
@@ -3842,7 +3842,7 @@
         <v>95</v>
       </c>
       <c r="AF39" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AG39" s="4">
         <v>1.4620299999999999</v>
@@ -3865,7 +3865,7 @@
       <c r="AO39" s="6"/>
       <c r="AP39" s="6"/>
     </row>
-    <row r="40" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="4"/>
       <c r="B40" s="4" t="s">
         <v>42</v>
@@ -3928,7 +3928,7 @@
         <v>95</v>
       </c>
       <c r="AF40" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG40" s="4"/>
       <c r="AH40" s="4"/>
@@ -3947,7 +3947,7 @@
       <c r="AO40" s="6"/>
       <c r="AP40" s="6"/>
     </row>
-    <row r="41" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="4"/>
       <c r="B41" s="4" t="s">
         <v>42</v>
@@ -4010,7 +4010,7 @@
         <v>95</v>
       </c>
       <c r="AF41" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AG41" s="4"/>
       <c r="AH41" s="4"/>
@@ -4029,7 +4029,7 @@
       <c r="AO41" s="6"/>
       <c r="AP41" s="6"/>
     </row>
-    <row r="42" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="4"/>
       <c r="B42" s="4" t="s">
         <v>42</v>
@@ -4092,7 +4092,7 @@
         <v>95</v>
       </c>
       <c r="AF42" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AG42" s="4"/>
       <c r="AH42" s="4"/>
@@ -4111,7 +4111,7 @@
       <c r="AO42" s="6"/>
       <c r="AP42" s="6"/>
     </row>
-    <row r="43" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="4"/>
       <c r="B43" s="4" t="s">
         <v>42</v>
@@ -4174,7 +4174,7 @@
         <v>95</v>
       </c>
       <c r="AF43" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AG43" s="4"/>
       <c r="AH43" s="4"/>
@@ -4193,7 +4193,7 @@
       <c r="AO43" s="6"/>
       <c r="AP43" s="6"/>
     </row>
-    <row r="44" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="4"/>
       <c r="B44" s="4" t="s">
         <v>42</v>
@@ -4256,7 +4256,7 @@
         <v>95</v>
       </c>
       <c r="AF44" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AG44" s="4"/>
       <c r="AH44" s="4"/>
@@ -4275,7 +4275,7 @@
       <c r="AO44" s="6"/>
       <c r="AP44" s="6"/>
     </row>
-    <row r="45" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="4"/>
       <c r="B45" s="4" t="s">
         <v>42</v>
@@ -4284,7 +4284,7 @@
         <v>99</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>100</v>
@@ -4345,7 +4345,7 @@
       <c r="AO45" s="6"/>
       <c r="AP45" s="6"/>
     </row>
-    <row r="46" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="4"/>
       <c r="B46" s="4" t="s">
         <v>42</v>
@@ -4417,7 +4417,7 @@
       <c r="AO46" s="6"/>
       <c r="AP46" s="6"/>
     </row>
-    <row r="47" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="4"/>
       <c r="B47" s="4" t="s">
         <v>42</v>
@@ -4489,7 +4489,7 @@
       <c r="AO47" s="6"/>
       <c r="AP47" s="6"/>
     </row>
-    <row r="48" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="4"/>
       <c r="B48" s="4" t="s">
         <v>42</v>
@@ -4563,7 +4563,7 @@
       <c r="AO48" s="6"/>
       <c r="AP48" s="6"/>
     </row>
-    <row r="49" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="4"/>
       <c r="B49" s="4" t="s">
         <v>42</v>
@@ -4637,7 +4637,7 @@
       <c r="AO49" s="6"/>
       <c r="AP49" s="6"/>
     </row>
-    <row r="50" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="4"/>
       <c r="B50" s="4" t="s">
         <v>42</v>
@@ -4709,16 +4709,16 @@
       <c r="AO50" s="6"/>
       <c r="AP50" s="6"/>
     </row>
-    <row r="51" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="4"/>
       <c r="B51" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>107</v>
@@ -4779,7 +4779,7 @@
       <c r="AO51" s="6"/>
       <c r="AP51" s="6"/>
     </row>
-    <row r="52" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="4"/>
       <c r="B52" s="4" t="s">
         <v>42</v>
@@ -4853,7 +4853,7 @@
       <c r="AO52" s="6"/>
       <c r="AP52" s="6"/>
     </row>
-    <row r="53" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="4"/>
       <c r="B53" s="4" t="s">
         <v>42</v>
@@ -4862,7 +4862,7 @@
         <v>108</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>109</v>
@@ -4925,16 +4925,16 @@
       <c r="AO53" s="6"/>
       <c r="AP53" s="6"/>
     </row>
-    <row r="54" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54" s="4"/>
       <c r="B54" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>112</v>
@@ -4997,16 +4997,16 @@
       <c r="AO54" s="6"/>
       <c r="AP54" s="6"/>
     </row>
-    <row r="55" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" s="4"/>
       <c r="B55" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>113</v>
@@ -5028,7 +5028,7 @@
         <v>126</v>
       </c>
       <c r="P55" s="4" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="Q55" s="4">
         <v>90</v>
@@ -5037,7 +5037,7 @@
         <v>50</v>
       </c>
       <c r="S55" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="T55" s="4">
         <v>1</v>
@@ -5067,16 +5067,16 @@
       <c r="AO55" s="6"/>
       <c r="AP55" s="6"/>
     </row>
-    <row r="56" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56" s="4"/>
       <c r="B56" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>113</v>
@@ -5098,7 +5098,7 @@
         <v>410</v>
       </c>
       <c r="P56" s="4" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="Q56" s="4">
         <v>90</v>
@@ -5113,7 +5113,7 @@
         <v>10</v>
       </c>
       <c r="U56" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="V56" s="4"/>
       <c r="W56" s="4"/>
@@ -5137,19 +5137,19 @@
       <c r="AO56" s="6"/>
       <c r="AP56" s="6"/>
     </row>
-    <row r="57" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57" s="4"/>
       <c r="B57" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
@@ -5183,7 +5183,7 @@
         <v>1</v>
       </c>
       <c r="U57" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="V57" s="4"/>
       <c r="W57" s="4"/>
@@ -5207,19 +5207,19 @@
       <c r="AO57" s="6"/>
       <c r="AP57" s="6"/>
     </row>
-    <row r="58" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A58" s="4"/>
       <c r="B58" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="4"/>
@@ -5253,7 +5253,7 @@
         <v>1</v>
       </c>
       <c r="U58" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="V58" s="4"/>
       <c r="W58" s="4"/>
@@ -5277,22 +5277,22 @@
       <c r="AO58" s="6"/>
       <c r="AP58" s="6"/>
     </row>
-    <row r="59" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59" s="4"/>
       <c r="B59" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E59" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F59" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>120</v>
       </c>
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="K59" s="4"/>
       <c r="L59" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M59" s="4" t="s">
         <v>48</v>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="O59" s="4"/>
       <c r="P59" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q59" s="4">
         <v>7</v>
@@ -5351,22 +5351,22 @@
       <c r="AO59" s="6"/>
       <c r="AP59" s="6"/>
     </row>
-    <row r="60" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A60" s="4"/>
       <c r="B60" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E60" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F60" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>120</v>
       </c>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="K60" s="4"/>
       <c r="L60" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M60" s="4" t="s">
         <v>48</v>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="O60" s="4"/>
       <c r="P60" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q60" s="4">
         <v>30</v>
@@ -5425,22 +5425,22 @@
       <c r="AO60" s="6"/>
       <c r="AP60" s="6"/>
     </row>
-    <row r="61" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A61" s="4"/>
       <c r="B61" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E61" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F61" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>120</v>
       </c>
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="K61" s="4"/>
       <c r="L61" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M61" s="4" t="s">
         <v>48</v>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="O61" s="4"/>
       <c r="P61" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q61" s="4">
         <v>7</v>
@@ -5469,7 +5469,7 @@
         <v>50</v>
       </c>
       <c r="S61" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="T61" s="4">
         <v>1</v>
@@ -5499,22 +5499,22 @@
       <c r="AO61" s="6"/>
       <c r="AP61" s="6"/>
     </row>
-    <row r="62" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A62" s="4"/>
       <c r="B62" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E62" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F62" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>120</v>
       </c>
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="K62" s="4"/>
       <c r="L62" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M62" s="4" t="s">
         <v>48</v>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="O62" s="4"/>
       <c r="P62" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q62" s="4">
         <v>1</v>
@@ -5543,7 +5543,7 @@
         <v>50</v>
       </c>
       <c r="S62" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="T62" s="4">
         <v>1</v>
@@ -5573,22 +5573,22 @@
       <c r="AO62" s="6"/>
       <c r="AP62" s="6"/>
     </row>
-    <row r="63" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A63" s="4"/>
       <c r="B63" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E63" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F63" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>120</v>
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="K63" s="4"/>
       <c r="L63" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M63" s="4" t="s">
         <v>48</v>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="O63" s="4"/>
       <c r="P63" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q63" s="4">
         <v>1</v>
@@ -5617,7 +5617,7 @@
         <v>50</v>
       </c>
       <c r="S63" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="T63" s="4">
         <v>1</v>
@@ -5647,19 +5647,19 @@
       <c r="AO63" s="6"/>
       <c r="AP63" s="6"/>
     </row>
-    <row r="64" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A64" s="4"/>
       <c r="B64" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>55</v>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="K64" s="4"/>
       <c r="L64" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M64" s="4" t="s">
         <v>67</v>
@@ -5682,7 +5682,7 @@
       <c r="N64" s="4"/>
       <c r="O64" s="4"/>
       <c r="P64" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q64" s="4">
         <v>1</v>
@@ -5709,10 +5709,10 @@
       <c r="AC64" s="4"/>
       <c r="AD64" s="4"/>
       <c r="AE64" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AF64" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AG64" s="4"/>
       <c r="AH64" s="4"/>
@@ -5725,19 +5725,19 @@
       <c r="AO64" s="6"/>
       <c r="AP64" s="6"/>
     </row>
-    <row r="65" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A65" s="4"/>
       <c r="B65" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F65" s="4" t="s">
         <v>55</v>
@@ -5758,7 +5758,7 @@
       <c r="N65" s="4"/>
       <c r="O65" s="4"/>
       <c r="P65" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q65" s="4">
         <v>30</v>
@@ -5785,10 +5785,10 @@
       <c r="AC65" s="4"/>
       <c r="AD65" s="4"/>
       <c r="AE65" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="AF65" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="AF65" s="4" t="s">
-        <v>129</v>
       </c>
       <c r="AG65" s="4"/>
       <c r="AH65" s="4"/>

--- a/inst/extdata/blackfeet_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/blackfeet_tribe_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBB60F2B-4287-4E1F-B327-A1104AEB08CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2059C3BF-FEA9-4515-96A4-28B4B0F0BCB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{9CAA114B-CC1B-4AA7-94E1-A6CD4C5CB112}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{9CAA114B-CC1B-4AA7-94E1-A6CD4C5CB112}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -134,9 +134,6 @@
     <t>EquationType</t>
   </si>
   <si>
-    <t>Equation</t>
-  </si>
-  <si>
     <t>hardness_param_1</t>
   </si>
   <si>
@@ -498,6 +495,9 @@
   </si>
   <si>
     <t>CFU/100ML</t>
+  </si>
+  <si>
+    <t>EquationFormula</t>
   </si>
 </sst>
 </file>
@@ -907,19 +907,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{057945F5-944B-4C7F-AE65-F75344336C85}">
   <dimension ref="A1:AP65"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.1796875" style="3"/>
+    <col min="1" max="2" width="9.140625" style="3"/>
     <col min="3" max="3" width="27" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.54296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="18" width="9.1796875" style="3"/>
-    <col min="19" max="19" width="19.7265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="20" max="31" width="9.1796875" style="3"/>
-    <col min="32" max="32" width="12.453125" style="3" customWidth="1"/>
-    <col min="33" max="16384" width="9.1796875" style="3"/>
+    <col min="4" max="4" width="31.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="18" width="9.140625" style="3"/>
+    <col min="19" max="19" width="19.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="20" max="31" width="9.140625" style="3"/>
+    <col min="32" max="32" width="12.42578125" style="3" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="46.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:42" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1014,88 +1014,88 @@
         <v>30</v>
       </c>
       <c r="AF1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="AG1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AK1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>45</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N2" s="4"/>
       <c r="O2" s="4">
         <v>20000</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q2" s="4">
         <v>4</v>
       </c>
       <c r="R2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="T2" s="4">
+        <v>1</v>
+      </c>
+      <c r="U2" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="T2" s="4">
-        <v>1</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>52</v>
       </c>
       <c r="V2" s="4"/>
       <c r="W2" s="4"/>
@@ -1119,57 +1119,57 @@
       <c r="AO2" s="6"/>
       <c r="AP2" s="6"/>
     </row>
-    <row r="3" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>55</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K3" s="4"/>
       <c r="L3" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N3" s="4"/>
       <c r="O3" s="4">
         <v>1.5</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q3" s="4">
         <v>30</v>
       </c>
       <c r="R3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S3" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S3" s="4" t="s">
+      <c r="T3" s="4">
+        <v>1</v>
+      </c>
+      <c r="U3" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="T3" s="4">
-        <v>1</v>
-      </c>
-      <c r="U3" s="4" t="s">
-        <v>52</v>
       </c>
       <c r="V3" s="4"/>
       <c r="W3" s="4"/>
@@ -1193,57 +1193,57 @@
       <c r="AO3" s="6"/>
       <c r="AP3" s="6"/>
     </row>
-    <row r="4" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>55</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K4" s="4"/>
       <c r="L4" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N4" s="4"/>
       <c r="O4" s="4">
         <v>3.1</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q4" s="4">
         <v>30</v>
       </c>
       <c r="R4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S4" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S4" s="4" t="s">
+      <c r="T4" s="4">
+        <v>1</v>
+      </c>
+      <c r="U4" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="T4" s="4">
-        <v>1</v>
-      </c>
-      <c r="U4" s="4" t="s">
-        <v>52</v>
       </c>
       <c r="V4" s="4"/>
       <c r="W4" s="4"/>
@@ -1267,53 +1267,53 @@
       <c r="AO4" s="6"/>
       <c r="AP4" s="6"/>
     </row>
-    <row r="5" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>59</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N5" s="4"/>
       <c r="O5" s="4">
         <v>5.6</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q5" s="4">
         <v>30</v>
       </c>
       <c r="R5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S5" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S5" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="T5" s="4">
         <v>1</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V5" s="4"/>
       <c r="W5" s="4"/>
@@ -1337,53 +1337,53 @@
       <c r="AO5" s="6"/>
       <c r="AP5" s="6"/>
     </row>
-    <row r="6" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>59</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N6" s="4"/>
       <c r="O6" s="4">
         <v>5.6</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q6" s="4">
         <v>30</v>
       </c>
       <c r="R6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S6" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S6" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="T6" s="4">
         <v>1</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V6" s="4"/>
       <c r="W6" s="4"/>
@@ -1407,57 +1407,57 @@
       <c r="AO6" s="6"/>
       <c r="AP6" s="6"/>
     </row>
-    <row r="7" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>63</v>
-      </c>
       <c r="F7" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N7" s="4"/>
       <c r="O7" s="4">
         <v>340</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q7" s="4">
         <v>1</v>
       </c>
       <c r="R7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S7" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S7" s="4" t="s">
+      <c r="T7" s="4">
+        <v>1</v>
+      </c>
+      <c r="U7" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="T7" s="4">
-        <v>1</v>
-      </c>
-      <c r="U7" s="4" t="s">
-        <v>52</v>
       </c>
       <c r="V7" s="4"/>
       <c r="W7" s="4"/>
@@ -1481,55 +1481,55 @@
       <c r="AO7" s="6"/>
       <c r="AP7" s="6"/>
     </row>
-    <row r="8" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>63</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N8" s="4"/>
       <c r="O8" s="4">
         <v>150</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q8" s="4">
         <v>4</v>
       </c>
       <c r="R8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S8" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S8" s="4" t="s">
+      <c r="T8" s="4">
+        <v>1</v>
+      </c>
+      <c r="U8" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="T8" s="4">
-        <v>1</v>
-      </c>
-      <c r="U8" s="4" t="s">
-        <v>52</v>
       </c>
       <c r="V8" s="4"/>
       <c r="W8" s="4"/>
@@ -1553,53 +1553,53 @@
       <c r="AO8" s="6"/>
       <c r="AP8" s="6"/>
     </row>
-    <row r="9" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>63</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N9" s="4"/>
       <c r="O9" s="4">
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q9" s="4">
         <v>30</v>
       </c>
       <c r="R9" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S9" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S9" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="T9" s="4">
         <v>1</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V9" s="4"/>
       <c r="W9" s="4"/>
@@ -1623,55 +1623,55 @@
       <c r="AO9" s="6"/>
       <c r="AP9" s="6"/>
     </row>
-    <row r="10" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>66</v>
-      </c>
       <c r="F10" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
       <c r="P10" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q10" s="4">
         <v>1</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T10" s="4">
         <v>1</v>
       </c>
       <c r="U10" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V10" s="4"/>
       <c r="W10" s="4"/>
@@ -1683,10 +1683,10 @@
       <c r="AC10" s="4"/>
       <c r="AD10" s="4"/>
       <c r="AE10" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AF10" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AG10" s="4"/>
       <c r="AH10" s="4"/>
@@ -1699,55 +1699,55 @@
       <c r="AO10" s="6"/>
       <c r="AP10" s="6"/>
     </row>
-    <row r="11" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>66</v>
-      </c>
       <c r="F11" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
       <c r="P11" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q11" s="4">
         <v>30</v>
       </c>
       <c r="R11" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S11" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S11" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="T11" s="4">
         <v>1</v>
       </c>
       <c r="U11" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V11" s="4"/>
       <c r="W11" s="4"/>
@@ -1759,10 +1759,10 @@
       <c r="AC11" s="4"/>
       <c r="AD11" s="4"/>
       <c r="AE11" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AF11" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AG11" s="4"/>
       <c r="AH11" s="4"/>
@@ -1775,55 +1775,55 @@
       <c r="AO11" s="6"/>
       <c r="AP11" s="6"/>
     </row>
-    <row r="12" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E12" s="4" t="s">
+      <c r="F12" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>73</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N12" s="4"/>
       <c r="O12" s="4">
         <v>1300</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q12" s="4">
         <v>1</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T12" s="4">
         <v>1</v>
       </c>
       <c r="U12" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V12" s="4"/>
       <c r="W12" s="4"/>
@@ -1847,57 +1847,57 @@
       <c r="AO12" s="6"/>
       <c r="AP12" s="6"/>
     </row>
-    <row r="13" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>75</v>
-      </c>
       <c r="F13" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I13" s="4"/>
       <c r="J13" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N13" s="4"/>
       <c r="O13" s="4">
         <v>2.5</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q13" s="4">
         <v>30</v>
       </c>
       <c r="R13" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S13" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S13" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="T13" s="4">
         <v>1</v>
       </c>
       <c r="U13" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V13" s="4"/>
       <c r="W13" s="4"/>
@@ -1921,57 +1921,57 @@
       <c r="AO13" s="6"/>
       <c r="AP13" s="6"/>
     </row>
-    <row r="14" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>77</v>
-      </c>
       <c r="F14" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I14" s="4"/>
       <c r="J14" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N14" s="4"/>
       <c r="O14" s="4">
         <v>1.4</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q14" s="4">
         <v>1</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S14" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T14" s="4">
         <v>1</v>
       </c>
       <c r="U14" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V14" s="4"/>
       <c r="W14" s="4"/>
@@ -1995,55 +1995,55 @@
       <c r="AO14" s="6"/>
       <c r="AP14" s="6"/>
     </row>
-    <row r="15" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
       <c r="B15" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>77</v>
-      </c>
       <c r="F15" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N15" s="4"/>
       <c r="O15" s="4">
         <v>0.05</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q15" s="4">
         <v>1</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S15" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T15" s="4">
         <v>1</v>
       </c>
       <c r="U15" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V15" s="4"/>
       <c r="W15" s="4"/>
@@ -2067,55 +2067,55 @@
       <c r="AO15" s="6"/>
       <c r="AP15" s="6"/>
     </row>
-    <row r="16" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C16" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>77</v>
-      </c>
       <c r="F16" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
       <c r="J16" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N16" s="4"/>
       <c r="O16" s="4">
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q16" s="4">
         <v>30</v>
       </c>
       <c r="R16" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S16" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S16" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="T16" s="4">
         <v>1</v>
       </c>
       <c r="U16" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V16" s="4"/>
       <c r="W16" s="4"/>
@@ -2139,53 +2139,53 @@
       <c r="AO16" s="6"/>
       <c r="AP16" s="6"/>
     </row>
-    <row r="17" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
       <c r="B17" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
       <c r="J17" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N17" s="4"/>
       <c r="O17" s="4">
         <v>0.3</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q17" s="4">
         <v>30</v>
       </c>
       <c r="R17" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S17" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S17" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="T17" s="4">
         <v>1</v>
       </c>
       <c r="U17" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V17" s="4"/>
       <c r="W17" s="4"/>
@@ -2209,53 +2209,53 @@
       <c r="AO17" s="6"/>
       <c r="AP17" s="6"/>
     </row>
-    <row r="18" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
       <c r="B18" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
       <c r="J18" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N18" s="4"/>
       <c r="O18" s="4">
         <v>0.3</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q18" s="4">
         <v>30</v>
       </c>
       <c r="R18" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S18" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S18" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="T18" s="4">
         <v>1</v>
       </c>
       <c r="U18" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V18" s="4"/>
       <c r="W18" s="4"/>
@@ -2279,57 +2279,57 @@
       <c r="AO18" s="6"/>
       <c r="AP18" s="6"/>
     </row>
-    <row r="19" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
       <c r="B19" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I19" s="4"/>
       <c r="J19" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
       <c r="M19" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N19" s="4"/>
       <c r="O19" s="4">
         <v>16</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q19" s="4">
         <v>1</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S19" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T19" s="4">
         <v>1</v>
       </c>
       <c r="U19" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V19" s="4"/>
       <c r="W19" s="4"/>
@@ -2353,57 +2353,57 @@
       <c r="AO19" s="6"/>
       <c r="AP19" s="6"/>
     </row>
-    <row r="20" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
       <c r="M20" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N20" s="4"/>
       <c r="O20" s="4">
         <v>11</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q20" s="4">
         <v>30</v>
       </c>
       <c r="R20" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S20" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S20" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="T20" s="4">
         <v>1</v>
       </c>
       <c r="U20" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V20" s="4"/>
       <c r="W20" s="4"/>
@@ -2427,55 +2427,55 @@
       <c r="AO20" s="6"/>
       <c r="AP20" s="6"/>
     </row>
-    <row r="21" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
       <c r="B21" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>83</v>
-      </c>
       <c r="F21" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
       <c r="J21" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
       <c r="M21" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N21" s="4"/>
       <c r="O21" s="4">
         <v>610</v>
       </c>
       <c r="P21" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q21" s="4">
         <v>1</v>
       </c>
       <c r="R21" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S21" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T21" s="4">
         <v>1</v>
       </c>
       <c r="U21" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V21" s="4"/>
       <c r="W21" s="4"/>
@@ -2499,55 +2499,55 @@
       <c r="AO21" s="6"/>
       <c r="AP21" s="6"/>
     </row>
-    <row r="22" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C22" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>83</v>
-      </c>
       <c r="F22" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
       <c r="J22" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
       <c r="M22" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N22" s="4"/>
       <c r="O22" s="4">
         <v>4600</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q22" s="4">
         <v>30</v>
       </c>
       <c r="R22" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S22" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S22" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="T22" s="4">
         <v>1</v>
       </c>
       <c r="U22" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V22" s="4"/>
       <c r="W22" s="4"/>
@@ -2571,55 +2571,55 @@
       <c r="AO22" s="6"/>
       <c r="AP22" s="6"/>
     </row>
-    <row r="23" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C23" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>54</v>
-      </c>
       <c r="F23" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
       <c r="J23" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N23" s="4"/>
       <c r="O23" s="4">
         <v>170</v>
       </c>
       <c r="P23" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q23" s="4">
         <v>1</v>
       </c>
       <c r="R23" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S23" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T23" s="4">
         <v>1</v>
       </c>
       <c r="U23" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V23" s="4"/>
       <c r="W23" s="4"/>
@@ -2643,55 +2643,55 @@
       <c r="AO23" s="6"/>
       <c r="AP23" s="6"/>
     </row>
-    <row r="24" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
       <c r="B24" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C24" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D24" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>54</v>
-      </c>
       <c r="F24" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
       <c r="J24" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
       <c r="M24" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N24" s="4"/>
       <c r="O24" s="4">
         <v>4200</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q24" s="4">
         <v>30</v>
       </c>
       <c r="R24" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S24" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S24" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="T24" s="4">
         <v>1</v>
       </c>
       <c r="U24" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V24" s="4"/>
       <c r="W24" s="4"/>
@@ -2715,55 +2715,55 @@
       <c r="AO24" s="6"/>
       <c r="AP24" s="6"/>
     </row>
-    <row r="25" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
       <c r="B25" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C25" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>85</v>
-      </c>
       <c r="F25" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
       <c r="J25" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
       <c r="M25" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N25" s="4"/>
       <c r="O25" s="4">
         <v>0.24</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q25" s="4">
         <v>1</v>
       </c>
       <c r="R25" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S25" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T25" s="4">
         <v>1</v>
       </c>
       <c r="U25" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V25" s="4"/>
       <c r="W25" s="4"/>
@@ -2787,55 +2787,55 @@
       <c r="AO25" s="6"/>
       <c r="AP25" s="6"/>
     </row>
-    <row r="26" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
       <c r="B26" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C26" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D26" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>85</v>
-      </c>
       <c r="F26" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
       <c r="J26" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
       <c r="M26" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N26" s="4"/>
       <c r="O26" s="4">
         <v>0.47</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q26" s="4">
         <v>30</v>
       </c>
       <c r="R26" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S26" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S26" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="T26" s="4">
         <v>1</v>
       </c>
       <c r="U26" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V26" s="4"/>
       <c r="W26" s="4"/>
@@ -2859,55 +2859,55 @@
       <c r="AO26" s="6"/>
       <c r="AP26" s="6"/>
     </row>
-    <row r="27" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
       <c r="B27" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C27" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>87</v>
-      </c>
       <c r="F27" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
       <c r="J27" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
       <c r="M27" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N27" s="4"/>
       <c r="O27" s="4">
         <v>7400</v>
       </c>
       <c r="P27" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q27" s="4">
         <v>1</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S27" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T27" s="4">
         <v>1</v>
       </c>
       <c r="U27" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V27" s="4"/>
       <c r="W27" s="4"/>
@@ -2931,55 +2931,55 @@
       <c r="AO27" s="6"/>
       <c r="AP27" s="6"/>
     </row>
-    <row r="28" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="B28" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C28" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D28" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>87</v>
-      </c>
       <c r="F28" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
       <c r="J28" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
       <c r="M28" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N28" s="4"/>
       <c r="O28" s="4">
         <v>26000</v>
       </c>
       <c r="P28" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q28" s="4">
         <v>30</v>
       </c>
       <c r="R28" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S28" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S28" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="T28" s="4">
         <v>1</v>
       </c>
       <c r="U28" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V28" s="4"/>
       <c r="W28" s="4"/>
@@ -3003,55 +3003,55 @@
       <c r="AO28" s="6"/>
       <c r="AP28" s="6"/>
     </row>
-    <row r="29" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C29" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>89</v>
       </c>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I29" s="4"/>
       <c r="J29" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
       <c r="M29" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N29" s="4"/>
       <c r="O29" s="4">
         <v>22</v>
       </c>
       <c r="P29" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q29" s="4">
         <v>1</v>
       </c>
       <c r="R29" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S29" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T29" s="4">
         <v>1</v>
       </c>
       <c r="U29" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V29" s="4"/>
       <c r="W29" s="4"/>
@@ -3075,55 +3075,55 @@
       <c r="AO29" s="6"/>
       <c r="AP29" s="6"/>
     </row>
-    <row r="30" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
       <c r="B30" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C30" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>89</v>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I30" s="4"/>
       <c r="J30" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N30" s="4"/>
       <c r="O30" s="4">
         <v>5.2</v>
       </c>
       <c r="P30" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q30" s="4">
         <v>30</v>
       </c>
       <c r="R30" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S30" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S30" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="T30" s="4">
         <v>1</v>
       </c>
       <c r="U30" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V30" s="4"/>
       <c r="W30" s="4"/>
@@ -3147,53 +3147,53 @@
       <c r="AO30" s="6"/>
       <c r="AP30" s="6"/>
     </row>
-    <row r="31" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="4"/>
       <c r="B31" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C31" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E31" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>89</v>
       </c>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
       <c r="J31" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
       <c r="M31" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N31" s="4"/>
       <c r="O31" s="4">
         <v>4</v>
       </c>
       <c r="P31" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q31" s="4">
         <v>1</v>
       </c>
       <c r="R31" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S31" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T31" s="4">
         <v>1</v>
       </c>
       <c r="U31" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V31" s="4"/>
       <c r="W31" s="4"/>
@@ -3217,53 +3217,53 @@
       <c r="AO31" s="6"/>
       <c r="AP31" s="6"/>
     </row>
-    <row r="32" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
       <c r="B32" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C32" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>89</v>
       </c>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
       <c r="J32" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
       <c r="M32" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N32" s="4"/>
       <c r="O32" s="4">
         <v>400</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q32" s="4">
         <v>30</v>
       </c>
       <c r="R32" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S32" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S32" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="T32" s="4">
         <v>1</v>
       </c>
       <c r="U32" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V32" s="4"/>
       <c r="W32" s="4"/>
@@ -3287,53 +3287,53 @@
       <c r="AO32" s="6"/>
       <c r="AP32" s="6"/>
     </row>
-    <row r="33" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
       <c r="B33" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>91</v>
       </c>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
       <c r="J33" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
       <c r="M33" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N33" s="4"/>
       <c r="O33" s="4">
         <v>7000000</v>
       </c>
       <c r="P33" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q33" s="4">
         <v>1</v>
       </c>
       <c r="R33" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S33" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T33" s="4">
         <v>1</v>
       </c>
       <c r="U33" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V33" s="4"/>
       <c r="W33" s="4"/>
@@ -3357,55 +3357,55 @@
       <c r="AO33" s="6"/>
       <c r="AP33" s="6"/>
     </row>
-    <row r="34" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="4"/>
       <c r="B34" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C34" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E34" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D34" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>94</v>
-      </c>
       <c r="F34" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I34" s="4"/>
       <c r="J34" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
       <c r="M34" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N34" s="4"/>
       <c r="O34" s="4"/>
       <c r="P34" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q34" s="4">
         <v>1</v>
       </c>
       <c r="R34" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S34" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T34" s="4">
         <v>1</v>
       </c>
       <c r="U34" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V34" s="4"/>
       <c r="W34" s="4"/>
@@ -3417,10 +3417,10 @@
       <c r="AC34" s="4"/>
       <c r="AD34" s="4"/>
       <c r="AE34" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AF34" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AG34" s="4">
         <v>1.1366719999999999</v>
@@ -3443,55 +3443,55 @@
       <c r="AO34" s="6"/>
       <c r="AP34" s="6"/>
     </row>
-    <row r="35" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="4"/>
       <c r="B35" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C35" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E35" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D35" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>94</v>
-      </c>
       <c r="F35" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I35" s="4"/>
       <c r="J35" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
       <c r="M35" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N35" s="4"/>
       <c r="O35" s="4"/>
       <c r="P35" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q35" s="4">
         <v>30</v>
       </c>
       <c r="R35" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S35" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S35" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="T35" s="4">
         <v>1</v>
       </c>
       <c r="U35" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V35" s="4"/>
       <c r="W35" s="4"/>
@@ -3503,10 +3503,10 @@
       <c r="AC35" s="4"/>
       <c r="AD35" s="4"/>
       <c r="AE35" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AF35" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AG35" s="4">
         <v>1.101672</v>
@@ -3529,55 +3529,55 @@
       <c r="AO35" s="6"/>
       <c r="AP35" s="6"/>
     </row>
-    <row r="36" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
       <c r="B36" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G36" s="4"/>
       <c r="H36" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I36" s="4"/>
       <c r="J36" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
       <c r="M36" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N36" s="4"/>
       <c r="O36" s="4"/>
       <c r="P36" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q36" s="4">
         <v>1</v>
       </c>
       <c r="R36" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S36" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T36" s="4">
         <v>1</v>
       </c>
       <c r="U36" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V36" s="4"/>
       <c r="W36" s="4"/>
@@ -3589,10 +3589,10 @@
       <c r="AC36" s="4"/>
       <c r="AD36" s="4"/>
       <c r="AE36" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AF36" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AG36" s="4"/>
       <c r="AH36" s="4"/>
@@ -3611,55 +3611,55 @@
       <c r="AO36" s="6"/>
       <c r="AP36" s="6"/>
     </row>
-    <row r="37" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="4"/>
       <c r="B37" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I37" s="4"/>
       <c r="J37" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
       <c r="M37" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N37" s="4"/>
       <c r="O37" s="4"/>
       <c r="P37" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q37" s="4">
         <v>30</v>
       </c>
       <c r="R37" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S37" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S37" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="T37" s="4">
         <v>1</v>
       </c>
       <c r="U37" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V37" s="4"/>
       <c r="W37" s="4"/>
@@ -3671,10 +3671,10 @@
       <c r="AC37" s="4"/>
       <c r="AD37" s="4"/>
       <c r="AE37" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AF37" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG37" s="4"/>
       <c r="AH37" s="4"/>
@@ -3693,55 +3693,55 @@
       <c r="AO37" s="6"/>
       <c r="AP37" s="6"/>
     </row>
-    <row r="38" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
       <c r="B38" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C38" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E38" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D38" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>75</v>
-      </c>
       <c r="F38" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I38" s="4"/>
       <c r="J38" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
       <c r="M38" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N38" s="4"/>
       <c r="O38" s="4"/>
       <c r="P38" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q38" s="4">
         <v>1</v>
       </c>
       <c r="R38" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S38" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T38" s="4">
         <v>1</v>
       </c>
       <c r="U38" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V38" s="4"/>
       <c r="W38" s="4"/>
@@ -3753,10 +3753,10 @@
       <c r="AC38" s="4"/>
       <c r="AD38" s="4"/>
       <c r="AE38" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AF38" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AG38" s="4">
         <v>1.4620299999999999</v>
@@ -3779,55 +3779,55 @@
       <c r="AO38" s="6"/>
       <c r="AP38" s="6"/>
     </row>
-    <row r="39" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="4"/>
       <c r="B39" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C39" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E39" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D39" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>75</v>
-      </c>
       <c r="F39" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I39" s="4"/>
       <c r="J39" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
       <c r="M39" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N39" s="4"/>
       <c r="O39" s="4"/>
       <c r="P39" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q39" s="4">
         <v>30</v>
       </c>
       <c r="R39" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S39" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S39" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="T39" s="4">
         <v>1</v>
       </c>
       <c r="U39" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V39" s="4"/>
       <c r="W39" s="4"/>
@@ -3839,10 +3839,10 @@
       <c r="AC39" s="4"/>
       <c r="AD39" s="4"/>
       <c r="AE39" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AF39" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AG39" s="4">
         <v>1.4620299999999999</v>
@@ -3865,55 +3865,55 @@
       <c r="AO39" s="6"/>
       <c r="AP39" s="6"/>
     </row>
-    <row r="40" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
       <c r="B40" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C40" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E40" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D40" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>83</v>
-      </c>
       <c r="F40" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I40" s="4"/>
       <c r="J40" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
       <c r="M40" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N40" s="4"/>
       <c r="O40" s="4"/>
       <c r="P40" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q40" s="4">
         <v>1</v>
       </c>
       <c r="R40" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S40" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T40" s="4">
         <v>1</v>
       </c>
       <c r="U40" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V40" s="4"/>
       <c r="W40" s="4"/>
@@ -3925,10 +3925,10 @@
       <c r="AC40" s="4"/>
       <c r="AD40" s="4"/>
       <c r="AE40" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AF40" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AG40" s="4"/>
       <c r="AH40" s="4"/>
@@ -3947,55 +3947,55 @@
       <c r="AO40" s="6"/>
       <c r="AP40" s="6"/>
     </row>
-    <row r="41" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
       <c r="B41" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C41" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E41" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D41" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>83</v>
-      </c>
       <c r="F41" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I41" s="4"/>
       <c r="J41" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
       <c r="M41" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N41" s="4"/>
       <c r="O41" s="4"/>
       <c r="P41" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q41" s="4">
         <v>30</v>
       </c>
       <c r="R41" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S41" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S41" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="T41" s="4">
         <v>1</v>
       </c>
       <c r="U41" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V41" s="4"/>
       <c r="W41" s="4"/>
@@ -4007,10 +4007,10 @@
       <c r="AC41" s="4"/>
       <c r="AD41" s="4"/>
       <c r="AE41" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AF41" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG41" s="4"/>
       <c r="AH41" s="4"/>
@@ -4029,55 +4029,55 @@
       <c r="AO41" s="6"/>
       <c r="AP41" s="6"/>
     </row>
-    <row r="42" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
       <c r="B42" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C42" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E42" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D42" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>98</v>
-      </c>
       <c r="F42" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I42" s="4"/>
       <c r="J42" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
       <c r="M42" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N42" s="4"/>
       <c r="O42" s="4"/>
       <c r="P42" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q42" s="4">
         <v>1</v>
       </c>
       <c r="R42" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S42" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T42" s="4">
         <v>1</v>
       </c>
       <c r="U42" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V42" s="4"/>
       <c r="W42" s="4"/>
@@ -4089,10 +4089,10 @@
       <c r="AC42" s="4"/>
       <c r="AD42" s="4"/>
       <c r="AE42" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AF42" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AG42" s="4"/>
       <c r="AH42" s="4"/>
@@ -4111,55 +4111,55 @@
       <c r="AO42" s="6"/>
       <c r="AP42" s="6"/>
     </row>
-    <row r="43" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="4"/>
       <c r="B43" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C43" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E43" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D43" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>87</v>
-      </c>
       <c r="F43" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I43" s="4"/>
       <c r="J43" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
       <c r="M43" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N43" s="4"/>
       <c r="O43" s="4"/>
       <c r="P43" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q43" s="4">
         <v>1</v>
       </c>
       <c r="R43" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S43" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T43" s="4">
         <v>1</v>
       </c>
       <c r="U43" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V43" s="4"/>
       <c r="W43" s="4"/>
@@ -4171,10 +4171,10 @@
       <c r="AC43" s="4"/>
       <c r="AD43" s="4"/>
       <c r="AE43" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AF43" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AG43" s="4"/>
       <c r="AH43" s="4"/>
@@ -4193,55 +4193,55 @@
       <c r="AO43" s="6"/>
       <c r="AP43" s="6"/>
     </row>
-    <row r="44" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="4"/>
       <c r="B44" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C44" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E44" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D44" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>87</v>
-      </c>
       <c r="F44" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I44" s="4"/>
       <c r="J44" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
       <c r="M44" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N44" s="4"/>
       <c r="O44" s="4"/>
       <c r="P44" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q44" s="4">
         <v>30</v>
       </c>
       <c r="R44" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S44" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S44" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="T44" s="4">
         <v>1</v>
       </c>
       <c r="U44" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V44" s="4"/>
       <c r="W44" s="4"/>
@@ -4253,10 +4253,10 @@
       <c r="AC44" s="4"/>
       <c r="AD44" s="4"/>
       <c r="AE44" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AF44" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AG44" s="4"/>
       <c r="AH44" s="4"/>
@@ -4275,53 +4275,53 @@
       <c r="AO44" s="6"/>
       <c r="AP44" s="6"/>
     </row>
-    <row r="45" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="4"/>
       <c r="B45" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C45" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E45" s="4" t="s">
         <v>99</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>100</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
       <c r="J45" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
       <c r="M45" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N45" s="4"/>
       <c r="O45" s="4">
         <v>1000</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q45" s="4">
         <v>1</v>
       </c>
       <c r="R45" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S45" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T45" s="4">
         <v>1</v>
       </c>
       <c r="U45" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V45" s="4"/>
       <c r="W45" s="4"/>
@@ -4345,55 +4345,55 @@
       <c r="AO45" s="6"/>
       <c r="AP45" s="6"/>
     </row>
-    <row r="46" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
       <c r="B46" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C46" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E46" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>102</v>
       </c>
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I46" s="4"/>
       <c r="J46" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
       <c r="M46" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N46" s="4"/>
       <c r="O46" s="4">
         <v>860000</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q46" s="4">
         <v>1</v>
       </c>
       <c r="R46" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S46" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T46" s="4">
         <v>1</v>
       </c>
       <c r="U46" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V46" s="4"/>
       <c r="W46" s="4"/>
@@ -4417,55 +4417,55 @@
       <c r="AO46" s="6"/>
       <c r="AP46" s="6"/>
     </row>
-    <row r="47" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="4"/>
       <c r="B47" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C47" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E47" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>102</v>
       </c>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I47" s="4"/>
       <c r="J47" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
       <c r="M47" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N47" s="4"/>
       <c r="O47" s="4">
         <v>230000</v>
       </c>
       <c r="P47" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q47" s="4">
         <v>30</v>
       </c>
       <c r="R47" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S47" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S47" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="T47" s="4">
         <v>1</v>
       </c>
       <c r="U47" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V47" s="4"/>
       <c r="W47" s="4"/>
@@ -4489,57 +4489,57 @@
       <c r="AO47" s="6"/>
       <c r="AP47" s="6"/>
     </row>
-    <row r="48" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
       <c r="B48" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C48" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E48" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D48" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>104</v>
-      </c>
       <c r="F48" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I48" s="4"/>
       <c r="J48" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
       <c r="M48" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N48" s="4"/>
       <c r="O48" s="4">
         <v>19</v>
       </c>
       <c r="P48" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q48" s="4">
         <v>1</v>
       </c>
       <c r="R48" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S48" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T48" s="4">
         <v>1</v>
       </c>
       <c r="U48" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V48" s="4"/>
       <c r="W48" s="4"/>
@@ -4563,57 +4563,57 @@
       <c r="AO48" s="6"/>
       <c r="AP48" s="6"/>
     </row>
-    <row r="49" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="4"/>
       <c r="B49" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C49" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E49" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D49" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>104</v>
-      </c>
       <c r="F49" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I49" s="4"/>
       <c r="J49" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
       <c r="M49" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N49" s="4"/>
       <c r="O49" s="4">
         <v>11</v>
       </c>
       <c r="P49" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q49" s="4">
         <v>30</v>
       </c>
       <c r="R49" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S49" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S49" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="T49" s="4">
         <v>1</v>
       </c>
       <c r="U49" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V49" s="4"/>
       <c r="W49" s="4"/>
@@ -4637,55 +4637,55 @@
       <c r="AO49" s="6"/>
       <c r="AP49" s="6"/>
     </row>
-    <row r="50" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="4"/>
       <c r="B50" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C50" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E50" s="4" t="s">
         <v>105</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>106</v>
       </c>
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
       <c r="H50" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I50" s="4"/>
       <c r="J50" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
       <c r="M50" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N50" s="4"/>
       <c r="O50" s="4">
         <v>1000</v>
       </c>
       <c r="P50" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q50" s="4">
         <v>30</v>
       </c>
       <c r="R50" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S50" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S50" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="T50" s="4">
         <v>1</v>
       </c>
       <c r="U50" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V50" s="4"/>
       <c r="W50" s="4"/>
@@ -4709,53 +4709,53 @@
       <c r="AO50" s="6"/>
       <c r="AP50" s="6"/>
     </row>
-    <row r="51" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="4"/>
       <c r="B51" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
       <c r="J51" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
       <c r="M51" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N51" s="4"/>
       <c r="O51" s="4">
         <v>10000</v>
       </c>
       <c r="P51" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q51" s="4">
         <v>1</v>
       </c>
       <c r="R51" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S51" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T51" s="4">
         <v>1</v>
       </c>
       <c r="U51" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V51" s="4"/>
       <c r="W51" s="4"/>
@@ -4779,33 +4779,33 @@
       <c r="AO51" s="6"/>
       <c r="AP51" s="6"/>
     </row>
-    <row r="52" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="4"/>
       <c r="B52" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C52" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E52" s="4" t="s">
         <v>108</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>109</v>
       </c>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I52" s="4"/>
       <c r="J52" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
       <c r="M52" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N52" s="4">
         <v>6.5</v>
@@ -4814,22 +4814,22 @@
         <v>9</v>
       </c>
       <c r="P52" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q52" s="4">
         <v>7</v>
       </c>
       <c r="R52" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S52" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="T52" s="4">
         <v>1</v>
       </c>
       <c r="U52" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V52" s="4"/>
       <c r="W52" s="4"/>
@@ -4853,31 +4853,31 @@
       <c r="AO52" s="6"/>
       <c r="AP52" s="6"/>
     </row>
-    <row r="53" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="4"/>
       <c r="B53" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C53" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E53" s="4" t="s">
         <v>108</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>109</v>
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
       <c r="J53" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
       <c r="M53" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N53" s="4">
         <v>5</v>
@@ -4886,22 +4886,22 @@
         <v>9</v>
       </c>
       <c r="P53" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q53" s="4">
+        <v>1</v>
+      </c>
+      <c r="R53" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S53" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="Q53" s="4">
-        <v>1</v>
-      </c>
-      <c r="R53" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="S53" s="4" t="s">
-        <v>111</v>
-      </c>
       <c r="T53" s="4">
         <v>1</v>
       </c>
       <c r="U53" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V53" s="4"/>
       <c r="W53" s="4"/>
@@ -4925,55 +4925,55 @@
       <c r="AO53" s="6"/>
       <c r="AP53" s="6"/>
     </row>
-    <row r="54" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="4"/>
       <c r="B54" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
       <c r="J54" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>
       <c r="M54" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N54" s="4"/>
       <c r="O54" s="4">
         <v>250000</v>
       </c>
       <c r="P54" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q54" s="4">
         <v>1</v>
       </c>
       <c r="R54" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S54" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T54" s="4">
         <v>1</v>
       </c>
       <c r="U54" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V54" s="4"/>
       <c r="W54" s="4"/>
@@ -4997,53 +4997,53 @@
       <c r="AO54" s="6"/>
       <c r="AP54" s="6"/>
     </row>
-    <row r="55" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="4"/>
       <c r="B55" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
       <c r="J55" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K55" s="4"/>
       <c r="L55" s="4"/>
       <c r="M55" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N55" s="4"/>
       <c r="O55" s="4">
         <v>126</v>
       </c>
       <c r="P55" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q55" s="4">
         <v>90</v>
       </c>
       <c r="R55" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S55" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="T55" s="4">
         <v>1</v>
       </c>
       <c r="U55" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V55" s="4"/>
       <c r="W55" s="4"/>
@@ -5067,53 +5067,53 @@
       <c r="AO55" s="6"/>
       <c r="AP55" s="6"/>
     </row>
-    <row r="56" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="4"/>
       <c r="B56" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
       <c r="J56" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K56" s="4"/>
       <c r="L56" s="4"/>
       <c r="M56" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N56" s="4"/>
       <c r="O56" s="4">
         <v>410</v>
       </c>
       <c r="P56" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q56" s="4">
         <v>90</v>
       </c>
       <c r="R56" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S56" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="S56" s="4" t="s">
-        <v>51</v>
       </c>
       <c r="T56" s="4">
         <v>10</v>
       </c>
       <c r="U56" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="V56" s="4"/>
       <c r="W56" s="4"/>
@@ -5137,53 +5137,53 @@
       <c r="AO56" s="6"/>
       <c r="AP56" s="6"/>
     </row>
-    <row r="57" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="4"/>
       <c r="B57" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
       <c r="J57" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K57" s="4"/>
       <c r="L57" s="4"/>
       <c r="M57" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N57" s="4"/>
       <c r="O57" s="4">
         <v>8</v>
       </c>
       <c r="P57" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q57" s="4">
         <v>1</v>
       </c>
       <c r="R57" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S57" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T57" s="4">
         <v>1</v>
       </c>
       <c r="U57" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="V57" s="4"/>
       <c r="W57" s="4"/>
@@ -5207,53 +5207,53 @@
       <c r="AO57" s="6"/>
       <c r="AP57" s="6"/>
     </row>
-    <row r="58" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="4"/>
       <c r="B58" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
       <c r="J58" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K58" s="4"/>
       <c r="L58" s="4"/>
       <c r="M58" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N58" s="4"/>
       <c r="O58" s="4">
         <v>15</v>
       </c>
       <c r="P58" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q58" s="4">
         <v>1</v>
       </c>
       <c r="R58" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S58" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T58" s="4">
         <v>1</v>
       </c>
       <c r="U58" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="V58" s="4"/>
       <c r="W58" s="4"/>
@@ -5277,57 +5277,57 @@
       <c r="AO58" s="6"/>
       <c r="AP58" s="6"/>
     </row>
-    <row r="59" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="4"/>
       <c r="B59" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E59" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F59" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>119</v>
       </c>
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
       <c r="J59" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K59" s="4"/>
       <c r="L59" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M59" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N59" s="4">
         <v>9.5</v>
       </c>
       <c r="O59" s="4"/>
       <c r="P59" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q59" s="4">
         <v>7</v>
       </c>
       <c r="R59" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S59" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S59" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="T59" s="4">
         <v>1</v>
       </c>
       <c r="U59" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V59" s="4"/>
       <c r="W59" s="4"/>
@@ -5351,57 +5351,57 @@
       <c r="AO59" s="6"/>
       <c r="AP59" s="6"/>
     </row>
-    <row r="60" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="4"/>
       <c r="B60" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E60" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F60" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>119</v>
       </c>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
       <c r="J60" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K60" s="4"/>
       <c r="L60" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M60" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N60" s="4">
         <v>6.5</v>
       </c>
       <c r="O60" s="4"/>
       <c r="P60" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q60" s="4">
         <v>30</v>
       </c>
       <c r="R60" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S60" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S60" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="T60" s="4">
         <v>1</v>
       </c>
       <c r="U60" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V60" s="4"/>
       <c r="W60" s="4"/>
@@ -5425,57 +5425,57 @@
       <c r="AO60" s="6"/>
       <c r="AP60" s="6"/>
     </row>
-    <row r="61" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="4"/>
       <c r="B61" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E61" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F61" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>119</v>
       </c>
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
       <c r="J61" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K61" s="4"/>
       <c r="L61" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M61" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N61" s="4">
         <v>5</v>
       </c>
       <c r="O61" s="4"/>
       <c r="P61" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q61" s="4">
         <v>7</v>
       </c>
       <c r="R61" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S61" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="T61" s="4">
         <v>1</v>
       </c>
       <c r="U61" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V61" s="4"/>
       <c r="W61" s="4"/>
@@ -5499,57 +5499,57 @@
       <c r="AO61" s="6"/>
       <c r="AP61" s="6"/>
     </row>
-    <row r="62" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="4"/>
       <c r="B62" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E62" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F62" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>119</v>
       </c>
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
       <c r="J62" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K62" s="4"/>
       <c r="L62" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M62" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N62" s="4">
         <v>8</v>
       </c>
       <c r="O62" s="4"/>
       <c r="P62" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q62" s="4">
         <v>1</v>
       </c>
       <c r="R62" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S62" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="T62" s="4">
         <v>1</v>
       </c>
       <c r="U62" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V62" s="4"/>
       <c r="W62" s="4"/>
@@ -5573,57 +5573,57 @@
       <c r="AO62" s="6"/>
       <c r="AP62" s="6"/>
     </row>
-    <row r="63" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="4"/>
       <c r="B63" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E63" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F63" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>119</v>
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
       <c r="J63" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K63" s="4"/>
       <c r="L63" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N63" s="4">
         <v>4</v>
       </c>
       <c r="O63" s="4"/>
       <c r="P63" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q63" s="4">
         <v>1</v>
       </c>
       <c r="R63" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S63" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="T63" s="4">
         <v>1</v>
       </c>
       <c r="U63" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V63" s="4"/>
       <c r="W63" s="4"/>
@@ -5647,57 +5647,57 @@
       <c r="AO63" s="6"/>
       <c r="AP63" s="6"/>
     </row>
-    <row r="64" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="4"/>
       <c r="B64" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C64" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E64" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D64" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E64" s="4" t="s">
-        <v>126</v>
-      </c>
       <c r="F64" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G64" s="4"/>
       <c r="H64" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I64" s="4"/>
       <c r="J64" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K64" s="4"/>
       <c r="L64" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="M64" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N64" s="4"/>
       <c r="O64" s="4"/>
       <c r="P64" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q64" s="4">
         <v>1</v>
       </c>
       <c r="R64" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S64" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T64" s="4">
         <v>1</v>
       </c>
       <c r="U64" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V64" s="4"/>
       <c r="W64" s="4"/>
@@ -5709,10 +5709,10 @@
       <c r="AC64" s="4"/>
       <c r="AD64" s="4"/>
       <c r="AE64" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AF64" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG64" s="4"/>
       <c r="AH64" s="4"/>
@@ -5725,55 +5725,55 @@
       <c r="AO64" s="6"/>
       <c r="AP64" s="6"/>
     </row>
-    <row r="65" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="4"/>
       <c r="B65" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C65" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E65" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D65" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E65" s="4" t="s">
-        <v>126</v>
-      </c>
       <c r="F65" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G65" s="4"/>
       <c r="H65" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I65" s="4"/>
       <c r="J65" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K65" s="4"/>
       <c r="L65" s="6"/>
       <c r="M65" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N65" s="4"/>
       <c r="O65" s="4"/>
       <c r="P65" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q65" s="4">
         <v>30</v>
       </c>
       <c r="R65" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S65" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S65" s="4" t="s">
+      <c r="T65" s="4">
+        <v>1</v>
+      </c>
+      <c r="U65" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="T65" s="4">
-        <v>1</v>
-      </c>
-      <c r="U65" s="4" t="s">
-        <v>52</v>
       </c>
       <c r="V65" s="4"/>
       <c r="W65" s="4"/>
@@ -5785,10 +5785,10 @@
       <c r="AC65" s="4"/>
       <c r="AD65" s="4"/>
       <c r="AE65" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="AF65" s="4" t="s">
         <v>127</v>
-      </c>
-      <c r="AF65" s="4" t="s">
-        <v>128</v>
       </c>
       <c r="AG65" s="4"/>
       <c r="AH65" s="4"/>

--- a/inst/extdata/blackfeet_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/blackfeet_tribe_criteria_crosswalk.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/hannah_ferriby_tetratech_com/Documents/Documents/GitHub/TADACommunityHub/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2059C3BF-FEA9-4515-96A4-28B4B0F0BCB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="13_ncr:1_{2059C3BF-FEA9-4515-96A4-28B4B0F0BCB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{130860C9-82A3-4FB5-A050-0286E6625664}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{9CAA114B-CC1B-4AA7-94E1-A6CD4C5CB112}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9CAA114B-CC1B-4AA7-94E1-A6CD4C5CB112}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AP$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AQ$65</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="161">
   <si>
     <t>TADA.ComparableDataIdentifier</t>
   </si>
@@ -146,12 +146,6 @@
     <t>hardness_param_4</t>
   </si>
   <si>
-    <t>hardness_param_5</t>
-  </si>
-  <si>
-    <t>hardness_param_6</t>
-  </si>
-  <si>
     <t>pH_param_1</t>
   </si>
   <si>
@@ -245,12 +239,6 @@
     <t>arithmetic max</t>
   </si>
   <si>
-    <t>EPA Aluminum calculator</t>
-  </si>
-  <si>
-    <t>Additional Information</t>
-  </si>
-  <si>
     <t>Copper</t>
   </si>
   <si>
@@ -497,7 +485,43 @@
     <t>CFU/100ML</t>
   </si>
   <si>
-    <t>EquationFormula</t>
+    <t>Equation</t>
+  </si>
+  <si>
+    <t>pHThreshold</t>
+  </si>
+  <si>
+    <t>pHDirection</t>
+  </si>
+  <si>
+    <t>TemperatureExtreme</t>
+  </si>
+  <si>
+    <t>pH_param_5</t>
+  </si>
+  <si>
+    <t>pH_param_6</t>
+  </si>
+  <si>
+    <t>pH_param_7</t>
+  </si>
+  <si>
+    <t>pH_param_8</t>
+  </si>
+  <si>
+    <t>pH_param_9</t>
+  </si>
+  <si>
+    <t>MinEqMagnitude</t>
+  </si>
+  <si>
+    <t>MaxEqMagnitude</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Max</t>
   </si>
 </sst>
 </file>
@@ -576,7 +600,32 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF0E442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFCD758F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -906,7 +955,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{057945F5-944B-4C7F-AE65-F75344336C85}">
-  <dimension ref="A1:AP65"/>
+  <dimension ref="A1:AY65"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="3"/>
@@ -914,12 +963,19 @@
     <col min="4" max="4" width="31.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="18" width="9.140625" style="3"/>
     <col min="19" max="19" width="19.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="20" max="31" width="9.140625" style="3"/>
-    <col min="32" max="32" width="12.42578125" style="3" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="3"/>
+    <col min="20" max="30" width="9.140625" style="3"/>
+    <col min="31" max="31" width="20.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="149.7109375" style="3" customWidth="1"/>
+    <col min="33" max="33" width="12.42578125" style="3" customWidth="1"/>
+    <col min="34" max="34" width="15" style="3" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="22" style="3" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="13.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="24.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="15.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:51" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1014,88 +1070,113 @@
         <v>30</v>
       </c>
       <c r="AF1" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AR1" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="AG1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AJ1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AS1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="AY1" s="4"/>
+    </row>
+    <row r="2" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N2" s="4"/>
       <c r="O2" s="4">
         <v>20000</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q2" s="4">
         <v>4</v>
       </c>
       <c r="R2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="T2" s="4">
+        <v>1</v>
+      </c>
+      <c r="U2" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="T2" s="4">
-        <v>1</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>51</v>
       </c>
       <c r="V2" s="4"/>
       <c r="W2" s="4"/>
@@ -1114,62 +1195,63 @@
       <c r="AJ2" s="4"/>
       <c r="AK2" s="4"/>
       <c r="AL2" s="4"/>
-      <c r="AM2" s="6"/>
+      <c r="AM2" s="4"/>
       <c r="AN2" s="6"/>
       <c r="AO2" s="6"/>
       <c r="AP2" s="6"/>
-    </row>
-    <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ2" s="6"/>
+    </row>
+    <row r="3" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="E3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>54</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K3" s="4"/>
       <c r="L3" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N3" s="4"/>
       <c r="O3" s="4">
         <v>1.5</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q3" s="4">
         <v>30</v>
       </c>
       <c r="R3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="T3" s="4">
+        <v>1</v>
+      </c>
+      <c r="U3" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="T3" s="4">
-        <v>1</v>
-      </c>
-      <c r="U3" s="4" t="s">
-        <v>51</v>
       </c>
       <c r="V3" s="4"/>
       <c r="W3" s="4"/>
@@ -1188,62 +1270,63 @@
       <c r="AJ3" s="4"/>
       <c r="AK3" s="4"/>
       <c r="AL3" s="4"/>
-      <c r="AM3" s="6"/>
+      <c r="AM3" s="4"/>
       <c r="AN3" s="6"/>
       <c r="AO3" s="6"/>
       <c r="AP3" s="6"/>
-    </row>
-    <row r="4" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ3" s="6"/>
+    </row>
+    <row r="4" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="E4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>54</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K4" s="4"/>
       <c r="L4" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N4" s="4"/>
       <c r="O4" s="4">
         <v>3.1</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q4" s="4">
         <v>30</v>
       </c>
       <c r="R4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="T4" s="4">
+        <v>1</v>
+      </c>
+      <c r="U4" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="S4" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="T4" s="4">
-        <v>1</v>
-      </c>
-      <c r="U4" s="4" t="s">
-        <v>51</v>
       </c>
       <c r="V4" s="4"/>
       <c r="W4" s="4"/>
@@ -1262,58 +1345,59 @@
       <c r="AJ4" s="4"/>
       <c r="AK4" s="4"/>
       <c r="AL4" s="4"/>
-      <c r="AM4" s="6"/>
+      <c r="AM4" s="4"/>
       <c r="AN4" s="6"/>
       <c r="AO4" s="6"/>
       <c r="AP4" s="6"/>
-    </row>
-    <row r="5" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ4" s="6"/>
+    </row>
+    <row r="5" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E5" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N5" s="4"/>
       <c r="O5" s="4">
         <v>5.6</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q5" s="4">
         <v>30</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T5" s="4">
         <v>1</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V5" s="4"/>
       <c r="W5" s="4"/>
@@ -1332,58 +1416,59 @@
       <c r="AJ5" s="4"/>
       <c r="AK5" s="4"/>
       <c r="AL5" s="4"/>
-      <c r="AM5" s="6"/>
+      <c r="AM5" s="4"/>
       <c r="AN5" s="6"/>
       <c r="AO5" s="6"/>
       <c r="AP5" s="6"/>
-    </row>
-    <row r="6" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ5" s="6"/>
+    </row>
+    <row r="6" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N6" s="4"/>
       <c r="O6" s="4">
         <v>5.6</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q6" s="4">
         <v>30</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T6" s="4">
         <v>1</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V6" s="4"/>
       <c r="W6" s="4"/>
@@ -1402,62 +1487,63 @@
       <c r="AJ6" s="4"/>
       <c r="AK6" s="4"/>
       <c r="AL6" s="4"/>
-      <c r="AM6" s="6"/>
+      <c r="AM6" s="4"/>
       <c r="AN6" s="6"/>
       <c r="AO6" s="6"/>
       <c r="AP6" s="6"/>
-    </row>
-    <row r="7" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ6" s="6"/>
+    </row>
+    <row r="7" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E7" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N7" s="4"/>
       <c r="O7" s="4">
         <v>340</v>
       </c>
       <c r="P7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>1</v>
+      </c>
+      <c r="R7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="S7" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="Q7" s="4">
-        <v>1</v>
-      </c>
-      <c r="R7" s="4" t="s">
+      <c r="T7" s="4">
+        <v>1</v>
+      </c>
+      <c r="U7" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="S7" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="T7" s="4">
-        <v>1</v>
-      </c>
-      <c r="U7" s="4" t="s">
-        <v>51</v>
       </c>
       <c r="V7" s="4"/>
       <c r="W7" s="4"/>
@@ -1476,60 +1562,61 @@
       <c r="AJ7" s="4"/>
       <c r="AK7" s="4"/>
       <c r="AL7" s="4"/>
-      <c r="AM7" s="6"/>
+      <c r="AM7" s="4"/>
       <c r="AN7" s="6"/>
       <c r="AO7" s="6"/>
       <c r="AP7" s="6"/>
-    </row>
-    <row r="8" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ7" s="6"/>
+    </row>
+    <row r="8" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E8" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N8" s="4"/>
       <c r="O8" s="4">
         <v>150</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q8" s="4">
         <v>4</v>
       </c>
       <c r="R8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="S8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="T8" s="4">
+        <v>1</v>
+      </c>
+      <c r="U8" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="S8" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="T8" s="4">
-        <v>1</v>
-      </c>
-      <c r="U8" s="4" t="s">
-        <v>51</v>
       </c>
       <c r="V8" s="4"/>
       <c r="W8" s="4"/>
@@ -1548,58 +1635,59 @@
       <c r="AJ8" s="4"/>
       <c r="AK8" s="4"/>
       <c r="AL8" s="4"/>
-      <c r="AM8" s="6"/>
+      <c r="AM8" s="4"/>
       <c r="AN8" s="6"/>
       <c r="AO8" s="6"/>
       <c r="AP8" s="6"/>
-    </row>
-    <row r="9" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ8" s="6"/>
+    </row>
+    <row r="9" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>62</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N9" s="4"/>
       <c r="O9" s="4">
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q9" s="4">
         <v>30</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T9" s="4">
         <v>1</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V9" s="4"/>
       <c r="W9" s="4"/>
@@ -1618,60 +1706,61 @@
       <c r="AJ9" s="4"/>
       <c r="AK9" s="4"/>
       <c r="AL9" s="4"/>
-      <c r="AM9" s="6"/>
+      <c r="AM9" s="4"/>
       <c r="AN9" s="6"/>
       <c r="AO9" s="6"/>
       <c r="AP9" s="6"/>
-    </row>
-    <row r="10" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ9" s="6"/>
+    </row>
+    <row r="10" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E10" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
       <c r="P10" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q10" s="4">
         <v>1</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T10" s="4">
         <v>1</v>
       </c>
       <c r="U10" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V10" s="4"/>
       <c r="W10" s="4"/>
@@ -1682,72 +1771,69 @@
       <c r="AB10" s="4"/>
       <c r="AC10" s="4"/>
       <c r="AD10" s="4"/>
-      <c r="AE10" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="AF10" s="4" t="s">
-        <v>68</v>
-      </c>
+      <c r="AE10" s="4"/>
+      <c r="AF10" s="4"/>
       <c r="AG10" s="4"/>
       <c r="AH10" s="4"/>
       <c r="AI10" s="4"/>
       <c r="AJ10" s="4"/>
       <c r="AK10" s="4"/>
       <c r="AL10" s="4"/>
-      <c r="AM10" s="6"/>
+      <c r="AM10" s="4"/>
       <c r="AN10" s="6"/>
       <c r="AO10" s="6"/>
       <c r="AP10" s="6"/>
-    </row>
-    <row r="11" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ10" s="6"/>
+    </row>
+    <row r="11" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E11" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
       <c r="P11" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q11" s="4">
         <v>30</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T11" s="4">
         <v>1</v>
       </c>
       <c r="U11" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V11" s="4"/>
       <c r="W11" s="4"/>
@@ -1758,72 +1844,69 @@
       <c r="AB11" s="4"/>
       <c r="AC11" s="4"/>
       <c r="AD11" s="4"/>
-      <c r="AE11" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="AF11" s="4" t="s">
-        <v>68</v>
-      </c>
+      <c r="AE11" s="4"/>
+      <c r="AF11" s="4"/>
       <c r="AG11" s="4"/>
       <c r="AH11" s="4"/>
       <c r="AI11" s="4"/>
       <c r="AJ11" s="4"/>
       <c r="AK11" s="4"/>
       <c r="AL11" s="4"/>
-      <c r="AM11" s="6"/>
+      <c r="AM11" s="4"/>
       <c r="AN11" s="6"/>
       <c r="AO11" s="6"/>
       <c r="AP11" s="6"/>
-    </row>
-    <row r="12" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ11" s="6"/>
+    </row>
+    <row r="12" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N12" s="4"/>
       <c r="O12" s="4">
         <v>1300</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q12" s="4">
         <v>1</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T12" s="4">
         <v>1</v>
       </c>
       <c r="U12" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V12" s="4"/>
       <c r="W12" s="4"/>
@@ -1842,62 +1925,63 @@
       <c r="AJ12" s="4"/>
       <c r="AK12" s="4"/>
       <c r="AL12" s="4"/>
-      <c r="AM12" s="6"/>
+      <c r="AM12" s="4"/>
       <c r="AN12" s="6"/>
       <c r="AO12" s="6"/>
       <c r="AP12" s="6"/>
-    </row>
-    <row r="13" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ12" s="6"/>
+    </row>
+    <row r="13" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E13" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I13" s="4"/>
       <c r="J13" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N13" s="4"/>
       <c r="O13" s="4">
         <v>2.5</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q13" s="4">
         <v>30</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T13" s="4">
         <v>1</v>
       </c>
       <c r="U13" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V13" s="4"/>
       <c r="W13" s="4"/>
@@ -1916,62 +2000,63 @@
       <c r="AJ13" s="4"/>
       <c r="AK13" s="4"/>
       <c r="AL13" s="4"/>
-      <c r="AM13" s="6"/>
+      <c r="AM13" s="4"/>
       <c r="AN13" s="6"/>
       <c r="AO13" s="6"/>
       <c r="AP13" s="6"/>
-    </row>
-    <row r="14" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ13" s="6"/>
+    </row>
+    <row r="14" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E14" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I14" s="4"/>
       <c r="J14" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N14" s="4"/>
       <c r="O14" s="4">
         <v>1.4</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q14" s="4">
         <v>1</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S14" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T14" s="4">
         <v>1</v>
       </c>
       <c r="U14" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V14" s="4"/>
       <c r="W14" s="4"/>
@@ -1990,60 +2075,61 @@
       <c r="AJ14" s="4"/>
       <c r="AK14" s="4"/>
       <c r="AL14" s="4"/>
-      <c r="AM14" s="6"/>
+      <c r="AM14" s="4"/>
       <c r="AN14" s="6"/>
       <c r="AO14" s="6"/>
       <c r="AP14" s="6"/>
-    </row>
-    <row r="15" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ14" s="6"/>
+    </row>
+    <row r="15" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
       <c r="B15" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N15" s="4"/>
       <c r="O15" s="4">
         <v>0.05</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q15" s="4">
         <v>1</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S15" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T15" s="4">
         <v>1</v>
       </c>
       <c r="U15" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V15" s="4"/>
       <c r="W15" s="4"/>
@@ -2062,60 +2148,61 @@
       <c r="AJ15" s="4"/>
       <c r="AK15" s="4"/>
       <c r="AL15" s="4"/>
-      <c r="AM15" s="6"/>
+      <c r="AM15" s="4"/>
       <c r="AN15" s="6"/>
       <c r="AO15" s="6"/>
       <c r="AP15" s="6"/>
-    </row>
-    <row r="16" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ15" s="6"/>
+    </row>
+    <row r="16" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E16" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
       <c r="J16" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N16" s="4"/>
       <c r="O16" s="4">
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q16" s="4">
         <v>30</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T16" s="4">
         <v>1</v>
       </c>
       <c r="U16" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V16" s="4"/>
       <c r="W16" s="4"/>
@@ -2134,58 +2221,59 @@
       <c r="AJ16" s="4"/>
       <c r="AK16" s="4"/>
       <c r="AL16" s="4"/>
-      <c r="AM16" s="6"/>
+      <c r="AM16" s="4"/>
       <c r="AN16" s="6"/>
       <c r="AO16" s="6"/>
       <c r="AP16" s="6"/>
-    </row>
-    <row r="17" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ16" s="6"/>
+    </row>
+    <row r="17" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
       <c r="B17" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E17" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
       <c r="J17" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N17" s="4"/>
       <c r="O17" s="4">
         <v>0.3</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="Q17" s="4">
         <v>30</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S17" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T17" s="4">
         <v>1</v>
       </c>
       <c r="U17" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V17" s="4"/>
       <c r="W17" s="4"/>
@@ -2204,58 +2292,59 @@
       <c r="AJ17" s="4"/>
       <c r="AK17" s="4"/>
       <c r="AL17" s="4"/>
-      <c r="AM17" s="6"/>
+      <c r="AM17" s="4"/>
       <c r="AN17" s="6"/>
       <c r="AO17" s="6"/>
       <c r="AP17" s="6"/>
-    </row>
-    <row r="18" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ17" s="6"/>
+    </row>
+    <row r="18" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
       <c r="B18" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E18" s="4" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
       <c r="J18" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N18" s="4"/>
       <c r="O18" s="4">
         <v>0.3</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="Q18" s="4">
         <v>30</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T18" s="4">
         <v>1</v>
       </c>
       <c r="U18" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V18" s="4"/>
       <c r="W18" s="4"/>
@@ -2274,62 +2363,63 @@
       <c r="AJ18" s="4"/>
       <c r="AK18" s="4"/>
       <c r="AL18" s="4"/>
-      <c r="AM18" s="6"/>
+      <c r="AM18" s="4"/>
       <c r="AN18" s="6"/>
       <c r="AO18" s="6"/>
       <c r="AP18" s="6"/>
-    </row>
-    <row r="19" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ18" s="6"/>
+    </row>
+    <row r="19" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
       <c r="B19" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E19" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I19" s="4"/>
       <c r="J19" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
       <c r="M19" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N19" s="4"/>
       <c r="O19" s="4">
         <v>16</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q19" s="4">
         <v>1</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S19" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T19" s="4">
         <v>1</v>
       </c>
       <c r="U19" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V19" s="4"/>
       <c r="W19" s="4"/>
@@ -2348,62 +2438,63 @@
       <c r="AJ19" s="4"/>
       <c r="AK19" s="4"/>
       <c r="AL19" s="4"/>
-      <c r="AM19" s="6"/>
+      <c r="AM19" s="4"/>
       <c r="AN19" s="6"/>
       <c r="AO19" s="6"/>
       <c r="AP19" s="6"/>
-    </row>
-    <row r="20" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ19" s="6"/>
+    </row>
+    <row r="20" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E20" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
       <c r="M20" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N20" s="4"/>
       <c r="O20" s="4">
         <v>11</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q20" s="4">
         <v>30</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T20" s="4">
         <v>1</v>
       </c>
       <c r="U20" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V20" s="4"/>
       <c r="W20" s="4"/>
@@ -2422,60 +2513,61 @@
       <c r="AJ20" s="4"/>
       <c r="AK20" s="4"/>
       <c r="AL20" s="4"/>
-      <c r="AM20" s="6"/>
+      <c r="AM20" s="4"/>
       <c r="AN20" s="6"/>
       <c r="AO20" s="6"/>
       <c r="AP20" s="6"/>
-    </row>
-    <row r="21" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ20" s="6"/>
+    </row>
+    <row r="21" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
       <c r="B21" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
       <c r="J21" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
       <c r="M21" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N21" s="4"/>
       <c r="O21" s="4">
         <v>610</v>
       </c>
       <c r="P21" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q21" s="4">
         <v>1</v>
       </c>
       <c r="R21" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S21" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T21" s="4">
         <v>1</v>
       </c>
       <c r="U21" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V21" s="4"/>
       <c r="W21" s="4"/>
@@ -2494,60 +2586,61 @@
       <c r="AJ21" s="4"/>
       <c r="AK21" s="4"/>
       <c r="AL21" s="4"/>
-      <c r="AM21" s="6"/>
+      <c r="AM21" s="4"/>
       <c r="AN21" s="6"/>
       <c r="AO21" s="6"/>
       <c r="AP21" s="6"/>
-    </row>
-    <row r="22" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ21" s="6"/>
+    </row>
+    <row r="22" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E22" s="4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
       <c r="J22" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
       <c r="M22" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N22" s="4"/>
       <c r="O22" s="4">
         <v>4600</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q22" s="4">
         <v>30</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S22" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T22" s="4">
         <v>1</v>
       </c>
       <c r="U22" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V22" s="4"/>
       <c r="W22" s="4"/>
@@ -2566,60 +2659,61 @@
       <c r="AJ22" s="4"/>
       <c r="AK22" s="4"/>
       <c r="AL22" s="4"/>
-      <c r="AM22" s="6"/>
+      <c r="AM22" s="4"/>
       <c r="AN22" s="6"/>
       <c r="AO22" s="6"/>
       <c r="AP22" s="6"/>
-    </row>
-    <row r="23" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ22" s="6"/>
+    </row>
+    <row r="23" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
       <c r="J23" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N23" s="4"/>
       <c r="O23" s="4">
         <v>170</v>
       </c>
       <c r="P23" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q23" s="4">
         <v>1</v>
       </c>
       <c r="R23" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S23" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T23" s="4">
         <v>1</v>
       </c>
       <c r="U23" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V23" s="4"/>
       <c r="W23" s="4"/>
@@ -2638,60 +2732,61 @@
       <c r="AJ23" s="4"/>
       <c r="AK23" s="4"/>
       <c r="AL23" s="4"/>
-      <c r="AM23" s="6"/>
+      <c r="AM23" s="4"/>
       <c r="AN23" s="6"/>
       <c r="AO23" s="6"/>
       <c r="AP23" s="6"/>
-    </row>
-    <row r="24" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ23" s="6"/>
+    </row>
+    <row r="24" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
       <c r="B24" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E24" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
       <c r="J24" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
       <c r="M24" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N24" s="4"/>
       <c r="O24" s="4">
         <v>4200</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q24" s="4">
         <v>30</v>
       </c>
       <c r="R24" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S24" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T24" s="4">
         <v>1</v>
       </c>
       <c r="U24" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V24" s="4"/>
       <c r="W24" s="4"/>
@@ -2710,60 +2805,61 @@
       <c r="AJ24" s="4"/>
       <c r="AK24" s="4"/>
       <c r="AL24" s="4"/>
-      <c r="AM24" s="6"/>
+      <c r="AM24" s="4"/>
       <c r="AN24" s="6"/>
       <c r="AO24" s="6"/>
       <c r="AP24" s="6"/>
-    </row>
-    <row r="25" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ24" s="6"/>
+    </row>
+    <row r="25" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
       <c r="B25" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
       <c r="J25" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
       <c r="M25" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N25" s="4"/>
       <c r="O25" s="4">
         <v>0.24</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q25" s="4">
         <v>1</v>
       </c>
       <c r="R25" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S25" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T25" s="4">
         <v>1</v>
       </c>
       <c r="U25" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V25" s="4"/>
       <c r="W25" s="4"/>
@@ -2782,60 +2878,61 @@
       <c r="AJ25" s="4"/>
       <c r="AK25" s="4"/>
       <c r="AL25" s="4"/>
-      <c r="AM25" s="6"/>
+      <c r="AM25" s="4"/>
       <c r="AN25" s="6"/>
       <c r="AO25" s="6"/>
       <c r="AP25" s="6"/>
-    </row>
-    <row r="26" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ25" s="6"/>
+    </row>
+    <row r="26" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
       <c r="B26" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E26" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
       <c r="J26" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
       <c r="M26" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N26" s="4"/>
       <c r="O26" s="4">
         <v>0.47</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q26" s="4">
         <v>30</v>
       </c>
       <c r="R26" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S26" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T26" s="4">
         <v>1</v>
       </c>
       <c r="U26" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V26" s="4"/>
       <c r="W26" s="4"/>
@@ -2854,60 +2951,61 @@
       <c r="AJ26" s="4"/>
       <c r="AK26" s="4"/>
       <c r="AL26" s="4"/>
-      <c r="AM26" s="6"/>
+      <c r="AM26" s="4"/>
       <c r="AN26" s="6"/>
       <c r="AO26" s="6"/>
       <c r="AP26" s="6"/>
-    </row>
-    <row r="27" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ26" s="6"/>
+    </row>
+    <row r="27" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
       <c r="B27" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
       <c r="J27" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
       <c r="M27" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N27" s="4"/>
       <c r="O27" s="4">
         <v>7400</v>
       </c>
       <c r="P27" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q27" s="4">
         <v>1</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S27" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T27" s="4">
         <v>1</v>
       </c>
       <c r="U27" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V27" s="4"/>
       <c r="W27" s="4"/>
@@ -2926,60 +3024,61 @@
       <c r="AJ27" s="4"/>
       <c r="AK27" s="4"/>
       <c r="AL27" s="4"/>
-      <c r="AM27" s="6"/>
+      <c r="AM27" s="4"/>
       <c r="AN27" s="6"/>
       <c r="AO27" s="6"/>
       <c r="AP27" s="6"/>
-    </row>
-    <row r="28" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ27" s="6"/>
+    </row>
+    <row r="28" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="B28" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E28" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
       <c r="J28" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
       <c r="M28" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N28" s="4"/>
       <c r="O28" s="4">
         <v>26000</v>
       </c>
       <c r="P28" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q28" s="4">
         <v>30</v>
       </c>
       <c r="R28" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S28" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T28" s="4">
         <v>1</v>
       </c>
       <c r="U28" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V28" s="4"/>
       <c r="W28" s="4"/>
@@ -2998,60 +3097,61 @@
       <c r="AJ28" s="4"/>
       <c r="AK28" s="4"/>
       <c r="AL28" s="4"/>
-      <c r="AM28" s="6"/>
+      <c r="AM28" s="4"/>
       <c r="AN28" s="6"/>
       <c r="AO28" s="6"/>
       <c r="AP28" s="6"/>
-    </row>
-    <row r="29" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ28" s="6"/>
+    </row>
+    <row r="29" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E29" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I29" s="4"/>
       <c r="J29" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
       <c r="M29" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N29" s="4"/>
       <c r="O29" s="4">
         <v>22</v>
       </c>
       <c r="P29" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q29" s="4">
         <v>1</v>
       </c>
       <c r="R29" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S29" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T29" s="4">
         <v>1</v>
       </c>
       <c r="U29" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V29" s="4"/>
       <c r="W29" s="4"/>
@@ -3070,60 +3170,61 @@
       <c r="AJ29" s="4"/>
       <c r="AK29" s="4"/>
       <c r="AL29" s="4"/>
-      <c r="AM29" s="6"/>
+      <c r="AM29" s="4"/>
       <c r="AN29" s="6"/>
       <c r="AO29" s="6"/>
       <c r="AP29" s="6"/>
-    </row>
-    <row r="30" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ29" s="6"/>
+    </row>
+    <row r="30" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
       <c r="B30" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E30" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I30" s="4"/>
       <c r="J30" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N30" s="4"/>
       <c r="O30" s="4">
         <v>5.2</v>
       </c>
       <c r="P30" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q30" s="4">
         <v>30</v>
       </c>
       <c r="R30" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S30" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T30" s="4">
         <v>1</v>
       </c>
       <c r="U30" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V30" s="4"/>
       <c r="W30" s="4"/>
@@ -3142,58 +3243,59 @@
       <c r="AJ30" s="4"/>
       <c r="AK30" s="4"/>
       <c r="AL30" s="4"/>
-      <c r="AM30" s="6"/>
+      <c r="AM30" s="4"/>
       <c r="AN30" s="6"/>
       <c r="AO30" s="6"/>
       <c r="AP30" s="6"/>
-    </row>
-    <row r="31" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ30" s="6"/>
+    </row>
+    <row r="31" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="4"/>
       <c r="B31" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
       <c r="J31" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
       <c r="M31" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N31" s="4"/>
       <c r="O31" s="4">
         <v>4</v>
       </c>
       <c r="P31" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q31" s="4">
         <v>1</v>
       </c>
       <c r="R31" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S31" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T31" s="4">
         <v>1</v>
       </c>
       <c r="U31" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V31" s="4"/>
       <c r="W31" s="4"/>
@@ -3212,58 +3314,59 @@
       <c r="AJ31" s="4"/>
       <c r="AK31" s="4"/>
       <c r="AL31" s="4"/>
-      <c r="AM31" s="6"/>
+      <c r="AM31" s="4"/>
       <c r="AN31" s="6"/>
       <c r="AO31" s="6"/>
       <c r="AP31" s="6"/>
-    </row>
-    <row r="32" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ31" s="6"/>
+    </row>
+    <row r="32" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
       <c r="B32" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C32" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E32" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
       <c r="J32" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
       <c r="M32" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N32" s="4"/>
       <c r="O32" s="4">
         <v>400</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q32" s="4">
         <v>30</v>
       </c>
       <c r="R32" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S32" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T32" s="4">
         <v>1</v>
       </c>
       <c r="U32" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V32" s="4"/>
       <c r="W32" s="4"/>
@@ -3282,58 +3385,59 @@
       <c r="AJ32" s="4"/>
       <c r="AK32" s="4"/>
       <c r="AL32" s="4"/>
-      <c r="AM32" s="6"/>
+      <c r="AM32" s="4"/>
       <c r="AN32" s="6"/>
       <c r="AO32" s="6"/>
       <c r="AP32" s="6"/>
-    </row>
-    <row r="33" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ32" s="6"/>
+    </row>
+    <row r="33" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
       <c r="B33" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
       <c r="J33" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
       <c r="M33" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N33" s="4"/>
       <c r="O33" s="4">
         <v>7000000</v>
       </c>
       <c r="P33" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="Q33" s="4">
         <v>1</v>
       </c>
       <c r="R33" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S33" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T33" s="4">
         <v>1</v>
       </c>
       <c r="U33" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V33" s="4"/>
       <c r="W33" s="4"/>
@@ -3352,60 +3456,61 @@
       <c r="AJ33" s="4"/>
       <c r="AK33" s="4"/>
       <c r="AL33" s="4"/>
-      <c r="AM33" s="6"/>
+      <c r="AM33" s="4"/>
       <c r="AN33" s="6"/>
       <c r="AO33" s="6"/>
       <c r="AP33" s="6"/>
-    </row>
-    <row r="34" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ33" s="6"/>
+    </row>
+    <row r="34" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="4"/>
       <c r="B34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C34" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E34" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I34" s="4"/>
       <c r="J34" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
       <c r="M34" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N34" s="4"/>
       <c r="O34" s="4"/>
       <c r="P34" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q34" s="4">
         <v>1</v>
       </c>
       <c r="R34" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S34" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T34" s="4">
         <v>1</v>
       </c>
       <c r="U34" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V34" s="4"/>
       <c r="W34" s="4"/>
@@ -3417,81 +3522,79 @@
       <c r="AC34" s="4"/>
       <c r="AD34" s="4"/>
       <c r="AE34" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="AF34" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="AG34" s="4">
+        <v>136</v>
+      </c>
+      <c r="AG34" s="4"/>
+      <c r="AH34" s="4"/>
+      <c r="AI34" s="4">
         <v>1.1366719999999999</v>
       </c>
-      <c r="AH34" s="4">
+      <c r="AJ34" s="4">
         <v>4.1838E-2</v>
       </c>
-      <c r="AI34" s="4">
-        <v>1</v>
-      </c>
-      <c r="AJ34" s="4">
+      <c r="AK34" s="4">
         <v>0.97889999999999999</v>
       </c>
-      <c r="AK34" s="4">
+      <c r="AL34" s="4">
         <v>-3.8660000000000001</v>
       </c>
-      <c r="AL34" s="4"/>
-      <c r="AM34" s="6"/>
       <c r="AN34" s="6"/>
       <c r="AO34" s="6"/>
       <c r="AP34" s="6"/>
-    </row>
-    <row r="35" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ34" s="6"/>
+    </row>
+    <row r="35" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="4"/>
       <c r="B35" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D35" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C35" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E35" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I35" s="4"/>
       <c r="J35" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
       <c r="M35" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N35" s="4"/>
       <c r="O35" s="4"/>
       <c r="P35" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q35" s="4">
         <v>30</v>
       </c>
       <c r="R35" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S35" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T35" s="4">
         <v>1</v>
       </c>
       <c r="U35" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V35" s="4"/>
       <c r="W35" s="4"/>
@@ -3503,81 +3606,79 @@
       <c r="AC35" s="4"/>
       <c r="AD35" s="4"/>
       <c r="AE35" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="AF35" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="AG35" s="4">
+        <v>137</v>
+      </c>
+      <c r="AG35" s="4"/>
+      <c r="AH35" s="4"/>
+      <c r="AI35" s="4">
         <v>1.101672</v>
       </c>
-      <c r="AH35" s="4">
+      <c r="AJ35" s="4">
         <v>4.1838E-2</v>
       </c>
-      <c r="AI35" s="4">
-        <v>1</v>
-      </c>
-      <c r="AJ35" s="4">
+      <c r="AK35" s="4">
         <v>0.7409</v>
       </c>
-      <c r="AK35" s="4">
+      <c r="AL35" s="4">
         <v>-4.7190000000000003</v>
       </c>
-      <c r="AL35" s="4"/>
-      <c r="AM35" s="6"/>
       <c r="AN35" s="6"/>
       <c r="AO35" s="6"/>
       <c r="AP35" s="6"/>
-    </row>
-    <row r="36" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ35" s="6"/>
+    </row>
+    <row r="36" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
       <c r="B36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C36" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E36" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G36" s="4"/>
       <c r="H36" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I36" s="4"/>
       <c r="J36" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
       <c r="M36" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N36" s="4"/>
       <c r="O36" s="4"/>
       <c r="P36" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q36" s="4">
         <v>1</v>
       </c>
       <c r="R36" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S36" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T36" s="4">
         <v>1</v>
       </c>
       <c r="U36" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V36" s="4"/>
       <c r="W36" s="4"/>
@@ -3589,77 +3690,77 @@
       <c r="AC36" s="4"/>
       <c r="AD36" s="4"/>
       <c r="AE36" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="AF36" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG36" s="4"/>
       <c r="AH36" s="4"/>
-      <c r="AI36" s="4">
+      <c r="AI36" s="4"/>
+      <c r="AJ36" s="4">
         <v>0.316</v>
       </c>
-      <c r="AJ36" s="4">
+      <c r="AK36" s="4">
         <v>0.81899999999999995</v>
       </c>
-      <c r="AK36" s="4">
+      <c r="AL36" s="4">
         <v>3.7256</v>
       </c>
-      <c r="AL36" s="4"/>
-      <c r="AM36" s="6"/>
       <c r="AN36" s="6"/>
       <c r="AO36" s="6"/>
       <c r="AP36" s="6"/>
-    </row>
-    <row r="37" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ36" s="6"/>
+    </row>
+    <row r="37" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="4"/>
       <c r="B37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C37" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E37" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I37" s="4"/>
       <c r="J37" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
       <c r="M37" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N37" s="4"/>
       <c r="O37" s="4"/>
       <c r="P37" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q37" s="4">
         <v>30</v>
       </c>
       <c r="R37" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S37" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T37" s="4">
         <v>1</v>
       </c>
       <c r="U37" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V37" s="4"/>
       <c r="W37" s="4"/>
@@ -3671,77 +3772,77 @@
       <c r="AC37" s="4"/>
       <c r="AD37" s="4"/>
       <c r="AE37" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="AF37" s="4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="AG37" s="4"/>
       <c r="AH37" s="4"/>
-      <c r="AI37" s="4">
+      <c r="AI37" s="4"/>
+      <c r="AJ37" s="4">
         <v>0.86</v>
       </c>
-      <c r="AJ37" s="4">
+      <c r="AK37" s="4">
         <v>0.81899999999999995</v>
       </c>
-      <c r="AK37" s="4">
+      <c r="AL37" s="4">
         <v>0.68479999999999996</v>
       </c>
-      <c r="AL37" s="4"/>
-      <c r="AM37" s="6"/>
       <c r="AN37" s="6"/>
       <c r="AO37" s="6"/>
       <c r="AP37" s="6"/>
-    </row>
-    <row r="38" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ37" s="6"/>
+    </row>
+    <row r="38" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
       <c r="B38" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C38" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E38" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I38" s="4"/>
       <c r="J38" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
       <c r="M38" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N38" s="4"/>
       <c r="O38" s="4"/>
       <c r="P38" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q38" s="4">
         <v>1</v>
       </c>
       <c r="R38" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S38" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T38" s="4">
         <v>1</v>
       </c>
       <c r="U38" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V38" s="4"/>
       <c r="W38" s="4"/>
@@ -3753,81 +3854,79 @@
       <c r="AC38" s="4"/>
       <c r="AD38" s="4"/>
       <c r="AE38" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="AF38" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="AG38" s="4">
+        <v>140</v>
+      </c>
+      <c r="AG38" s="4"/>
+      <c r="AH38" s="4"/>
+      <c r="AI38" s="4">
         <v>1.4620299999999999</v>
       </c>
-      <c r="AH38" s="4">
+      <c r="AJ38" s="4">
         <v>0.14571200000000001</v>
       </c>
-      <c r="AI38" s="4">
-        <v>1</v>
-      </c>
-      <c r="AJ38" s="4">
+      <c r="AK38" s="4">
         <v>1.2729999999999999</v>
       </c>
-      <c r="AK38" s="4">
+      <c r="AL38" s="4">
         <v>-1.46</v>
       </c>
-      <c r="AL38" s="4"/>
-      <c r="AM38" s="6"/>
       <c r="AN38" s="6"/>
       <c r="AO38" s="6"/>
       <c r="AP38" s="6"/>
-    </row>
-    <row r="39" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ38" s="6"/>
+    </row>
+    <row r="39" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="4"/>
       <c r="B39" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D39" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C39" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E39" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I39" s="4"/>
       <c r="J39" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
       <c r="M39" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N39" s="4"/>
       <c r="O39" s="4"/>
       <c r="P39" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q39" s="4">
         <v>30</v>
       </c>
       <c r="R39" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S39" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T39" s="4">
         <v>1</v>
       </c>
       <c r="U39" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V39" s="4"/>
       <c r="W39" s="4"/>
@@ -3839,81 +3938,79 @@
       <c r="AC39" s="4"/>
       <c r="AD39" s="4"/>
       <c r="AE39" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="AF39" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="AG39" s="4">
+        <v>141</v>
+      </c>
+      <c r="AG39" s="4"/>
+      <c r="AH39" s="4"/>
+      <c r="AI39" s="4">
         <v>1.4620299999999999</v>
       </c>
-      <c r="AH39" s="4">
+      <c r="AJ39" s="4">
         <v>0.14571200000000001</v>
       </c>
-      <c r="AI39" s="4">
-        <v>1</v>
-      </c>
-      <c r="AJ39" s="4">
+      <c r="AK39" s="4">
         <v>1.2729999999999999</v>
       </c>
-      <c r="AK39" s="4">
+      <c r="AL39" s="4">
         <v>-4.7050000000000001</v>
       </c>
-      <c r="AL39" s="4"/>
-      <c r="AM39" s="6"/>
       <c r="AN39" s="6"/>
       <c r="AO39" s="6"/>
       <c r="AP39" s="6"/>
-    </row>
-    <row r="40" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ39" s="6"/>
+    </row>
+    <row r="40" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
       <c r="B40" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D40" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C40" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E40" s="4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I40" s="4"/>
       <c r="J40" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
       <c r="M40" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N40" s="4"/>
       <c r="O40" s="4"/>
       <c r="P40" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q40" s="4">
         <v>1</v>
       </c>
       <c r="R40" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S40" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T40" s="4">
         <v>1</v>
       </c>
       <c r="U40" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V40" s="4"/>
       <c r="W40" s="4"/>
@@ -3925,77 +4022,77 @@
       <c r="AC40" s="4"/>
       <c r="AD40" s="4"/>
       <c r="AE40" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="AF40" s="4" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AG40" s="4"/>
       <c r="AH40" s="4"/>
-      <c r="AI40" s="4">
+      <c r="AI40" s="4"/>
+      <c r="AJ40" s="4">
         <v>0.998</v>
       </c>
-      <c r="AJ40" s="4">
+      <c r="AK40" s="4">
         <v>0.84599999999999997</v>
       </c>
-      <c r="AK40" s="4">
+      <c r="AL40" s="4">
         <v>2.2549999999999999</v>
       </c>
-      <c r="AL40" s="4"/>
-      <c r="AM40" s="6"/>
       <c r="AN40" s="6"/>
       <c r="AO40" s="6"/>
       <c r="AP40" s="6"/>
-    </row>
-    <row r="41" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ40" s="6"/>
+    </row>
+    <row r="41" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
       <c r="B41" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D41" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C41" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E41" s="4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I41" s="4"/>
       <c r="J41" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
       <c r="M41" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N41" s="4"/>
       <c r="O41" s="4"/>
       <c r="P41" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q41" s="4">
         <v>30</v>
       </c>
       <c r="R41" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S41" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T41" s="4">
         <v>1</v>
       </c>
       <c r="U41" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V41" s="4"/>
       <c r="W41" s="4"/>
@@ -4007,77 +4104,77 @@
       <c r="AC41" s="4"/>
       <c r="AD41" s="4"/>
       <c r="AE41" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="AF41" s="4" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="AG41" s="4"/>
       <c r="AH41" s="4"/>
-      <c r="AI41" s="4">
+      <c r="AI41" s="4"/>
+      <c r="AJ41" s="4">
         <v>0.997</v>
       </c>
-      <c r="AJ41" s="4">
+      <c r="AK41" s="4">
         <v>0.84599999999999997</v>
       </c>
-      <c r="AK41" s="4">
+      <c r="AL41" s="4">
         <v>5.8400000000000001E-2</v>
       </c>
-      <c r="AL41" s="4"/>
-      <c r="AM41" s="6"/>
       <c r="AN41" s="6"/>
       <c r="AO41" s="6"/>
       <c r="AP41" s="6"/>
-    </row>
-    <row r="42" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ41" s="6"/>
+    </row>
+    <row r="42" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
       <c r="B42" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E42" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I42" s="4"/>
       <c r="J42" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
       <c r="M42" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N42" s="4"/>
       <c r="O42" s="4"/>
       <c r="P42" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q42" s="4">
         <v>1</v>
       </c>
       <c r="R42" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S42" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T42" s="4">
         <v>1</v>
       </c>
       <c r="U42" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V42" s="4"/>
       <c r="W42" s="4"/>
@@ -4089,77 +4186,77 @@
       <c r="AC42" s="4"/>
       <c r="AD42" s="4"/>
       <c r="AE42" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="AF42" s="4" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="AG42" s="4"/>
       <c r="AH42" s="4"/>
-      <c r="AI42" s="4">
+      <c r="AI42" s="4"/>
+      <c r="AJ42" s="4">
         <v>0.85</v>
       </c>
-      <c r="AJ42" s="4">
+      <c r="AK42" s="4">
         <v>1.72</v>
       </c>
-      <c r="AK42" s="4">
+      <c r="AL42" s="4">
         <v>-6.59</v>
       </c>
-      <c r="AL42" s="4"/>
-      <c r="AM42" s="6"/>
       <c r="AN42" s="6"/>
       <c r="AO42" s="6"/>
       <c r="AP42" s="6"/>
-    </row>
-    <row r="43" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ42" s="6"/>
+    </row>
+    <row r="43" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="4"/>
       <c r="B43" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C43" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E43" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I43" s="4"/>
       <c r="J43" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
       <c r="M43" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N43" s="4"/>
       <c r="O43" s="4"/>
       <c r="P43" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q43" s="4">
         <v>1</v>
       </c>
       <c r="R43" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S43" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T43" s="4">
         <v>1</v>
       </c>
       <c r="U43" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V43" s="4"/>
       <c r="W43" s="4"/>
@@ -4171,77 +4268,77 @@
       <c r="AC43" s="4"/>
       <c r="AD43" s="4"/>
       <c r="AE43" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="AF43" s="4" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="AG43" s="4"/>
       <c r="AH43" s="4"/>
-      <c r="AI43" s="4">
+      <c r="AI43" s="4"/>
+      <c r="AJ43" s="4">
         <v>0.97799999999999998</v>
       </c>
-      <c r="AJ43" s="4">
+      <c r="AK43" s="4">
         <v>0.84730000000000005</v>
       </c>
-      <c r="AK43" s="4">
+      <c r="AL43" s="4">
         <v>0.88400000000000001</v>
       </c>
-      <c r="AL43" s="4"/>
-      <c r="AM43" s="6"/>
       <c r="AN43" s="6"/>
       <c r="AO43" s="6"/>
       <c r="AP43" s="6"/>
-    </row>
-    <row r="44" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ43" s="6"/>
+    </row>
+    <row r="44" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="4"/>
       <c r="B44" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C44" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E44" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I44" s="4"/>
       <c r="J44" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
       <c r="M44" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N44" s="4"/>
       <c r="O44" s="4"/>
       <c r="P44" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q44" s="4">
         <v>30</v>
       </c>
       <c r="R44" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S44" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T44" s="4">
         <v>1</v>
       </c>
       <c r="U44" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V44" s="4"/>
       <c r="W44" s="4"/>
@@ -4253,75 +4350,75 @@
       <c r="AC44" s="4"/>
       <c r="AD44" s="4"/>
       <c r="AE44" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="AF44" s="4" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="AG44" s="4"/>
       <c r="AH44" s="4"/>
-      <c r="AI44" s="4">
+      <c r="AI44" s="4"/>
+      <c r="AJ44" s="4">
         <v>0.98599999999999999</v>
       </c>
-      <c r="AJ44" s="4">
+      <c r="AK44" s="4">
         <v>0.84730000000000005</v>
       </c>
-      <c r="AK44" s="4">
+      <c r="AL44" s="4">
         <v>0.88400000000000001</v>
       </c>
-      <c r="AL44" s="4"/>
-      <c r="AM44" s="6"/>
       <c r="AN44" s="6"/>
       <c r="AO44" s="6"/>
       <c r="AP44" s="6"/>
-    </row>
-    <row r="45" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ44" s="6"/>
+    </row>
+    <row r="45" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="4"/>
       <c r="B45" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
       <c r="J45" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
       <c r="M45" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N45" s="4"/>
       <c r="O45" s="4">
         <v>1000</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q45" s="4">
         <v>1</v>
       </c>
       <c r="R45" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S45" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T45" s="4">
         <v>1</v>
       </c>
       <c r="U45" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V45" s="4"/>
       <c r="W45" s="4"/>
@@ -4340,60 +4437,61 @@
       <c r="AJ45" s="4"/>
       <c r="AK45" s="4"/>
       <c r="AL45" s="4"/>
-      <c r="AM45" s="6"/>
+      <c r="AM45" s="4"/>
       <c r="AN45" s="6"/>
       <c r="AO45" s="6"/>
       <c r="AP45" s="6"/>
-    </row>
-    <row r="46" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ45" s="6"/>
+    </row>
+    <row r="46" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
       <c r="B46" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D46" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C46" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E46" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I46" s="4"/>
       <c r="J46" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
       <c r="M46" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N46" s="4"/>
       <c r="O46" s="4">
         <v>860000</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q46" s="4">
         <v>1</v>
       </c>
       <c r="R46" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S46" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T46" s="4">
         <v>1</v>
       </c>
       <c r="U46" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V46" s="4"/>
       <c r="W46" s="4"/>
@@ -4412,60 +4510,61 @@
       <c r="AJ46" s="4"/>
       <c r="AK46" s="4"/>
       <c r="AL46" s="4"/>
-      <c r="AM46" s="6"/>
+      <c r="AM46" s="4"/>
       <c r="AN46" s="6"/>
       <c r="AO46" s="6"/>
       <c r="AP46" s="6"/>
-    </row>
-    <row r="47" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ46" s="6"/>
+    </row>
+    <row r="47" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="4"/>
       <c r="B47" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D47" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E47" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I47" s="4"/>
       <c r="J47" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
       <c r="M47" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N47" s="4"/>
       <c r="O47" s="4">
         <v>230000</v>
       </c>
       <c r="P47" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q47" s="4">
         <v>30</v>
       </c>
       <c r="R47" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S47" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T47" s="4">
         <v>1</v>
       </c>
       <c r="U47" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V47" s="4"/>
       <c r="W47" s="4"/>
@@ -4484,62 +4583,63 @@
       <c r="AJ47" s="4"/>
       <c r="AK47" s="4"/>
       <c r="AL47" s="4"/>
-      <c r="AM47" s="6"/>
+      <c r="AM47" s="4"/>
       <c r="AN47" s="6"/>
       <c r="AO47" s="6"/>
       <c r="AP47" s="6"/>
-    </row>
-    <row r="48" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ47" s="6"/>
+    </row>
+    <row r="48" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
       <c r="B48" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D48" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C48" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E48" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I48" s="4"/>
       <c r="J48" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
       <c r="M48" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N48" s="4"/>
       <c r="O48" s="4">
         <v>19</v>
       </c>
       <c r="P48" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q48" s="4">
         <v>1</v>
       </c>
       <c r="R48" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S48" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T48" s="4">
         <v>1</v>
       </c>
       <c r="U48" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V48" s="4"/>
       <c r="W48" s="4"/>
@@ -4558,62 +4658,63 @@
       <c r="AJ48" s="4"/>
       <c r="AK48" s="4"/>
       <c r="AL48" s="4"/>
-      <c r="AM48" s="6"/>
+      <c r="AM48" s="4"/>
       <c r="AN48" s="6"/>
       <c r="AO48" s="6"/>
       <c r="AP48" s="6"/>
-    </row>
-    <row r="49" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ48" s="6"/>
+    </row>
+    <row r="49" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="4"/>
       <c r="B49" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D49" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E49" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I49" s="4"/>
       <c r="J49" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
       <c r="M49" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N49" s="4"/>
       <c r="O49" s="4">
         <v>11</v>
       </c>
       <c r="P49" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q49" s="4">
         <v>30</v>
       </c>
       <c r="R49" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S49" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T49" s="4">
         <v>1</v>
       </c>
       <c r="U49" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V49" s="4"/>
       <c r="W49" s="4"/>
@@ -4632,60 +4733,61 @@
       <c r="AJ49" s="4"/>
       <c r="AK49" s="4"/>
       <c r="AL49" s="4"/>
-      <c r="AM49" s="6"/>
+      <c r="AM49" s="4"/>
       <c r="AN49" s="6"/>
       <c r="AO49" s="6"/>
       <c r="AP49" s="6"/>
-    </row>
-    <row r="50" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ49" s="6"/>
+    </row>
+    <row r="50" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="4"/>
       <c r="B50" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D50" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C50" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E50" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
       <c r="H50" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I50" s="4"/>
       <c r="J50" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
       <c r="M50" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N50" s="4"/>
       <c r="O50" s="4">
         <v>1000</v>
       </c>
       <c r="P50" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q50" s="4">
         <v>30</v>
       </c>
       <c r="R50" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S50" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T50" s="4">
         <v>1</v>
       </c>
       <c r="U50" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V50" s="4"/>
       <c r="W50" s="4"/>
@@ -4704,58 +4806,59 @@
       <c r="AJ50" s="4"/>
       <c r="AK50" s="4"/>
       <c r="AL50" s="4"/>
-      <c r="AM50" s="6"/>
+      <c r="AM50" s="4"/>
       <c r="AN50" s="6"/>
       <c r="AO50" s="6"/>
       <c r="AP50" s="6"/>
-    </row>
-    <row r="51" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ50" s="6"/>
+    </row>
+    <row r="51" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="4"/>
       <c r="B51" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
       <c r="J51" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
       <c r="M51" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N51" s="4"/>
       <c r="O51" s="4">
         <v>10000</v>
       </c>
       <c r="P51" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q51" s="4">
         <v>1</v>
       </c>
       <c r="R51" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S51" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T51" s="4">
         <v>1</v>
       </c>
       <c r="U51" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V51" s="4"/>
       <c r="W51" s="4"/>
@@ -4774,38 +4877,39 @@
       <c r="AJ51" s="4"/>
       <c r="AK51" s="4"/>
       <c r="AL51" s="4"/>
-      <c r="AM51" s="6"/>
+      <c r="AM51" s="4"/>
       <c r="AN51" s="6"/>
       <c r="AO51" s="6"/>
       <c r="AP51" s="6"/>
-    </row>
-    <row r="52" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ51" s="6"/>
+    </row>
+    <row r="52" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="4"/>
       <c r="B52" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D52" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E52" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I52" s="4"/>
       <c r="J52" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
       <c r="M52" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N52" s="4">
         <v>6.5</v>
@@ -4814,22 +4918,22 @@
         <v>9</v>
       </c>
       <c r="P52" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="Q52" s="4">
         <v>7</v>
       </c>
       <c r="R52" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S52" s="4" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="T52" s="4">
         <v>1</v>
       </c>
       <c r="U52" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V52" s="4"/>
       <c r="W52" s="4"/>
@@ -4848,36 +4952,37 @@
       <c r="AJ52" s="4"/>
       <c r="AK52" s="4"/>
       <c r="AL52" s="4"/>
-      <c r="AM52" s="6"/>
+      <c r="AM52" s="4"/>
       <c r="AN52" s="6"/>
       <c r="AO52" s="6"/>
       <c r="AP52" s="6"/>
-    </row>
-    <row r="53" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ52" s="6"/>
+    </row>
+    <row r="53" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="4"/>
       <c r="B53" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
       <c r="J53" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
       <c r="M53" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N53" s="4">
         <v>5</v>
@@ -4886,22 +4991,22 @@
         <v>9</v>
       </c>
       <c r="P53" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="Q53" s="4">
         <v>1</v>
       </c>
       <c r="R53" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S53" s="4" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="T53" s="4">
         <v>1</v>
       </c>
       <c r="U53" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V53" s="4"/>
       <c r="W53" s="4"/>
@@ -4920,60 +5025,61 @@
       <c r="AJ53" s="4"/>
       <c r="AK53" s="4"/>
       <c r="AL53" s="4"/>
-      <c r="AM53" s="6"/>
+      <c r="AM53" s="4"/>
       <c r="AN53" s="6"/>
       <c r="AO53" s="6"/>
       <c r="AP53" s="6"/>
-    </row>
-    <row r="54" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ53" s="6"/>
+    </row>
+    <row r="54" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="4"/>
       <c r="B54" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C54" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D54" s="4" t="s">
-        <v>136</v>
-      </c>
       <c r="E54" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
       <c r="J54" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>
       <c r="M54" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N54" s="4"/>
       <c r="O54" s="4">
         <v>250000</v>
       </c>
       <c r="P54" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q54" s="4">
         <v>1</v>
       </c>
       <c r="R54" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S54" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T54" s="4">
         <v>1</v>
       </c>
       <c r="U54" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V54" s="4"/>
       <c r="W54" s="4"/>
@@ -4992,58 +5098,59 @@
       <c r="AJ54" s="4"/>
       <c r="AK54" s="4"/>
       <c r="AL54" s="4"/>
-      <c r="AM54" s="6"/>
+      <c r="AM54" s="4"/>
       <c r="AN54" s="6"/>
       <c r="AO54" s="6"/>
       <c r="AP54" s="6"/>
-    </row>
-    <row r="55" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ54" s="6"/>
+    </row>
+    <row r="55" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="4"/>
       <c r="B55" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C55" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D55" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="D55" s="4" t="s">
-        <v>137</v>
-      </c>
       <c r="E55" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
       <c r="J55" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K55" s="4"/>
       <c r="L55" s="4"/>
       <c r="M55" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N55" s="4"/>
       <c r="O55" s="4">
         <v>126</v>
       </c>
       <c r="P55" s="4" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="Q55" s="4">
         <v>90</v>
       </c>
       <c r="R55" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S55" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="T55" s="4">
         <v>1</v>
       </c>
       <c r="U55" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V55" s="4"/>
       <c r="W55" s="4"/>
@@ -5062,58 +5169,59 @@
       <c r="AJ55" s="4"/>
       <c r="AK55" s="4"/>
       <c r="AL55" s="4"/>
-      <c r="AM55" s="6"/>
+      <c r="AM55" s="4"/>
       <c r="AN55" s="6"/>
       <c r="AO55" s="6"/>
       <c r="AP55" s="6"/>
-    </row>
-    <row r="56" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ55" s="6"/>
+    </row>
+    <row r="56" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="4"/>
       <c r="B56" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C56" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D56" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="D56" s="4" t="s">
-        <v>137</v>
-      </c>
       <c r="E56" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
       <c r="J56" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K56" s="4"/>
       <c r="L56" s="4"/>
       <c r="M56" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N56" s="4"/>
       <c r="O56" s="4">
         <v>410</v>
       </c>
       <c r="P56" s="4" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="Q56" s="4">
         <v>90</v>
       </c>
       <c r="R56" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S56" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T56" s="4">
         <v>10</v>
       </c>
       <c r="U56" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="V56" s="4"/>
       <c r="W56" s="4"/>
@@ -5132,58 +5240,59 @@
       <c r="AJ56" s="4"/>
       <c r="AK56" s="4"/>
       <c r="AL56" s="4"/>
-      <c r="AM56" s="6"/>
+      <c r="AM56" s="4"/>
       <c r="AN56" s="6"/>
       <c r="AO56" s="6"/>
       <c r="AP56" s="6"/>
-    </row>
-    <row r="57" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ56" s="6"/>
+    </row>
+    <row r="57" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="4"/>
       <c r="B57" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
       <c r="J57" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K57" s="4"/>
       <c r="L57" s="4"/>
       <c r="M57" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N57" s="4"/>
       <c r="O57" s="4">
         <v>8</v>
       </c>
       <c r="P57" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q57" s="4">
         <v>1</v>
       </c>
       <c r="R57" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S57" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T57" s="4">
         <v>1</v>
       </c>
       <c r="U57" s="4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="V57" s="4"/>
       <c r="W57" s="4"/>
@@ -5202,58 +5311,59 @@
       <c r="AJ57" s="4"/>
       <c r="AK57" s="4"/>
       <c r="AL57" s="4"/>
-      <c r="AM57" s="6"/>
+      <c r="AM57" s="4"/>
       <c r="AN57" s="6"/>
       <c r="AO57" s="6"/>
       <c r="AP57" s="6"/>
-    </row>
-    <row r="58" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ57" s="6"/>
+    </row>
+    <row r="58" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="4"/>
       <c r="B58" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
       <c r="J58" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K58" s="4"/>
       <c r="L58" s="4"/>
       <c r="M58" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N58" s="4"/>
       <c r="O58" s="4">
         <v>15</v>
       </c>
       <c r="P58" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q58" s="4">
         <v>1</v>
       </c>
       <c r="R58" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S58" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T58" s="4">
         <v>1</v>
       </c>
       <c r="U58" s="4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="V58" s="4"/>
       <c r="W58" s="4"/>
@@ -5272,62 +5382,63 @@
       <c r="AJ58" s="4"/>
       <c r="AK58" s="4"/>
       <c r="AL58" s="4"/>
-      <c r="AM58" s="6"/>
+      <c r="AM58" s="4"/>
       <c r="AN58" s="6"/>
       <c r="AO58" s="6"/>
       <c r="AP58" s="6"/>
-    </row>
-    <row r="59" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ58" s="6"/>
+    </row>
+    <row r="59" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="4"/>
       <c r="B59" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C59" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E59" s="4" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
       <c r="J59" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K59" s="4"/>
       <c r="L59" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="M59" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N59" s="4">
         <v>9.5</v>
       </c>
       <c r="O59" s="4"/>
       <c r="P59" s="4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="Q59" s="4">
         <v>7</v>
       </c>
       <c r="R59" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S59" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T59" s="4">
         <v>1</v>
       </c>
       <c r="U59" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V59" s="4"/>
       <c r="W59" s="4"/>
@@ -5346,62 +5457,63 @@
       <c r="AJ59" s="4"/>
       <c r="AK59" s="4"/>
       <c r="AL59" s="4"/>
-      <c r="AM59" s="6"/>
+      <c r="AM59" s="4"/>
       <c r="AN59" s="6"/>
       <c r="AO59" s="6"/>
       <c r="AP59" s="6"/>
-    </row>
-    <row r="60" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ59" s="6"/>
+    </row>
+    <row r="60" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="4"/>
       <c r="B60" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D60" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C60" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E60" s="4" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
       <c r="J60" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K60" s="4"/>
       <c r="L60" s="4" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="M60" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N60" s="4">
         <v>6.5</v>
       </c>
       <c r="O60" s="4"/>
       <c r="P60" s="4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="Q60" s="4">
         <v>30</v>
       </c>
       <c r="R60" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S60" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T60" s="4">
         <v>1</v>
       </c>
       <c r="U60" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V60" s="4"/>
       <c r="W60" s="4"/>
@@ -5420,62 +5532,63 @@
       <c r="AJ60" s="4"/>
       <c r="AK60" s="4"/>
       <c r="AL60" s="4"/>
-      <c r="AM60" s="6"/>
+      <c r="AM60" s="4"/>
       <c r="AN60" s="6"/>
       <c r="AO60" s="6"/>
       <c r="AP60" s="6"/>
-    </row>
-    <row r="61" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ60" s="6"/>
+    </row>
+    <row r="61" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="4"/>
       <c r="B61" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D61" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C61" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E61" s="4" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
       <c r="J61" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K61" s="4"/>
       <c r="L61" s="4" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="M61" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N61" s="4">
         <v>5</v>
       </c>
       <c r="O61" s="4"/>
       <c r="P61" s="4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="Q61" s="4">
         <v>7</v>
       </c>
       <c r="R61" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S61" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="T61" s="4">
         <v>1</v>
       </c>
       <c r="U61" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V61" s="4"/>
       <c r="W61" s="4"/>
@@ -5494,62 +5607,63 @@
       <c r="AJ61" s="4"/>
       <c r="AK61" s="4"/>
       <c r="AL61" s="4"/>
-      <c r="AM61" s="6"/>
+      <c r="AM61" s="4"/>
       <c r="AN61" s="6"/>
       <c r="AO61" s="6"/>
       <c r="AP61" s="6"/>
-    </row>
-    <row r="62" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ61" s="6"/>
+    </row>
+    <row r="62" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="4"/>
       <c r="B62" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D62" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C62" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E62" s="4" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
       <c r="J62" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K62" s="4"/>
       <c r="L62" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="M62" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N62" s="4">
         <v>8</v>
       </c>
       <c r="O62" s="4"/>
       <c r="P62" s="4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="Q62" s="4">
         <v>1</v>
       </c>
       <c r="R62" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S62" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="T62" s="4">
         <v>1</v>
       </c>
       <c r="U62" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V62" s="4"/>
       <c r="W62" s="4"/>
@@ -5568,62 +5682,63 @@
       <c r="AJ62" s="4"/>
       <c r="AK62" s="4"/>
       <c r="AL62" s="4"/>
-      <c r="AM62" s="6"/>
+      <c r="AM62" s="4"/>
       <c r="AN62" s="6"/>
       <c r="AO62" s="6"/>
       <c r="AP62" s="6"/>
-    </row>
-    <row r="63" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ62" s="6"/>
+    </row>
+    <row r="63" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="4"/>
       <c r="B63" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D63" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C63" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E63" s="4" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
       <c r="J63" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K63" s="4"/>
       <c r="L63" s="4" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N63" s="4">
         <v>4</v>
       </c>
       <c r="O63" s="4"/>
       <c r="P63" s="4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="Q63" s="4">
         <v>1</v>
       </c>
       <c r="R63" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S63" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="T63" s="4">
         <v>1</v>
       </c>
       <c r="U63" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V63" s="4"/>
       <c r="W63" s="4"/>
@@ -5642,62 +5757,63 @@
       <c r="AJ63" s="4"/>
       <c r="AK63" s="4"/>
       <c r="AL63" s="4"/>
-      <c r="AM63" s="6"/>
+      <c r="AM63" s="4"/>
       <c r="AN63" s="6"/>
       <c r="AO63" s="6"/>
       <c r="AP63" s="6"/>
-    </row>
-    <row r="64" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ63" s="6"/>
+    </row>
+    <row r="64" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="4"/>
       <c r="B64" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D64" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C64" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E64" s="4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G64" s="4"/>
       <c r="H64" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I64" s="4"/>
       <c r="J64" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K64" s="4"/>
       <c r="L64" s="4" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M64" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N64" s="4"/>
       <c r="O64" s="4"/>
       <c r="P64" s="4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="Q64" s="4">
         <v>1</v>
       </c>
       <c r="R64" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="S64" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="T64" s="4">
+        <v>1</v>
+      </c>
+      <c r="U64" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="S64" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="T64" s="4">
-        <v>1</v>
-      </c>
-      <c r="U64" s="4" t="s">
-        <v>51</v>
       </c>
       <c r="V64" s="4"/>
       <c r="W64" s="4"/>
@@ -5709,10 +5825,10 @@
       <c r="AC64" s="4"/>
       <c r="AD64" s="4"/>
       <c r="AE64" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="AF64" s="4" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="AG64" s="4"/>
       <c r="AH64" s="4"/>
@@ -5720,60 +5836,63 @@
       <c r="AJ64" s="4"/>
       <c r="AK64" s="4"/>
       <c r="AL64" s="4"/>
-      <c r="AM64" s="6"/>
+      <c r="AM64" s="4" t="s">
+        <v>159</v>
+      </c>
       <c r="AN64" s="6"/>
       <c r="AO64" s="6"/>
       <c r="AP64" s="6"/>
-    </row>
-    <row r="65" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AQ64" s="6"/>
+    </row>
+    <row r="65" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="4"/>
       <c r="B65" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D65" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C65" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E65" s="4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G65" s="4"/>
       <c r="H65" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I65" s="4"/>
       <c r="J65" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K65" s="4"/>
       <c r="L65" s="6"/>
       <c r="M65" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N65" s="4"/>
       <c r="O65" s="4"/>
       <c r="P65" s="4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="Q65" s="4">
         <v>30</v>
       </c>
       <c r="R65" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="S65" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="T65" s="4">
+        <v>1</v>
+      </c>
+      <c r="U65" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="S65" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="T65" s="4">
-        <v>1</v>
-      </c>
-      <c r="U65" s="4" t="s">
-        <v>51</v>
       </c>
       <c r="V65" s="4"/>
       <c r="W65" s="4"/>
@@ -5785,10 +5904,10 @@
       <c r="AC65" s="4"/>
       <c r="AD65" s="4"/>
       <c r="AE65" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="AF65" s="4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="AG65" s="4"/>
       <c r="AH65" s="4"/>
@@ -5796,13 +5915,40 @@
       <c r="AJ65" s="4"/>
       <c r="AK65" s="4"/>
       <c r="AL65" s="4"/>
-      <c r="AM65" s="6"/>
-      <c r="AN65" s="6"/>
-      <c r="AO65" s="6"/>
-      <c r="AP65" s="6"/>
+      <c r="AM65" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="AN65" s="6">
+        <v>2.7799999999999998E-2</v>
+      </c>
+      <c r="AO65" s="6">
+        <v>7.6879999999999997</v>
+      </c>
+      <c r="AP65" s="6">
+        <v>1.1994</v>
+      </c>
+      <c r="AQ65" s="6">
+        <v>7.6879999999999997</v>
+      </c>
+      <c r="AR65" s="3">
+        <v>0.88759999999999994</v>
+      </c>
+      <c r="AS65" s="3">
+        <v>2.1259999999999999</v>
+      </c>
+      <c r="AT65" s="3">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="AU65" s="3">
+        <v>20</v>
+      </c>
+      <c r="AV65" s="3">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP65" xr:uid="{057945F5-944B-4C7F-AE65-F75344336C85}"/>
+  <autoFilter ref="A1:AQ65" xr:uid="{057945F5-944B-4C7F-AE65-F75344336C85}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/inst/extdata/blackfeet_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/blackfeet_tribe_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/hannah_ferriby_tetratech_com/Documents/Documents/GitHub/TADACommunityHub/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="13_ncr:1_{2059C3BF-FEA9-4515-96A4-28B4B0F0BCB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{130860C9-82A3-4FB5-A050-0286E6625664}"/>
+  <xr:revisionPtr revIDLastSave="88" documentId="13_ncr:1_{2059C3BF-FEA9-4515-96A4-28B4B0F0BCB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EB3C725-F7A9-487D-A28F-0DB4BE2BF55F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9CAA114B-CC1B-4AA7-94E1-A6CD4C5CB112}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9CAA114B-CC1B-4AA7-94E1-A6CD4C5CB112}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="164">
   <si>
     <t>TADA.ComparableDataIdentifier</t>
   </si>
@@ -494,9 +494,6 @@
     <t>pHDirection</t>
   </si>
   <si>
-    <t>TemperatureExtreme</t>
-  </si>
-  <si>
     <t>pH_param_5</t>
   </si>
   <si>
@@ -518,10 +515,22 @@
     <t>MaxEqMagnitude</t>
   </si>
   <si>
-    <t>Min</t>
-  </si>
-  <si>
-    <t>Max</t>
+    <t>AmmoniaEqType</t>
+  </si>
+  <si>
+    <t>pH_param_10</t>
+  </si>
+  <si>
+    <t>pH_param_11</t>
+  </si>
+  <si>
+    <t>pH_param_12</t>
+  </si>
+  <si>
+    <t>Overall Min</t>
+  </si>
+  <si>
+    <t>Max Exponent</t>
   </si>
 </sst>
 </file>
@@ -600,32 +609,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF0E442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFCD758F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -955,27 +939,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{057945F5-944B-4C7F-AE65-F75344336C85}">
-  <dimension ref="A1:AY65"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:BB65"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="9.140625" style="3"/>
+    <col min="1" max="2" width="9.109375" style="3"/>
     <col min="3" max="3" width="27" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="18" width="9.140625" style="3"/>
-    <col min="19" max="19" width="19.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="20" max="30" width="9.140625" style="3"/>
-    <col min="31" max="31" width="20.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="149.7109375" style="3" customWidth="1"/>
-    <col min="33" max="33" width="12.42578125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="31.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="11" width="9.109375" style="3"/>
+    <col min="12" max="12" width="26.21875" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="9.109375" style="3"/>
+    <col min="19" max="19" width="19.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="20" max="30" width="9.109375" style="3"/>
+    <col min="31" max="31" width="20.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="149.6640625" style="3" customWidth="1"/>
+    <col min="33" max="33" width="15.88671875" style="3" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="15" style="3" bestFit="1" customWidth="1"/>
     <col min="35" max="36" width="22" style="3" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="13.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="24.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="15.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="3"/>
+    <col min="37" max="38" width="15.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="24.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="15.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:54" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1091,7 +1077,7 @@
         <v>34</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="AN1" s="1" t="s">
         <v>35</v>
@@ -1106,29 +1092,38 @@
         <v>38</v>
       </c>
       <c r="AR1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="AS1" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="AX1" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="AY1" s="4"/>
-    </row>
-    <row r="2" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BB1" s="4"/>
+    </row>
+    <row r="2" spans="1:54" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="4" t="s">
         <v>39</v>
@@ -1201,7 +1196,7 @@
       <c r="AP2" s="6"/>
       <c r="AQ2" s="6"/>
     </row>
-    <row r="3" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:54" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="s">
         <v>39</v>
@@ -1276,7 +1271,7 @@
       <c r="AP3" s="6"/>
       <c r="AQ3" s="6"/>
     </row>
-    <row r="4" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:54" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="s">
         <v>39</v>
@@ -1351,7 +1346,7 @@
       <c r="AP4" s="6"/>
       <c r="AQ4" s="6"/>
     </row>
-    <row r="5" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:54" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
         <v>39</v>
@@ -1422,7 +1417,7 @@
       <c r="AP5" s="6"/>
       <c r="AQ5" s="6"/>
     </row>
-    <row r="6" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:54" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
         <v>39</v>
@@ -1493,7 +1488,7 @@
       <c r="AP6" s="6"/>
       <c r="AQ6" s="6"/>
     </row>
-    <row r="7" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:54" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>39</v>
@@ -1568,7 +1563,7 @@
       <c r="AP7" s="6"/>
       <c r="AQ7" s="6"/>
     </row>
-    <row r="8" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:54" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>39</v>
@@ -1641,7 +1636,7 @@
       <c r="AP8" s="6"/>
       <c r="AQ8" s="6"/>
     </row>
-    <row r="9" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:54" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>39</v>
@@ -1712,7 +1707,7 @@
       <c r="AP9" s="6"/>
       <c r="AQ9" s="6"/>
     </row>
-    <row r="10" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:54" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>39</v>
@@ -1785,7 +1780,7 @@
       <c r="AP10" s="6"/>
       <c r="AQ10" s="6"/>
     </row>
-    <row r="11" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:54" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
         <v>39</v>
@@ -1858,7 +1853,7 @@
       <c r="AP11" s="6"/>
       <c r="AQ11" s="6"/>
     </row>
-    <row r="12" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:54" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
         <v>39</v>
@@ -1931,7 +1926,7 @@
       <c r="AP12" s="6"/>
       <c r="AQ12" s="6"/>
     </row>
-    <row r="13" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:54" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
         <v>39</v>
@@ -2006,7 +2001,7 @@
       <c r="AP13" s="6"/>
       <c r="AQ13" s="6"/>
     </row>
-    <row r="14" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:54" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
         <v>39</v>
@@ -2081,7 +2076,7 @@
       <c r="AP14" s="6"/>
       <c r="AQ14" s="6"/>
     </row>
-    <row r="15" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:54" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
       <c r="B15" s="4" t="s">
         <v>39</v>
@@ -2154,7 +2149,7 @@
       <c r="AP15" s="6"/>
       <c r="AQ15" s="6"/>
     </row>
-    <row r="16" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:54" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
       <c r="B16" s="4" t="s">
         <v>39</v>
@@ -2227,7 +2222,7 @@
       <c r="AP16" s="6"/>
       <c r="AQ16" s="6"/>
     </row>
-    <row r="17" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="4"/>
       <c r="B17" s="4" t="s">
         <v>39</v>
@@ -2298,7 +2293,7 @@
       <c r="AP17" s="6"/>
       <c r="AQ17" s="6"/>
     </row>
-    <row r="18" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
       <c r="B18" s="4" t="s">
         <v>39</v>
@@ -2369,7 +2364,7 @@
       <c r="AP18" s="6"/>
       <c r="AQ18" s="6"/>
     </row>
-    <row r="19" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="4"/>
       <c r="B19" s="4" t="s">
         <v>39</v>
@@ -2444,7 +2439,7 @@
       <c r="AP19" s="6"/>
       <c r="AQ19" s="6"/>
     </row>
-    <row r="20" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="4"/>
       <c r="B20" s="4" t="s">
         <v>39</v>
@@ -2519,7 +2514,7 @@
       <c r="AP20" s="6"/>
       <c r="AQ20" s="6"/>
     </row>
-    <row r="21" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="4"/>
       <c r="B21" s="4" t="s">
         <v>39</v>
@@ -2592,7 +2587,7 @@
       <c r="AP21" s="6"/>
       <c r="AQ21" s="6"/>
     </row>
-    <row r="22" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
       <c r="B22" s="4" t="s">
         <v>39</v>
@@ -2665,7 +2660,7 @@
       <c r="AP22" s="6"/>
       <c r="AQ22" s="6"/>
     </row>
-    <row r="23" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="4"/>
       <c r="B23" s="4" t="s">
         <v>39</v>
@@ -2738,7 +2733,7 @@
       <c r="AP23" s="6"/>
       <c r="AQ23" s="6"/>
     </row>
-    <row r="24" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="4"/>
       <c r="B24" s="4" t="s">
         <v>39</v>
@@ -2811,7 +2806,7 @@
       <c r="AP24" s="6"/>
       <c r="AQ24" s="6"/>
     </row>
-    <row r="25" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="4"/>
       <c r="B25" s="4" t="s">
         <v>39</v>
@@ -2884,7 +2879,7 @@
       <c r="AP25" s="6"/>
       <c r="AQ25" s="6"/>
     </row>
-    <row r="26" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="4"/>
       <c r="B26" s="4" t="s">
         <v>39</v>
@@ -2957,7 +2952,7 @@
       <c r="AP26" s="6"/>
       <c r="AQ26" s="6"/>
     </row>
-    <row r="27" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="4"/>
       <c r="B27" s="4" t="s">
         <v>39</v>
@@ -3030,7 +3025,7 @@
       <c r="AP27" s="6"/>
       <c r="AQ27" s="6"/>
     </row>
-    <row r="28" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="4"/>
       <c r="B28" s="4" t="s">
         <v>39</v>
@@ -3103,7 +3098,7 @@
       <c r="AP28" s="6"/>
       <c r="AQ28" s="6"/>
     </row>
-    <row r="29" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="s">
         <v>39</v>
@@ -3176,7 +3171,7 @@
       <c r="AP29" s="6"/>
       <c r="AQ29" s="6"/>
     </row>
-    <row r="30" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="4"/>
       <c r="B30" s="4" t="s">
         <v>39</v>
@@ -3249,7 +3244,7 @@
       <c r="AP30" s="6"/>
       <c r="AQ30" s="6"/>
     </row>
-    <row r="31" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="4"/>
       <c r="B31" s="4" t="s">
         <v>39</v>
@@ -3320,7 +3315,7 @@
       <c r="AP31" s="6"/>
       <c r="AQ31" s="6"/>
     </row>
-    <row r="32" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="4"/>
       <c r="B32" s="4" t="s">
         <v>39</v>
@@ -3391,7 +3386,7 @@
       <c r="AP32" s="6"/>
       <c r="AQ32" s="6"/>
     </row>
-    <row r="33" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="4"/>
       <c r="B33" s="4" t="s">
         <v>39</v>
@@ -3462,7 +3457,7 @@
       <c r="AP33" s="6"/>
       <c r="AQ33" s="6"/>
     </row>
-    <row r="34" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="4"/>
       <c r="B34" s="4" t="s">
         <v>39</v>
@@ -3546,7 +3541,7 @@
       <c r="AP34" s="6"/>
       <c r="AQ34" s="6"/>
     </row>
-    <row r="35" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="4"/>
       <c r="B35" s="4" t="s">
         <v>39</v>
@@ -3630,7 +3625,7 @@
       <c r="AP35" s="6"/>
       <c r="AQ35" s="6"/>
     </row>
-    <row r="36" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="4"/>
       <c r="B36" s="4" t="s">
         <v>39</v>
@@ -3712,7 +3707,7 @@
       <c r="AP36" s="6"/>
       <c r="AQ36" s="6"/>
     </row>
-    <row r="37" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="4"/>
       <c r="B37" s="4" t="s">
         <v>39</v>
@@ -3794,7 +3789,7 @@
       <c r="AP37" s="6"/>
       <c r="AQ37" s="6"/>
     </row>
-    <row r="38" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="4"/>
       <c r="B38" s="4" t="s">
         <v>39</v>
@@ -3878,7 +3873,7 @@
       <c r="AP38" s="6"/>
       <c r="AQ38" s="6"/>
     </row>
-    <row r="39" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="4"/>
       <c r="B39" s="4" t="s">
         <v>39</v>
@@ -3962,7 +3957,7 @@
       <c r="AP39" s="6"/>
       <c r="AQ39" s="6"/>
     </row>
-    <row r="40" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="4"/>
       <c r="B40" s="4" t="s">
         <v>39</v>
@@ -4044,7 +4039,7 @@
       <c r="AP40" s="6"/>
       <c r="AQ40" s="6"/>
     </row>
-    <row r="41" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="4"/>
       <c r="B41" s="4" t="s">
         <v>39</v>
@@ -4126,7 +4121,7 @@
       <c r="AP41" s="6"/>
       <c r="AQ41" s="6"/>
     </row>
-    <row r="42" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="4"/>
       <c r="B42" s="4" t="s">
         <v>39</v>
@@ -4208,7 +4203,7 @@
       <c r="AP42" s="6"/>
       <c r="AQ42" s="6"/>
     </row>
-    <row r="43" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="4"/>
       <c r="B43" s="4" t="s">
         <v>39</v>
@@ -4290,7 +4285,7 @@
       <c r="AP43" s="6"/>
       <c r="AQ43" s="6"/>
     </row>
-    <row r="44" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="4"/>
       <c r="B44" s="4" t="s">
         <v>39</v>
@@ -4372,7 +4367,7 @@
       <c r="AP44" s="6"/>
       <c r="AQ44" s="6"/>
     </row>
-    <row r="45" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="4"/>
       <c r="B45" s="4" t="s">
         <v>39</v>
@@ -4443,7 +4438,7 @@
       <c r="AP45" s="6"/>
       <c r="AQ45" s="6"/>
     </row>
-    <row r="46" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="4"/>
       <c r="B46" s="4" t="s">
         <v>39</v>
@@ -4516,7 +4511,7 @@
       <c r="AP46" s="6"/>
       <c r="AQ46" s="6"/>
     </row>
-    <row r="47" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
       <c r="B47" s="4" t="s">
         <v>39</v>
@@ -4589,7 +4584,7 @@
       <c r="AP47" s="6"/>
       <c r="AQ47" s="6"/>
     </row>
-    <row r="48" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="4"/>
       <c r="B48" s="4" t="s">
         <v>39</v>
@@ -4664,7 +4659,7 @@
       <c r="AP48" s="6"/>
       <c r="AQ48" s="6"/>
     </row>
-    <row r="49" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
       <c r="B49" s="4" t="s">
         <v>39</v>
@@ -4739,7 +4734,7 @@
       <c r="AP49" s="6"/>
       <c r="AQ49" s="6"/>
     </row>
-    <row r="50" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="4"/>
       <c r="B50" s="4" t="s">
         <v>39</v>
@@ -4812,7 +4807,7 @@
       <c r="AP50" s="6"/>
       <c r="AQ50" s="6"/>
     </row>
-    <row r="51" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="4"/>
       <c r="B51" s="4" t="s">
         <v>39</v>
@@ -4883,7 +4878,7 @@
       <c r="AP51" s="6"/>
       <c r="AQ51" s="6"/>
     </row>
-    <row r="52" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="4"/>
       <c r="B52" s="4" t="s">
         <v>39</v>
@@ -4958,7 +4953,7 @@
       <c r="AP52" s="6"/>
       <c r="AQ52" s="6"/>
     </row>
-    <row r="53" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="4"/>
       <c r="B53" s="4" t="s">
         <v>39</v>
@@ -5031,7 +5026,7 @@
       <c r="AP53" s="6"/>
       <c r="AQ53" s="6"/>
     </row>
-    <row r="54" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="4"/>
       <c r="B54" s="4" t="s">
         <v>39</v>
@@ -5104,7 +5099,7 @@
       <c r="AP54" s="6"/>
       <c r="AQ54" s="6"/>
     </row>
-    <row r="55" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="4"/>
       <c r="B55" s="4" t="s">
         <v>39</v>
@@ -5175,7 +5170,7 @@
       <c r="AP55" s="6"/>
       <c r="AQ55" s="6"/>
     </row>
-    <row r="56" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="4"/>
       <c r="B56" s="4" t="s">
         <v>39</v>
@@ -5246,7 +5241,7 @@
       <c r="AP56" s="6"/>
       <c r="AQ56" s="6"/>
     </row>
-    <row r="57" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="4"/>
       <c r="B57" s="4" t="s">
         <v>39</v>
@@ -5317,7 +5312,7 @@
       <c r="AP57" s="6"/>
       <c r="AQ57" s="6"/>
     </row>
-    <row r="58" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="4"/>
       <c r="B58" s="4" t="s">
         <v>39</v>
@@ -5388,7 +5383,7 @@
       <c r="AP58" s="6"/>
       <c r="AQ58" s="6"/>
     </row>
-    <row r="59" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="4"/>
       <c r="B59" s="4" t="s">
         <v>39</v>
@@ -5463,7 +5458,7 @@
       <c r="AP59" s="6"/>
       <c r="AQ59" s="6"/>
     </row>
-    <row r="60" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="4"/>
       <c r="B60" s="4" t="s">
         <v>39</v>
@@ -5538,7 +5533,7 @@
       <c r="AP60" s="6"/>
       <c r="AQ60" s="6"/>
     </row>
-    <row r="61" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="4"/>
       <c r="B61" s="4" t="s">
         <v>39</v>
@@ -5613,7 +5608,7 @@
       <c r="AP61" s="6"/>
       <c r="AQ61" s="6"/>
     </row>
-    <row r="62" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="4"/>
       <c r="B62" s="4" t="s">
         <v>39</v>
@@ -5688,7 +5683,7 @@
       <c r="AP62" s="6"/>
       <c r="AQ62" s="6"/>
     </row>
-    <row r="63" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="4"/>
       <c r="B63" s="4" t="s">
         <v>39</v>
@@ -5763,7 +5758,7 @@
       <c r="AP63" s="6"/>
       <c r="AQ63" s="6"/>
     </row>
-    <row r="64" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="4"/>
       <c r="B64" s="4" t="s">
         <v>39</v>
@@ -5837,14 +5832,46 @@
       <c r="AK64" s="4"/>
       <c r="AL64" s="4"/>
       <c r="AM64" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="AN64" s="6"/>
-      <c r="AO64" s="6"/>
-      <c r="AP64" s="6"/>
-      <c r="AQ64" s="6"/>
-    </row>
-    <row r="65" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+      <c r="AN64" s="6">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="AO64" s="6">
+        <v>7.2039999999999997</v>
+      </c>
+      <c r="AP64" s="6">
+        <v>39</v>
+      </c>
+      <c r="AQ64" s="6">
+        <v>7.2039999999999997</v>
+      </c>
+      <c r="AR64" s="3">
+        <v>0.72489999999999999</v>
+      </c>
+      <c r="AS64" s="3">
+        <v>1.14E-2</v>
+      </c>
+      <c r="AT64" s="3">
+        <v>7.2039999999999997</v>
+      </c>
+      <c r="AU64" s="3">
+        <v>1.6181000000000001</v>
+      </c>
+      <c r="AV64" s="3">
+        <v>7.2039999999999997</v>
+      </c>
+      <c r="AW64" s="3">
+        <v>23.12</v>
+      </c>
+      <c r="AX64" s="3">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="AY64" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="4"/>
       <c r="B65" s="4" t="s">
         <v>39</v>
@@ -5916,7 +5943,7 @@
       <c r="AK65" s="4"/>
       <c r="AL65" s="4"/>
       <c r="AM65" s="4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AN65" s="6">
         <v>2.7799999999999998E-2</v>

--- a/inst/extdata/blackfeet_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/blackfeet_tribe_criteria_crosswalk.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/hannah_ferriby_tetratech_com/Documents/Documents/GitHub/TADACommunityHub/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="88" documentId="13_ncr:1_{2059C3BF-FEA9-4515-96A4-28B4B0F0BCB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EB3C725-F7A9-487D-A28F-0DB4BE2BF55F}"/>
+  <xr:revisionPtr revIDLastSave="93" documentId="13_ncr:1_{2059C3BF-FEA9-4515-96A4-28B4B0F0BCB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F6D89B3-3DBF-4E0B-9742-CF20FA2FE482}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9CAA114B-CC1B-4AA7-94E1-A6CD4C5CB112}"/>
   </bookViews>
@@ -104,18 +104,12 @@
     <t>FreqMethod</t>
   </si>
   <si>
-    <t>AssessPeriod</t>
-  </si>
-  <si>
     <t>AssessPeriodStartDate</t>
   </si>
   <si>
     <t>AssessPeriodEndDate</t>
   </si>
   <si>
-    <t>Season</t>
-  </si>
-  <si>
     <t>SeasonStartDate</t>
   </si>
   <si>
@@ -531,6 +525,12 @@
   </si>
   <si>
     <t>Max Exponent</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Links</t>
   </si>
 </sst>
 </file>
@@ -1047,138 +1047,138 @@
         <v>27</v>
       </c>
       <c r="AC1" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="AE1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="AI1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AK1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="AI1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AK1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AL1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="AX1" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="AN1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>157</v>
       </c>
       <c r="BB1" s="4"/>
     </row>
     <row r="2" spans="1:54" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N2" s="4"/>
       <c r="O2" s="4">
         <v>20000</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q2" s="4">
         <v>4</v>
       </c>
       <c r="R2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="T2" s="4">
+        <v>1</v>
+      </c>
+      <c r="U2" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="T2" s="4">
-        <v>1</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>49</v>
       </c>
       <c r="V2" s="4"/>
       <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="5"/>
-      <c r="AA2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="4"/>
+      <c r="AA2" s="4"/>
       <c r="AB2" s="4"/>
       <c r="AC2" s="4"/>
       <c r="AD2" s="4"/>
@@ -1199,61 +1199,61 @@
     <row r="3" spans="1:54" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="E3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>52</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K3" s="4"/>
       <c r="L3" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N3" s="4"/>
       <c r="O3" s="4">
         <v>1.5</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q3" s="4">
         <v>30</v>
       </c>
       <c r="R3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="T3" s="4">
+        <v>1</v>
+      </c>
+      <c r="U3" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="T3" s="4">
-        <v>1</v>
-      </c>
-      <c r="U3" s="4" t="s">
-        <v>49</v>
       </c>
       <c r="V3" s="4"/>
       <c r="W3" s="4"/>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="4"/>
-      <c r="Z3" s="5"/>
-      <c r="AA3" s="5"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="4"/>
+      <c r="AA3" s="4"/>
       <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
       <c r="AD3" s="4"/>
@@ -1274,61 +1274,61 @@
     <row r="4" spans="1:54" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="E4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>52</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K4" s="4"/>
       <c r="L4" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N4" s="4"/>
       <c r="O4" s="4">
         <v>3.1</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q4" s="4">
         <v>30</v>
       </c>
       <c r="R4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="T4" s="4">
+        <v>1</v>
+      </c>
+      <c r="U4" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="S4" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="T4" s="4">
-        <v>1</v>
-      </c>
-      <c r="U4" s="4" t="s">
-        <v>49</v>
       </c>
       <c r="V4" s="4"/>
       <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="4"/>
-      <c r="Z4" s="5"/>
-      <c r="AA4" s="5"/>
+      <c r="X4" s="5"/>
+      <c r="Y4" s="5"/>
+      <c r="Z4" s="4"/>
+      <c r="AA4" s="4"/>
       <c r="AB4" s="4"/>
       <c r="AC4" s="4"/>
       <c r="AD4" s="4"/>
@@ -1349,57 +1349,57 @@
     <row r="5" spans="1:54" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E5" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N5" s="4"/>
       <c r="O5" s="4">
         <v>5.6</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q5" s="4">
         <v>30</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T5" s="4">
         <v>1</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V5" s="4"/>
       <c r="W5" s="4"/>
-      <c r="X5" s="4"/>
-      <c r="Y5" s="4"/>
-      <c r="Z5" s="5"/>
-      <c r="AA5" s="5"/>
+      <c r="X5" s="5"/>
+      <c r="Y5" s="5"/>
+      <c r="Z5" s="4"/>
+      <c r="AA5" s="4"/>
       <c r="AB5" s="4"/>
       <c r="AC5" s="4"/>
       <c r="AD5" s="4"/>
@@ -1420,57 +1420,57 @@
     <row r="6" spans="1:54" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N6" s="4"/>
       <c r="O6" s="4">
         <v>5.6</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q6" s="4">
         <v>30</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T6" s="4">
         <v>1</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V6" s="4"/>
       <c r="W6" s="4"/>
-      <c r="X6" s="4"/>
-      <c r="Y6" s="4"/>
-      <c r="Z6" s="5"/>
-      <c r="AA6" s="5"/>
+      <c r="X6" s="5"/>
+      <c r="Y6" s="5"/>
+      <c r="Z6" s="4"/>
+      <c r="AA6" s="4"/>
       <c r="AB6" s="4"/>
       <c r="AC6" s="4"/>
       <c r="AD6" s="4"/>
@@ -1491,61 +1491,61 @@
     <row r="7" spans="1:54" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E7" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N7" s="4"/>
       <c r="O7" s="4">
         <v>340</v>
       </c>
       <c r="P7" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>1</v>
+      </c>
+      <c r="R7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="S7" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="Q7" s="4">
-        <v>1</v>
-      </c>
-      <c r="R7" s="4" t="s">
+      <c r="T7" s="4">
+        <v>1</v>
+      </c>
+      <c r="U7" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="S7" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="T7" s="4">
-        <v>1</v>
-      </c>
-      <c r="U7" s="4" t="s">
-        <v>49</v>
       </c>
       <c r="V7" s="4"/>
       <c r="W7" s="4"/>
-      <c r="X7" s="4"/>
-      <c r="Y7" s="4"/>
-      <c r="Z7" s="5"/>
-      <c r="AA7" s="5"/>
+      <c r="X7" s="5"/>
+      <c r="Y7" s="5"/>
+      <c r="Z7" s="4"/>
+      <c r="AA7" s="4"/>
       <c r="AB7" s="4"/>
       <c r="AC7" s="4"/>
       <c r="AD7" s="4"/>
@@ -1566,59 +1566,59 @@
     <row r="8" spans="1:54" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E8" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N8" s="4"/>
       <c r="O8" s="4">
         <v>150</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q8" s="4">
         <v>4</v>
       </c>
       <c r="R8" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="S8" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="T8" s="4">
+        <v>1</v>
+      </c>
+      <c r="U8" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="S8" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="T8" s="4">
-        <v>1</v>
-      </c>
-      <c r="U8" s="4" t="s">
-        <v>49</v>
       </c>
       <c r="V8" s="4"/>
       <c r="W8" s="4"/>
-      <c r="X8" s="4"/>
-      <c r="Y8" s="4"/>
-      <c r="Z8" s="5"/>
-      <c r="AA8" s="5"/>
+      <c r="X8" s="5"/>
+      <c r="Y8" s="5"/>
+      <c r="Z8" s="4"/>
+      <c r="AA8" s="4"/>
       <c r="AB8" s="4"/>
       <c r="AC8" s="4"/>
       <c r="AD8" s="4"/>
@@ -1639,57 +1639,57 @@
     <row r="9" spans="1:54" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>60</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N9" s="4"/>
       <c r="O9" s="4">
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q9" s="4">
         <v>30</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T9" s="4">
         <v>1</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V9" s="4"/>
       <c r="W9" s="4"/>
-      <c r="X9" s="4"/>
-      <c r="Y9" s="4"/>
-      <c r="Z9" s="5"/>
-      <c r="AA9" s="5"/>
+      <c r="X9" s="5"/>
+      <c r="Y9" s="5"/>
+      <c r="Z9" s="4"/>
+      <c r="AA9" s="4"/>
       <c r="AB9" s="4"/>
       <c r="AC9" s="4"/>
       <c r="AD9" s="4"/>
@@ -1710,59 +1710,59 @@
     <row r="10" spans="1:54" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E10" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
       <c r="P10" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q10" s="4">
         <v>1</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T10" s="4">
         <v>1</v>
       </c>
       <c r="U10" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V10" s="4"/>
       <c r="W10" s="4"/>
-      <c r="X10" s="4"/>
-      <c r="Y10" s="4"/>
-      <c r="Z10" s="5"/>
-      <c r="AA10" s="5"/>
+      <c r="X10" s="5"/>
+      <c r="Y10" s="5"/>
+      <c r="Z10" s="4"/>
+      <c r="AA10" s="4"/>
       <c r="AB10" s="4"/>
       <c r="AC10" s="4"/>
       <c r="AD10" s="4"/>
@@ -1783,59 +1783,59 @@
     <row r="11" spans="1:54" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E11" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
       <c r="P11" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q11" s="4">
         <v>30</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T11" s="4">
         <v>1</v>
       </c>
       <c r="U11" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V11" s="4"/>
       <c r="W11" s="4"/>
-      <c r="X11" s="4"/>
-      <c r="Y11" s="4"/>
-      <c r="Z11" s="5"/>
-      <c r="AA11" s="5"/>
+      <c r="X11" s="5"/>
+      <c r="Y11" s="5"/>
+      <c r="Z11" s="4"/>
+      <c r="AA11" s="4"/>
       <c r="AB11" s="4"/>
       <c r="AC11" s="4"/>
       <c r="AD11" s="4"/>
@@ -1856,59 +1856,59 @@
     <row r="12" spans="1:54" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>68</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N12" s="4"/>
       <c r="O12" s="4">
         <v>1300</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q12" s="4">
         <v>1</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T12" s="4">
         <v>1</v>
       </c>
       <c r="U12" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V12" s="4"/>
       <c r="W12" s="4"/>
-      <c r="X12" s="4"/>
-      <c r="Y12" s="4"/>
-      <c r="Z12" s="5"/>
-      <c r="AA12" s="5"/>
+      <c r="X12" s="5"/>
+      <c r="Y12" s="5"/>
+      <c r="Z12" s="4"/>
+      <c r="AA12" s="4"/>
       <c r="AB12" s="4"/>
       <c r="AC12" s="4"/>
       <c r="AD12" s="4"/>
@@ -1929,61 +1929,61 @@
     <row r="13" spans="1:54" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E13" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I13" s="4"/>
       <c r="J13" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N13" s="4"/>
       <c r="O13" s="4">
         <v>2.5</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q13" s="4">
         <v>30</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T13" s="4">
         <v>1</v>
       </c>
       <c r="U13" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V13" s="4"/>
       <c r="W13" s="4"/>
-      <c r="X13" s="4"/>
-      <c r="Y13" s="4"/>
-      <c r="Z13" s="5"/>
-      <c r="AA13" s="5"/>
+      <c r="X13" s="5"/>
+      <c r="Y13" s="5"/>
+      <c r="Z13" s="4"/>
+      <c r="AA13" s="4"/>
       <c r="AB13" s="4"/>
       <c r="AC13" s="4"/>
       <c r="AD13" s="4"/>
@@ -2004,61 +2004,61 @@
     <row r="14" spans="1:54" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E14" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I14" s="4"/>
       <c r="J14" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N14" s="4"/>
       <c r="O14" s="4">
         <v>1.4</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q14" s="4">
         <v>1</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S14" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T14" s="4">
         <v>1</v>
       </c>
       <c r="U14" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V14" s="4"/>
       <c r="W14" s="4"/>
-      <c r="X14" s="4"/>
-      <c r="Y14" s="4"/>
-      <c r="Z14" s="5"/>
-      <c r="AA14" s="5"/>
+      <c r="X14" s="5"/>
+      <c r="Y14" s="5"/>
+      <c r="Z14" s="4"/>
+      <c r="AA14" s="4"/>
       <c r="AB14" s="4"/>
       <c r="AC14" s="4"/>
       <c r="AD14" s="4"/>
@@ -2079,59 +2079,59 @@
     <row r="15" spans="1:54" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
       <c r="B15" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N15" s="4"/>
       <c r="O15" s="4">
         <v>0.05</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q15" s="4">
         <v>1</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S15" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T15" s="4">
         <v>1</v>
       </c>
       <c r="U15" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V15" s="4"/>
       <c r="W15" s="4"/>
-      <c r="X15" s="4"/>
-      <c r="Y15" s="4"/>
-      <c r="Z15" s="5"/>
-      <c r="AA15" s="5"/>
+      <c r="X15" s="5"/>
+      <c r="Y15" s="5"/>
+      <c r="Z15" s="4"/>
+      <c r="AA15" s="4"/>
       <c r="AB15" s="4"/>
       <c r="AC15" s="4"/>
       <c r="AD15" s="4"/>
@@ -2152,59 +2152,59 @@
     <row r="16" spans="1:54" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
       <c r="B16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E16" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
       <c r="J16" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N16" s="4"/>
       <c r="O16" s="4">
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q16" s="4">
         <v>30</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T16" s="4">
         <v>1</v>
       </c>
       <c r="U16" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V16" s="4"/>
       <c r="W16" s="4"/>
-      <c r="X16" s="4"/>
-      <c r="Y16" s="4"/>
-      <c r="Z16" s="5"/>
-      <c r="AA16" s="5"/>
+      <c r="X16" s="5"/>
+      <c r="Y16" s="5"/>
+      <c r="Z16" s="4"/>
+      <c r="AA16" s="4"/>
       <c r="AB16" s="4"/>
       <c r="AC16" s="4"/>
       <c r="AD16" s="4"/>
@@ -2225,57 +2225,57 @@
     <row r="17" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="4"/>
       <c r="B17" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E17" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
       <c r="J17" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N17" s="4"/>
       <c r="O17" s="4">
         <v>0.3</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Q17" s="4">
         <v>30</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S17" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T17" s="4">
         <v>1</v>
       </c>
       <c r="U17" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V17" s="4"/>
       <c r="W17" s="4"/>
-      <c r="X17" s="4"/>
-      <c r="Y17" s="4"/>
-      <c r="Z17" s="5"/>
-      <c r="AA17" s="5"/>
+      <c r="X17" s="5"/>
+      <c r="Y17" s="5"/>
+      <c r="Z17" s="4"/>
+      <c r="AA17" s="4"/>
       <c r="AB17" s="4"/>
       <c r="AC17" s="4"/>
       <c r="AD17" s="4"/>
@@ -2296,57 +2296,57 @@
     <row r="18" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
       <c r="B18" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E18" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
       <c r="J18" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N18" s="4"/>
       <c r="O18" s="4">
         <v>0.3</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Q18" s="4">
         <v>30</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T18" s="4">
         <v>1</v>
       </c>
       <c r="U18" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V18" s="4"/>
       <c r="W18" s="4"/>
-      <c r="X18" s="4"/>
-      <c r="Y18" s="4"/>
-      <c r="Z18" s="5"/>
-      <c r="AA18" s="5"/>
+      <c r="X18" s="5"/>
+      <c r="Y18" s="5"/>
+      <c r="Z18" s="4"/>
+      <c r="AA18" s="4"/>
       <c r="AB18" s="4"/>
       <c r="AC18" s="4"/>
       <c r="AD18" s="4"/>
@@ -2367,61 +2367,61 @@
     <row r="19" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="4"/>
       <c r="B19" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E19" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I19" s="4"/>
       <c r="J19" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
       <c r="M19" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N19" s="4"/>
       <c r="O19" s="4">
         <v>16</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q19" s="4">
         <v>1</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S19" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T19" s="4">
         <v>1</v>
       </c>
       <c r="U19" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V19" s="4"/>
       <c r="W19" s="4"/>
-      <c r="X19" s="4"/>
-      <c r="Y19" s="4"/>
-      <c r="Z19" s="5"/>
-      <c r="AA19" s="5"/>
+      <c r="X19" s="5"/>
+      <c r="Y19" s="5"/>
+      <c r="Z19" s="4"/>
+      <c r="AA19" s="4"/>
       <c r="AB19" s="4"/>
       <c r="AC19" s="4"/>
       <c r="AD19" s="4"/>
@@ -2442,61 +2442,61 @@
     <row r="20" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="4"/>
       <c r="B20" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E20" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
       <c r="M20" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N20" s="4"/>
       <c r="O20" s="4">
         <v>11</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q20" s="4">
         <v>30</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T20" s="4">
         <v>1</v>
       </c>
       <c r="U20" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V20" s="4"/>
       <c r="W20" s="4"/>
-      <c r="X20" s="4"/>
-      <c r="Y20" s="4"/>
-      <c r="Z20" s="5"/>
-      <c r="AA20" s="5"/>
+      <c r="X20" s="5"/>
+      <c r="Y20" s="5"/>
+      <c r="Z20" s="4"/>
+      <c r="AA20" s="4"/>
       <c r="AB20" s="4"/>
       <c r="AC20" s="4"/>
       <c r="AD20" s="4"/>
@@ -2517,59 +2517,59 @@
     <row r="21" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="4"/>
       <c r="B21" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
       <c r="J21" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
       <c r="M21" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N21" s="4"/>
       <c r="O21" s="4">
         <v>610</v>
       </c>
       <c r="P21" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q21" s="4">
         <v>1</v>
       </c>
       <c r="R21" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S21" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T21" s="4">
         <v>1</v>
       </c>
       <c r="U21" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V21" s="4"/>
       <c r="W21" s="4"/>
-      <c r="X21" s="4"/>
-      <c r="Y21" s="4"/>
-      <c r="Z21" s="5"/>
-      <c r="AA21" s="5"/>
+      <c r="X21" s="5"/>
+      <c r="Y21" s="5"/>
+      <c r="Z21" s="4"/>
+      <c r="AA21" s="4"/>
       <c r="AB21" s="4"/>
       <c r="AC21" s="4"/>
       <c r="AD21" s="4"/>
@@ -2590,59 +2590,59 @@
     <row r="22" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
       <c r="B22" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E22" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
       <c r="J22" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
       <c r="M22" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N22" s="4"/>
       <c r="O22" s="4">
         <v>4600</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q22" s="4">
         <v>30</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S22" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T22" s="4">
         <v>1</v>
       </c>
       <c r="U22" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V22" s="4"/>
       <c r="W22" s="4"/>
-      <c r="X22" s="4"/>
-      <c r="Y22" s="4"/>
-      <c r="Z22" s="5"/>
-      <c r="AA22" s="5"/>
+      <c r="X22" s="5"/>
+      <c r="Y22" s="5"/>
+      <c r="Z22" s="4"/>
+      <c r="AA22" s="4"/>
       <c r="AB22" s="4"/>
       <c r="AC22" s="4"/>
       <c r="AD22" s="4"/>
@@ -2663,59 +2663,59 @@
     <row r="23" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="4"/>
       <c r="B23" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
       <c r="J23" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N23" s="4"/>
       <c r="O23" s="4">
         <v>170</v>
       </c>
       <c r="P23" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q23" s="4">
         <v>1</v>
       </c>
       <c r="R23" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S23" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T23" s="4">
         <v>1</v>
       </c>
       <c r="U23" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V23" s="4"/>
       <c r="W23" s="4"/>
-      <c r="X23" s="4"/>
-      <c r="Y23" s="4"/>
-      <c r="Z23" s="5"/>
-      <c r="AA23" s="5"/>
+      <c r="X23" s="5"/>
+      <c r="Y23" s="5"/>
+      <c r="Z23" s="4"/>
+      <c r="AA23" s="4"/>
       <c r="AB23" s="4"/>
       <c r="AC23" s="4"/>
       <c r="AD23" s="4"/>
@@ -2736,59 +2736,59 @@
     <row r="24" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="4"/>
       <c r="B24" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E24" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
       <c r="J24" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
       <c r="M24" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N24" s="4"/>
       <c r="O24" s="4">
         <v>4200</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q24" s="4">
         <v>30</v>
       </c>
       <c r="R24" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S24" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T24" s="4">
         <v>1</v>
       </c>
       <c r="U24" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V24" s="4"/>
       <c r="W24" s="4"/>
-      <c r="X24" s="4"/>
-      <c r="Y24" s="4"/>
-      <c r="Z24" s="5"/>
-      <c r="AA24" s="5"/>
+      <c r="X24" s="5"/>
+      <c r="Y24" s="5"/>
+      <c r="Z24" s="4"/>
+      <c r="AA24" s="4"/>
       <c r="AB24" s="4"/>
       <c r="AC24" s="4"/>
       <c r="AD24" s="4"/>
@@ -2809,59 +2809,59 @@
     <row r="25" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="4"/>
       <c r="B25" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
       <c r="J25" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
       <c r="M25" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N25" s="4"/>
       <c r="O25" s="4">
         <v>0.24</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q25" s="4">
         <v>1</v>
       </c>
       <c r="R25" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S25" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T25" s="4">
         <v>1</v>
       </c>
       <c r="U25" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V25" s="4"/>
       <c r="W25" s="4"/>
-      <c r="X25" s="4"/>
-      <c r="Y25" s="4"/>
-      <c r="Z25" s="5"/>
-      <c r="AA25" s="5"/>
+      <c r="X25" s="5"/>
+      <c r="Y25" s="5"/>
+      <c r="Z25" s="4"/>
+      <c r="AA25" s="4"/>
       <c r="AB25" s="4"/>
       <c r="AC25" s="4"/>
       <c r="AD25" s="4"/>
@@ -2882,59 +2882,59 @@
     <row r="26" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="4"/>
       <c r="B26" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E26" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
       <c r="J26" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
       <c r="M26" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N26" s="4"/>
       <c r="O26" s="4">
         <v>0.47</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q26" s="4">
         <v>30</v>
       </c>
       <c r="R26" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S26" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T26" s="4">
         <v>1</v>
       </c>
       <c r="U26" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V26" s="4"/>
       <c r="W26" s="4"/>
-      <c r="X26" s="4"/>
-      <c r="Y26" s="4"/>
-      <c r="Z26" s="5"/>
-      <c r="AA26" s="5"/>
+      <c r="X26" s="5"/>
+      <c r="Y26" s="5"/>
+      <c r="Z26" s="4"/>
+      <c r="AA26" s="4"/>
       <c r="AB26" s="4"/>
       <c r="AC26" s="4"/>
       <c r="AD26" s="4"/>
@@ -2955,59 +2955,59 @@
     <row r="27" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="4"/>
       <c r="B27" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
       <c r="J27" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
       <c r="M27" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N27" s="4"/>
       <c r="O27" s="4">
         <v>7400</v>
       </c>
       <c r="P27" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q27" s="4">
         <v>1</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S27" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T27" s="4">
         <v>1</v>
       </c>
       <c r="U27" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V27" s="4"/>
       <c r="W27" s="4"/>
-      <c r="X27" s="4"/>
-      <c r="Y27" s="4"/>
-      <c r="Z27" s="5"/>
-      <c r="AA27" s="5"/>
+      <c r="X27" s="5"/>
+      <c r="Y27" s="5"/>
+      <c r="Z27" s="4"/>
+      <c r="AA27" s="4"/>
       <c r="AB27" s="4"/>
       <c r="AC27" s="4"/>
       <c r="AD27" s="4"/>
@@ -3028,59 +3028,59 @@
     <row r="28" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="4"/>
       <c r="B28" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E28" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
       <c r="J28" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
       <c r="M28" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N28" s="4"/>
       <c r="O28" s="4">
         <v>26000</v>
       </c>
       <c r="P28" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q28" s="4">
         <v>30</v>
       </c>
       <c r="R28" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S28" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T28" s="4">
         <v>1</v>
       </c>
       <c r="U28" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V28" s="4"/>
       <c r="W28" s="4"/>
-      <c r="X28" s="4"/>
-      <c r="Y28" s="4"/>
-      <c r="Z28" s="5"/>
-      <c r="AA28" s="5"/>
+      <c r="X28" s="5"/>
+      <c r="Y28" s="5"/>
+      <c r="Z28" s="4"/>
+      <c r="AA28" s="4"/>
       <c r="AB28" s="4"/>
       <c r="AC28" s="4"/>
       <c r="AD28" s="4"/>
@@ -3101,59 +3101,59 @@
     <row r="29" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E29" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I29" s="4"/>
       <c r="J29" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
       <c r="M29" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N29" s="4"/>
       <c r="O29" s="4">
         <v>22</v>
       </c>
       <c r="P29" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q29" s="4">
         <v>1</v>
       </c>
       <c r="R29" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S29" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T29" s="4">
         <v>1</v>
       </c>
       <c r="U29" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V29" s="4"/>
       <c r="W29" s="4"/>
-      <c r="X29" s="4"/>
-      <c r="Y29" s="4"/>
-      <c r="Z29" s="5"/>
-      <c r="AA29" s="5"/>
+      <c r="X29" s="5"/>
+      <c r="Y29" s="5"/>
+      <c r="Z29" s="4"/>
+      <c r="AA29" s="4"/>
       <c r="AB29" s="4"/>
       <c r="AC29" s="4"/>
       <c r="AD29" s="4"/>
@@ -3174,59 +3174,59 @@
     <row r="30" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="4"/>
       <c r="B30" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E30" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I30" s="4"/>
       <c r="J30" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N30" s="4"/>
       <c r="O30" s="4">
         <v>5.2</v>
       </c>
       <c r="P30" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q30" s="4">
         <v>30</v>
       </c>
       <c r="R30" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S30" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T30" s="4">
         <v>1</v>
       </c>
       <c r="U30" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V30" s="4"/>
       <c r="W30" s="4"/>
-      <c r="X30" s="4"/>
-      <c r="Y30" s="4"/>
-      <c r="Z30" s="5"/>
-      <c r="AA30" s="5"/>
+      <c r="X30" s="5"/>
+      <c r="Y30" s="5"/>
+      <c r="Z30" s="4"/>
+      <c r="AA30" s="4"/>
       <c r="AB30" s="4"/>
       <c r="AC30" s="4"/>
       <c r="AD30" s="4"/>
@@ -3247,57 +3247,57 @@
     <row r="31" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="4"/>
       <c r="B31" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
       <c r="J31" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
       <c r="M31" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N31" s="4"/>
       <c r="O31" s="4">
         <v>4</v>
       </c>
       <c r="P31" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q31" s="4">
         <v>1</v>
       </c>
       <c r="R31" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S31" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T31" s="4">
         <v>1</v>
       </c>
       <c r="U31" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V31" s="4"/>
       <c r="W31" s="4"/>
-      <c r="X31" s="4"/>
-      <c r="Y31" s="4"/>
-      <c r="Z31" s="5"/>
-      <c r="AA31" s="5"/>
+      <c r="X31" s="5"/>
+      <c r="Y31" s="5"/>
+      <c r="Z31" s="4"/>
+      <c r="AA31" s="4"/>
       <c r="AB31" s="4"/>
       <c r="AC31" s="4"/>
       <c r="AD31" s="4"/>
@@ -3318,57 +3318,57 @@
     <row r="32" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="4"/>
       <c r="B32" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E32" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
       <c r="J32" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
       <c r="M32" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N32" s="4"/>
       <c r="O32" s="4">
         <v>400</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q32" s="4">
         <v>30</v>
       </c>
       <c r="R32" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S32" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T32" s="4">
         <v>1</v>
       </c>
       <c r="U32" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V32" s="4"/>
       <c r="W32" s="4"/>
-      <c r="X32" s="4"/>
-      <c r="Y32" s="4"/>
-      <c r="Z32" s="5"/>
-      <c r="AA32" s="5"/>
+      <c r="X32" s="5"/>
+      <c r="Y32" s="5"/>
+      <c r="Z32" s="4"/>
+      <c r="AA32" s="4"/>
       <c r="AB32" s="4"/>
       <c r="AC32" s="4"/>
       <c r="AD32" s="4"/>
@@ -3389,57 +3389,57 @@
     <row r="33" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="4"/>
       <c r="B33" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
       <c r="J33" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
       <c r="M33" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N33" s="4"/>
       <c r="O33" s="4">
         <v>7000000</v>
       </c>
       <c r="P33" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="Q33" s="4">
         <v>1</v>
       </c>
       <c r="R33" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S33" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T33" s="4">
         <v>1</v>
       </c>
       <c r="U33" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V33" s="4"/>
       <c r="W33" s="4"/>
-      <c r="X33" s="4"/>
-      <c r="Y33" s="4"/>
-      <c r="Z33" s="5"/>
-      <c r="AA33" s="5"/>
+      <c r="X33" s="5"/>
+      <c r="Y33" s="5"/>
+      <c r="Z33" s="4"/>
+      <c r="AA33" s="4"/>
       <c r="AB33" s="4"/>
       <c r="AC33" s="4"/>
       <c r="AD33" s="4"/>
@@ -3460,67 +3460,67 @@
     <row r="34" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="4"/>
       <c r="B34" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E34" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I34" s="4"/>
       <c r="J34" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
       <c r="M34" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N34" s="4"/>
       <c r="O34" s="4"/>
       <c r="P34" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q34" s="4">
         <v>1</v>
       </c>
       <c r="R34" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S34" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T34" s="4">
         <v>1</v>
       </c>
       <c r="U34" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V34" s="4"/>
       <c r="W34" s="4"/>
-      <c r="X34" s="4"/>
-      <c r="Y34" s="4"/>
-      <c r="Z34" s="5"/>
-      <c r="AA34" s="5"/>
+      <c r="X34" s="5"/>
+      <c r="Y34" s="5"/>
+      <c r="Z34" s="4"/>
+      <c r="AA34" s="4"/>
       <c r="AB34" s="4"/>
       <c r="AC34" s="4"/>
       <c r="AD34" s="4"/>
       <c r="AE34" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AF34" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AG34" s="4"/>
       <c r="AH34" s="4"/>
@@ -3544,67 +3544,67 @@
     <row r="35" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="4"/>
       <c r="B35" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D35" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E35" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I35" s="4"/>
       <c r="J35" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
       <c r="M35" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N35" s="4"/>
       <c r="O35" s="4"/>
       <c r="P35" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q35" s="4">
         <v>30</v>
       </c>
       <c r="R35" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S35" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T35" s="4">
         <v>1</v>
       </c>
       <c r="U35" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V35" s="4"/>
       <c r="W35" s="4"/>
-      <c r="X35" s="4"/>
-      <c r="Y35" s="4"/>
-      <c r="Z35" s="5"/>
-      <c r="AA35" s="5"/>
+      <c r="X35" s="5"/>
+      <c r="Y35" s="5"/>
+      <c r="Z35" s="4"/>
+      <c r="AA35" s="4"/>
       <c r="AB35" s="4"/>
       <c r="AC35" s="4"/>
       <c r="AD35" s="4"/>
       <c r="AE35" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AF35" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AG35" s="4"/>
       <c r="AH35" s="4"/>
@@ -3628,67 +3628,67 @@
     <row r="36" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="4"/>
       <c r="B36" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C36" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E36" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G36" s="4"/>
       <c r="H36" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I36" s="4"/>
       <c r="J36" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
       <c r="M36" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N36" s="4"/>
       <c r="O36" s="4"/>
       <c r="P36" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q36" s="4">
         <v>1</v>
       </c>
       <c r="R36" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S36" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T36" s="4">
         <v>1</v>
       </c>
       <c r="U36" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V36" s="4"/>
       <c r="W36" s="4"/>
-      <c r="X36" s="4"/>
-      <c r="Y36" s="4"/>
-      <c r="Z36" s="5"/>
-      <c r="AA36" s="5"/>
+      <c r="X36" s="5"/>
+      <c r="Y36" s="5"/>
+      <c r="Z36" s="4"/>
+      <c r="AA36" s="4"/>
       <c r="AB36" s="4"/>
       <c r="AC36" s="4"/>
       <c r="AD36" s="4"/>
       <c r="AE36" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AF36" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AG36" s="4"/>
       <c r="AH36" s="4"/>
@@ -3710,67 +3710,67 @@
     <row r="37" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="4"/>
       <c r="B37" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C37" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E37" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I37" s="4"/>
       <c r="J37" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
       <c r="M37" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N37" s="4"/>
       <c r="O37" s="4"/>
       <c r="P37" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q37" s="4">
         <v>30</v>
       </c>
       <c r="R37" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S37" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T37" s="4">
         <v>1</v>
       </c>
       <c r="U37" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V37" s="4"/>
       <c r="W37" s="4"/>
-      <c r="X37" s="4"/>
-      <c r="Y37" s="4"/>
-      <c r="Z37" s="5"/>
-      <c r="AA37" s="5"/>
+      <c r="X37" s="5"/>
+      <c r="Y37" s="5"/>
+      <c r="Z37" s="4"/>
+      <c r="AA37" s="4"/>
       <c r="AB37" s="4"/>
       <c r="AC37" s="4"/>
       <c r="AD37" s="4"/>
       <c r="AE37" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AF37" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AG37" s="4"/>
       <c r="AH37" s="4"/>
@@ -3792,67 +3792,67 @@
     <row r="38" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="4"/>
       <c r="B38" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C38" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E38" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I38" s="4"/>
       <c r="J38" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
       <c r="M38" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N38" s="4"/>
       <c r="O38" s="4"/>
       <c r="P38" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q38" s="4">
         <v>1</v>
       </c>
       <c r="R38" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S38" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T38" s="4">
         <v>1</v>
       </c>
       <c r="U38" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V38" s="4"/>
       <c r="W38" s="4"/>
-      <c r="X38" s="4"/>
-      <c r="Y38" s="4"/>
-      <c r="Z38" s="5"/>
-      <c r="AA38" s="5"/>
+      <c r="X38" s="5"/>
+      <c r="Y38" s="5"/>
+      <c r="Z38" s="4"/>
+      <c r="AA38" s="4"/>
       <c r="AB38" s="4"/>
       <c r="AC38" s="4"/>
       <c r="AD38" s="4"/>
       <c r="AE38" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AF38" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AG38" s="4"/>
       <c r="AH38" s="4"/>
@@ -3876,67 +3876,67 @@
     <row r="39" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="4"/>
       <c r="B39" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D39" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C39" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E39" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I39" s="4"/>
       <c r="J39" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
       <c r="M39" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N39" s="4"/>
       <c r="O39" s="4"/>
       <c r="P39" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q39" s="4">
         <v>30</v>
       </c>
       <c r="R39" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S39" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T39" s="4">
         <v>1</v>
       </c>
       <c r="U39" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V39" s="4"/>
       <c r="W39" s="4"/>
-      <c r="X39" s="4"/>
-      <c r="Y39" s="4"/>
-      <c r="Z39" s="5"/>
-      <c r="AA39" s="5"/>
+      <c r="X39" s="5"/>
+      <c r="Y39" s="5"/>
+      <c r="Z39" s="4"/>
+      <c r="AA39" s="4"/>
       <c r="AB39" s="4"/>
       <c r="AC39" s="4"/>
       <c r="AD39" s="4"/>
       <c r="AE39" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AF39" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AG39" s="4"/>
       <c r="AH39" s="4"/>
@@ -3960,67 +3960,67 @@
     <row r="40" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="4"/>
       <c r="B40" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D40" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E40" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I40" s="4"/>
       <c r="J40" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
       <c r="M40" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N40" s="4"/>
       <c r="O40" s="4"/>
       <c r="P40" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q40" s="4">
         <v>1</v>
       </c>
       <c r="R40" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S40" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T40" s="4">
         <v>1</v>
       </c>
       <c r="U40" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V40" s="4"/>
       <c r="W40" s="4"/>
-      <c r="X40" s="4"/>
-      <c r="Y40" s="4"/>
-      <c r="Z40" s="5"/>
-      <c r="AA40" s="5"/>
+      <c r="X40" s="5"/>
+      <c r="Y40" s="5"/>
+      <c r="Z40" s="4"/>
+      <c r="AA40" s="4"/>
       <c r="AB40" s="4"/>
       <c r="AC40" s="4"/>
       <c r="AD40" s="4"/>
       <c r="AE40" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AF40" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AG40" s="4"/>
       <c r="AH40" s="4"/>
@@ -4042,67 +4042,67 @@
     <row r="41" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="4"/>
       <c r="B41" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D41" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C41" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E41" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I41" s="4"/>
       <c r="J41" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
       <c r="M41" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N41" s="4"/>
       <c r="O41" s="4"/>
       <c r="P41" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q41" s="4">
         <v>30</v>
       </c>
       <c r="R41" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S41" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T41" s="4">
         <v>1</v>
       </c>
       <c r="U41" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V41" s="4"/>
       <c r="W41" s="4"/>
-      <c r="X41" s="4"/>
-      <c r="Y41" s="4"/>
-      <c r="Z41" s="5"/>
-      <c r="AA41" s="5"/>
+      <c r="X41" s="5"/>
+      <c r="Y41" s="5"/>
+      <c r="Z41" s="4"/>
+      <c r="AA41" s="4"/>
       <c r="AB41" s="4"/>
       <c r="AC41" s="4"/>
       <c r="AD41" s="4"/>
       <c r="AE41" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AF41" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AG41" s="4"/>
       <c r="AH41" s="4"/>
@@ -4124,67 +4124,67 @@
     <row r="42" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="4"/>
       <c r="B42" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E42" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I42" s="4"/>
       <c r="J42" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
       <c r="M42" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N42" s="4"/>
       <c r="O42" s="4"/>
       <c r="P42" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q42" s="4">
         <v>1</v>
       </c>
       <c r="R42" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S42" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T42" s="4">
         <v>1</v>
       </c>
       <c r="U42" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V42" s="4"/>
       <c r="W42" s="4"/>
-      <c r="X42" s="4"/>
-      <c r="Y42" s="4"/>
-      <c r="Z42" s="5"/>
-      <c r="AA42" s="5"/>
+      <c r="X42" s="5"/>
+      <c r="Y42" s="5"/>
+      <c r="Z42" s="4"/>
+      <c r="AA42" s="4"/>
       <c r="AB42" s="4"/>
       <c r="AC42" s="4"/>
       <c r="AD42" s="4"/>
       <c r="AE42" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AF42" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AG42" s="4"/>
       <c r="AH42" s="4"/>
@@ -4206,67 +4206,67 @@
     <row r="43" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="4"/>
       <c r="B43" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C43" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E43" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I43" s="4"/>
       <c r="J43" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
       <c r="M43" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N43" s="4"/>
       <c r="O43" s="4"/>
       <c r="P43" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q43" s="4">
         <v>1</v>
       </c>
       <c r="R43" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S43" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T43" s="4">
         <v>1</v>
       </c>
       <c r="U43" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V43" s="4"/>
       <c r="W43" s="4"/>
-      <c r="X43" s="4"/>
-      <c r="Y43" s="4"/>
-      <c r="Z43" s="5"/>
-      <c r="AA43" s="5"/>
+      <c r="X43" s="5"/>
+      <c r="Y43" s="5"/>
+      <c r="Z43" s="4"/>
+      <c r="AA43" s="4"/>
       <c r="AB43" s="4"/>
       <c r="AC43" s="4"/>
       <c r="AD43" s="4"/>
       <c r="AE43" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AF43" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AG43" s="4"/>
       <c r="AH43" s="4"/>
@@ -4288,67 +4288,67 @@
     <row r="44" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="4"/>
       <c r="B44" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C44" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E44" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I44" s="4"/>
       <c r="J44" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
       <c r="M44" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N44" s="4"/>
       <c r="O44" s="4"/>
       <c r="P44" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q44" s="4">
         <v>30</v>
       </c>
       <c r="R44" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S44" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T44" s="4">
         <v>1</v>
       </c>
       <c r="U44" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V44" s="4"/>
       <c r="W44" s="4"/>
-      <c r="X44" s="4"/>
-      <c r="Y44" s="4"/>
-      <c r="Z44" s="5"/>
-      <c r="AA44" s="5"/>
+      <c r="X44" s="5"/>
+      <c r="Y44" s="5"/>
+      <c r="Z44" s="4"/>
+      <c r="AA44" s="4"/>
       <c r="AB44" s="4"/>
       <c r="AC44" s="4"/>
       <c r="AD44" s="4"/>
       <c r="AE44" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AF44" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AG44" s="4"/>
       <c r="AH44" s="4"/>
@@ -4370,57 +4370,57 @@
     <row r="45" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="4"/>
       <c r="B45" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
       <c r="J45" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
       <c r="M45" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N45" s="4"/>
       <c r="O45" s="4">
         <v>1000</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q45" s="4">
         <v>1</v>
       </c>
       <c r="R45" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S45" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T45" s="4">
         <v>1</v>
       </c>
       <c r="U45" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V45" s="4"/>
       <c r="W45" s="4"/>
-      <c r="X45" s="4"/>
-      <c r="Y45" s="4"/>
-      <c r="Z45" s="5"/>
-      <c r="AA45" s="5"/>
+      <c r="X45" s="5"/>
+      <c r="Y45" s="5"/>
+      <c r="Z45" s="4"/>
+      <c r="AA45" s="4"/>
       <c r="AB45" s="4"/>
       <c r="AC45" s="4"/>
       <c r="AD45" s="4"/>
@@ -4441,59 +4441,59 @@
     <row r="46" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="4"/>
       <c r="B46" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D46" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C46" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E46" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I46" s="4"/>
       <c r="J46" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
       <c r="M46" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N46" s="4"/>
       <c r="O46" s="4">
         <v>860000</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q46" s="4">
         <v>1</v>
       </c>
       <c r="R46" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S46" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T46" s="4">
         <v>1</v>
       </c>
       <c r="U46" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V46" s="4"/>
       <c r="W46" s="4"/>
-      <c r="X46" s="4"/>
-      <c r="Y46" s="4"/>
-      <c r="Z46" s="5"/>
-      <c r="AA46" s="5"/>
+      <c r="X46" s="5"/>
+      <c r="Y46" s="5"/>
+      <c r="Z46" s="4"/>
+      <c r="AA46" s="4"/>
       <c r="AB46" s="4"/>
       <c r="AC46" s="4"/>
       <c r="AD46" s="4"/>
@@ -4514,59 +4514,59 @@
     <row r="47" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
       <c r="B47" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D47" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C47" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E47" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I47" s="4"/>
       <c r="J47" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
       <c r="M47" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N47" s="4"/>
       <c r="O47" s="4">
         <v>230000</v>
       </c>
       <c r="P47" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q47" s="4">
         <v>30</v>
       </c>
       <c r="R47" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S47" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T47" s="4">
         <v>1</v>
       </c>
       <c r="U47" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V47" s="4"/>
       <c r="W47" s="4"/>
-      <c r="X47" s="4"/>
-      <c r="Y47" s="4"/>
-      <c r="Z47" s="5"/>
-      <c r="AA47" s="5"/>
+      <c r="X47" s="5"/>
+      <c r="Y47" s="5"/>
+      <c r="Z47" s="4"/>
+      <c r="AA47" s="4"/>
       <c r="AB47" s="4"/>
       <c r="AC47" s="4"/>
       <c r="AD47" s="4"/>
@@ -4587,61 +4587,61 @@
     <row r="48" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="4"/>
       <c r="B48" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D48" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E48" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I48" s="4"/>
       <c r="J48" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
       <c r="M48" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N48" s="4"/>
       <c r="O48" s="4">
         <v>19</v>
       </c>
       <c r="P48" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q48" s="4">
         <v>1</v>
       </c>
       <c r="R48" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S48" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T48" s="4">
         <v>1</v>
       </c>
       <c r="U48" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V48" s="4"/>
       <c r="W48" s="4"/>
-      <c r="X48" s="4"/>
-      <c r="Y48" s="4"/>
-      <c r="Z48" s="5"/>
-      <c r="AA48" s="5"/>
+      <c r="X48" s="5"/>
+      <c r="Y48" s="5"/>
+      <c r="Z48" s="4"/>
+      <c r="AA48" s="4"/>
       <c r="AB48" s="4"/>
       <c r="AC48" s="4"/>
       <c r="AD48" s="4"/>
@@ -4662,61 +4662,61 @@
     <row r="49" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
       <c r="B49" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D49" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C49" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E49" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I49" s="4"/>
       <c r="J49" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
       <c r="M49" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N49" s="4"/>
       <c r="O49" s="4">
         <v>11</v>
       </c>
       <c r="P49" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q49" s="4">
         <v>30</v>
       </c>
       <c r="R49" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S49" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T49" s="4">
         <v>1</v>
       </c>
       <c r="U49" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V49" s="4"/>
       <c r="W49" s="4"/>
-      <c r="X49" s="4"/>
-      <c r="Y49" s="4"/>
-      <c r="Z49" s="5"/>
-      <c r="AA49" s="5"/>
+      <c r="X49" s="5"/>
+      <c r="Y49" s="5"/>
+      <c r="Z49" s="4"/>
+      <c r="AA49" s="4"/>
       <c r="AB49" s="4"/>
       <c r="AC49" s="4"/>
       <c r="AD49" s="4"/>
@@ -4737,59 +4737,59 @@
     <row r="50" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="4"/>
       <c r="B50" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D50" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C50" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E50" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
       <c r="H50" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I50" s="4"/>
       <c r="J50" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
       <c r="M50" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N50" s="4"/>
       <c r="O50" s="4">
         <v>1000</v>
       </c>
       <c r="P50" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q50" s="4">
         <v>30</v>
       </c>
       <c r="R50" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S50" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T50" s="4">
         <v>1</v>
       </c>
       <c r="U50" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V50" s="4"/>
       <c r="W50" s="4"/>
-      <c r="X50" s="4"/>
-      <c r="Y50" s="4"/>
-      <c r="Z50" s="5"/>
-      <c r="AA50" s="5"/>
+      <c r="X50" s="5"/>
+      <c r="Y50" s="5"/>
+      <c r="Z50" s="4"/>
+      <c r="AA50" s="4"/>
       <c r="AB50" s="4"/>
       <c r="AC50" s="4"/>
       <c r="AD50" s="4"/>
@@ -4810,57 +4810,57 @@
     <row r="51" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="4"/>
       <c r="B51" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
       <c r="J51" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
       <c r="M51" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N51" s="4"/>
       <c r="O51" s="4">
         <v>10000</v>
       </c>
       <c r="P51" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q51" s="4">
         <v>1</v>
       </c>
       <c r="R51" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S51" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T51" s="4">
         <v>1</v>
       </c>
       <c r="U51" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V51" s="4"/>
       <c r="W51" s="4"/>
-      <c r="X51" s="4"/>
-      <c r="Y51" s="4"/>
-      <c r="Z51" s="5"/>
-      <c r="AA51" s="5"/>
+      <c r="X51" s="5"/>
+      <c r="Y51" s="5"/>
+      <c r="Z51" s="4"/>
+      <c r="AA51" s="4"/>
       <c r="AB51" s="4"/>
       <c r="AC51" s="4"/>
       <c r="AD51" s="4"/>
@@ -4881,30 +4881,30 @@
     <row r="52" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="4"/>
       <c r="B52" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D52" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C52" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E52" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I52" s="4"/>
       <c r="J52" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
       <c r="M52" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N52" s="4">
         <v>6.5</v>
@@ -4913,29 +4913,29 @@
         <v>9</v>
       </c>
       <c r="P52" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="Q52" s="4">
         <v>7</v>
       </c>
       <c r="R52" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S52" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T52" s="4">
         <v>1</v>
       </c>
       <c r="U52" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V52" s="4"/>
       <c r="W52" s="4"/>
-      <c r="X52" s="4"/>
-      <c r="Y52" s="4"/>
-      <c r="Z52" s="5"/>
-      <c r="AA52" s="5"/>
+      <c r="X52" s="5"/>
+      <c r="Y52" s="5"/>
+      <c r="Z52" s="4"/>
+      <c r="AA52" s="4"/>
       <c r="AB52" s="4"/>
       <c r="AC52" s="4"/>
       <c r="AD52" s="4"/>
@@ -4956,28 +4956,28 @@
     <row r="53" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="4"/>
       <c r="B53" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
       <c r="J53" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
       <c r="M53" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N53" s="4">
         <v>5</v>
@@ -4986,29 +4986,29 @@
         <v>9</v>
       </c>
       <c r="P53" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="Q53" s="4">
         <v>1</v>
       </c>
       <c r="R53" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S53" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T53" s="4">
         <v>1</v>
       </c>
       <c r="U53" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V53" s="4"/>
       <c r="W53" s="4"/>
-      <c r="X53" s="4"/>
-      <c r="Y53" s="4"/>
-      <c r="Z53" s="5"/>
-      <c r="AA53" s="5"/>
+      <c r="X53" s="5"/>
+      <c r="Y53" s="5"/>
+      <c r="Z53" s="4"/>
+      <c r="AA53" s="4"/>
       <c r="AB53" s="4"/>
       <c r="AC53" s="4"/>
       <c r="AD53" s="4"/>
@@ -5029,59 +5029,59 @@
     <row r="54" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="4"/>
       <c r="B54" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
       <c r="J54" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>
       <c r="M54" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N54" s="4"/>
       <c r="O54" s="4">
         <v>250000</v>
       </c>
       <c r="P54" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q54" s="4">
         <v>1</v>
       </c>
       <c r="R54" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S54" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T54" s="4">
         <v>1</v>
       </c>
       <c r="U54" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V54" s="4"/>
       <c r="W54" s="4"/>
-      <c r="X54" s="4"/>
-      <c r="Y54" s="4"/>
-      <c r="Z54" s="5"/>
-      <c r="AA54" s="5"/>
+      <c r="X54" s="5"/>
+      <c r="Y54" s="5"/>
+      <c r="Z54" s="4"/>
+      <c r="AA54" s="4"/>
       <c r="AB54" s="4"/>
       <c r="AC54" s="4"/>
       <c r="AD54" s="4"/>
@@ -5102,57 +5102,57 @@
     <row r="55" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="4"/>
       <c r="B55" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
       <c r="J55" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K55" s="4"/>
       <c r="L55" s="4"/>
       <c r="M55" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N55" s="4"/>
       <c r="O55" s="4">
         <v>126</v>
       </c>
       <c r="P55" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="Q55" s="4">
         <v>90</v>
       </c>
       <c r="R55" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S55" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T55" s="4">
         <v>1</v>
       </c>
       <c r="U55" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V55" s="4"/>
       <c r="W55" s="4"/>
-      <c r="X55" s="4"/>
-      <c r="Y55" s="4"/>
-      <c r="Z55" s="5"/>
-      <c r="AA55" s="5"/>
+      <c r="X55" s="5"/>
+      <c r="Y55" s="5"/>
+      <c r="Z55" s="4"/>
+      <c r="AA55" s="4"/>
       <c r="AB55" s="4"/>
       <c r="AC55" s="4"/>
       <c r="AD55" s="4"/>
@@ -5173,57 +5173,57 @@
     <row r="56" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="4"/>
       <c r="B56" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
       <c r="J56" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K56" s="4"/>
       <c r="L56" s="4"/>
       <c r="M56" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N56" s="4"/>
       <c r="O56" s="4">
         <v>410</v>
       </c>
       <c r="P56" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="Q56" s="4">
         <v>90</v>
       </c>
       <c r="R56" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S56" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T56" s="4">
         <v>10</v>
       </c>
       <c r="U56" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V56" s="4"/>
       <c r="W56" s="4"/>
-      <c r="X56" s="4"/>
-      <c r="Y56" s="4"/>
-      <c r="Z56" s="5"/>
-      <c r="AA56" s="5"/>
+      <c r="X56" s="5"/>
+      <c r="Y56" s="5"/>
+      <c r="Z56" s="4"/>
+      <c r="AA56" s="4"/>
       <c r="AB56" s="4"/>
       <c r="AC56" s="4"/>
       <c r="AD56" s="4"/>
@@ -5244,57 +5244,57 @@
     <row r="57" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="4"/>
       <c r="B57" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
       <c r="J57" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K57" s="4"/>
       <c r="L57" s="4"/>
       <c r="M57" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N57" s="4"/>
       <c r="O57" s="4">
         <v>8</v>
       </c>
       <c r="P57" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q57" s="4">
         <v>1</v>
       </c>
       <c r="R57" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S57" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T57" s="4">
         <v>1</v>
       </c>
       <c r="U57" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="V57" s="4"/>
       <c r="W57" s="4"/>
-      <c r="X57" s="4"/>
-      <c r="Y57" s="4"/>
-      <c r="Z57" s="5"/>
-      <c r="AA57" s="5"/>
+      <c r="X57" s="5"/>
+      <c r="Y57" s="5"/>
+      <c r="Z57" s="4"/>
+      <c r="AA57" s="4"/>
       <c r="AB57" s="4"/>
       <c r="AC57" s="4"/>
       <c r="AD57" s="4"/>
@@ -5315,57 +5315,57 @@
     <row r="58" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="4"/>
       <c r="B58" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
       <c r="J58" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K58" s="4"/>
       <c r="L58" s="4"/>
       <c r="M58" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N58" s="4"/>
       <c r="O58" s="4">
         <v>15</v>
       </c>
       <c r="P58" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q58" s="4">
         <v>1</v>
       </c>
       <c r="R58" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S58" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T58" s="4">
         <v>1</v>
       </c>
       <c r="U58" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="V58" s="4"/>
       <c r="W58" s="4"/>
-      <c r="X58" s="4"/>
-      <c r="Y58" s="4"/>
-      <c r="Z58" s="5"/>
-      <c r="AA58" s="5"/>
+      <c r="X58" s="5"/>
+      <c r="Y58" s="5"/>
+      <c r="Z58" s="4"/>
+      <c r="AA58" s="4"/>
       <c r="AB58" s="4"/>
       <c r="AC58" s="4"/>
       <c r="AD58" s="4"/>
@@ -5386,61 +5386,61 @@
     <row r="59" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="4"/>
       <c r="B59" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E59" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
       <c r="J59" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K59" s="4"/>
       <c r="L59" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="M59" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N59" s="4">
         <v>9.5</v>
       </c>
       <c r="O59" s="4"/>
       <c r="P59" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Q59" s="4">
         <v>7</v>
       </c>
       <c r="R59" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S59" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T59" s="4">
         <v>1</v>
       </c>
       <c r="U59" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V59" s="4"/>
       <c r="W59" s="4"/>
-      <c r="X59" s="4"/>
-      <c r="Y59" s="4"/>
-      <c r="Z59" s="5"/>
-      <c r="AA59" s="5"/>
+      <c r="X59" s="5"/>
+      <c r="Y59" s="5"/>
+      <c r="Z59" s="4"/>
+      <c r="AA59" s="4"/>
       <c r="AB59" s="4"/>
       <c r="AC59" s="4"/>
       <c r="AD59" s="4"/>
@@ -5461,61 +5461,61 @@
     <row r="60" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="4"/>
       <c r="B60" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D60" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E60" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
       <c r="J60" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K60" s="4"/>
       <c r="L60" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M60" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N60" s="4">
         <v>6.5</v>
       </c>
       <c r="O60" s="4"/>
       <c r="P60" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Q60" s="4">
         <v>30</v>
       </c>
       <c r="R60" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S60" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T60" s="4">
         <v>1</v>
       </c>
       <c r="U60" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V60" s="4"/>
       <c r="W60" s="4"/>
-      <c r="X60" s="4"/>
-      <c r="Y60" s="4"/>
-      <c r="Z60" s="5"/>
-      <c r="AA60" s="5"/>
+      <c r="X60" s="5"/>
+      <c r="Y60" s="5"/>
+      <c r="Z60" s="4"/>
+      <c r="AA60" s="4"/>
       <c r="AB60" s="4"/>
       <c r="AC60" s="4"/>
       <c r="AD60" s="4"/>
@@ -5536,61 +5536,61 @@
     <row r="61" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="4"/>
       <c r="B61" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D61" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C61" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E61" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
       <c r="J61" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K61" s="4"/>
       <c r="L61" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M61" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N61" s="4">
         <v>5</v>
       </c>
       <c r="O61" s="4"/>
       <c r="P61" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Q61" s="4">
         <v>7</v>
       </c>
       <c r="R61" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S61" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="T61" s="4">
         <v>1</v>
       </c>
       <c r="U61" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V61" s="4"/>
       <c r="W61" s="4"/>
-      <c r="X61" s="4"/>
-      <c r="Y61" s="4"/>
-      <c r="Z61" s="5"/>
-      <c r="AA61" s="5"/>
+      <c r="X61" s="5"/>
+      <c r="Y61" s="5"/>
+      <c r="Z61" s="4"/>
+      <c r="AA61" s="4"/>
       <c r="AB61" s="4"/>
       <c r="AC61" s="4"/>
       <c r="AD61" s="4"/>
@@ -5611,61 +5611,61 @@
     <row r="62" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="4"/>
       <c r="B62" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D62" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C62" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E62" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
       <c r="J62" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K62" s="4"/>
       <c r="L62" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="M62" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N62" s="4">
         <v>8</v>
       </c>
       <c r="O62" s="4"/>
       <c r="P62" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Q62" s="4">
         <v>1</v>
       </c>
       <c r="R62" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S62" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="T62" s="4">
         <v>1</v>
       </c>
       <c r="U62" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V62" s="4"/>
       <c r="W62" s="4"/>
-      <c r="X62" s="4"/>
-      <c r="Y62" s="4"/>
-      <c r="Z62" s="5"/>
-      <c r="AA62" s="5"/>
+      <c r="X62" s="5"/>
+      <c r="Y62" s="5"/>
+      <c r="Z62" s="4"/>
+      <c r="AA62" s="4"/>
       <c r="AB62" s="4"/>
       <c r="AC62" s="4"/>
       <c r="AD62" s="4"/>
@@ -5686,61 +5686,61 @@
     <row r="63" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="4"/>
       <c r="B63" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D63" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C63" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E63" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
       <c r="J63" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K63" s="4"/>
       <c r="L63" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N63" s="4">
         <v>4</v>
       </c>
       <c r="O63" s="4"/>
       <c r="P63" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Q63" s="4">
         <v>1</v>
       </c>
       <c r="R63" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S63" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="T63" s="4">
         <v>1</v>
       </c>
       <c r="U63" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V63" s="4"/>
       <c r="W63" s="4"/>
-      <c r="X63" s="4"/>
-      <c r="Y63" s="4"/>
-      <c r="Z63" s="5"/>
-      <c r="AA63" s="5"/>
+      <c r="X63" s="5"/>
+      <c r="Y63" s="5"/>
+      <c r="Z63" s="4"/>
+      <c r="AA63" s="4"/>
       <c r="AB63" s="4"/>
       <c r="AC63" s="4"/>
       <c r="AD63" s="4"/>
@@ -5761,69 +5761,69 @@
     <row r="64" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="4"/>
       <c r="B64" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D64" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C64" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E64" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G64" s="4"/>
       <c r="H64" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I64" s="4"/>
       <c r="J64" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K64" s="4"/>
       <c r="L64" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="M64" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N64" s="4"/>
       <c r="O64" s="4"/>
       <c r="P64" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Q64" s="4">
         <v>1</v>
       </c>
       <c r="R64" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="S64" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="T64" s="4">
+        <v>1</v>
+      </c>
+      <c r="U64" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="S64" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="T64" s="4">
-        <v>1</v>
-      </c>
-      <c r="U64" s="4" t="s">
-        <v>49</v>
       </c>
       <c r="V64" s="4"/>
       <c r="W64" s="4"/>
-      <c r="X64" s="4"/>
-      <c r="Y64" s="4"/>
-      <c r="Z64" s="5"/>
-      <c r="AA64" s="5"/>
+      <c r="X64" s="5"/>
+      <c r="Y64" s="5"/>
+      <c r="Z64" s="4"/>
+      <c r="AA64" s="4"/>
       <c r="AB64" s="4"/>
       <c r="AC64" s="4"/>
       <c r="AD64" s="4"/>
       <c r="AE64" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="AF64" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AG64" s="4"/>
       <c r="AH64" s="4"/>
@@ -5832,7 +5832,7 @@
       <c r="AK64" s="4"/>
       <c r="AL64" s="4"/>
       <c r="AM64" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AN64" s="6">
         <v>0.27500000000000002</v>
@@ -5874,67 +5874,67 @@
     <row r="65" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="4"/>
       <c r="B65" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D65" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C65" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E65" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G65" s="4"/>
       <c r="H65" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I65" s="4"/>
       <c r="J65" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K65" s="4"/>
       <c r="L65" s="6"/>
       <c r="M65" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N65" s="4"/>
       <c r="O65" s="4"/>
       <c r="P65" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Q65" s="4">
         <v>30</v>
       </c>
       <c r="R65" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="S65" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="T65" s="4">
+        <v>1</v>
+      </c>
+      <c r="U65" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="S65" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="T65" s="4">
-        <v>1</v>
-      </c>
-      <c r="U65" s="4" t="s">
-        <v>49</v>
       </c>
       <c r="V65" s="4"/>
       <c r="W65" s="4"/>
-      <c r="X65" s="4"/>
-      <c r="Y65" s="4"/>
-      <c r="Z65" s="5"/>
-      <c r="AA65" s="5"/>
+      <c r="X65" s="5"/>
+      <c r="Y65" s="5"/>
+      <c r="Z65" s="4"/>
+      <c r="AA65" s="4"/>
       <c r="AB65" s="4"/>
       <c r="AC65" s="4"/>
       <c r="AD65" s="4"/>
       <c r="AE65" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="AF65" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AG65" s="4"/>
       <c r="AH65" s="4"/>
@@ -5943,7 +5943,7 @@
       <c r="AK65" s="4"/>
       <c r="AL65" s="4"/>
       <c r="AM65" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="AN65" s="6">
         <v>2.7799999999999998E-2</v>
